--- a/data/prod_parameters/PlantNutrientMgmt.xlsx
+++ b/data/prod_parameters/PlantNutrientMgmt.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="124">
   <si>
     <t>f_crop</t>
   </si>
@@ -295,8 +295,89 @@
     <t>f_prod_system</t>
   </si>
   <si>
+    <t>4 Svealands slättbygder</t>
+  </si>
+  <si>
+    <t>5 Götalands skogsbygder</t>
+  </si>
+  <si>
+    <t>3 Götalands norra slättbygder</t>
+  </si>
+  <si>
+    <t>6 Mellersta Sveriges skogsbygder</t>
+  </si>
+  <si>
+    <t>2 Götalands mellanbygder</t>
+  </si>
+  <si>
+    <t>1 Götalands södra slättbygder</t>
+  </si>
+  <si>
+    <t>7 Nedre Norrland</t>
+  </si>
+  <si>
+    <t>8 Övre Norrland</t>
+  </si>
+  <si>
+    <t>po8</t>
+  </si>
+  <si>
+    <t>f_po8</t>
+  </si>
+  <si>
+    <t>Höstvete foder/bröd, södra götaland</t>
+  </si>
+  <si>
+    <t>Höstevete foder/bröd norra götaland och svealand</t>
+  </si>
+  <si>
+    <t>Rågvete/höstkorn, södra götaland</t>
+  </si>
+  <si>
+    <t>Råg, södra götaland</t>
+  </si>
+  <si>
+    <t>Korn foder, södra götaland</t>
+  </si>
+  <si>
+    <t>Korn, malt södra götaland</t>
+  </si>
+  <si>
+    <t>Havre södra götaland</t>
+  </si>
+  <si>
+    <t>Korn, norrland</t>
+  </si>
+  <si>
+    <t>Potatis</t>
+  </si>
+  <si>
+    <t>Assume same as apples</t>
+  </si>
+  <si>
+    <t>Assume same as carrots</t>
+  </si>
+  <si>
+    <t>Assume same as lettuce</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>organic</t>
+  </si>
+  <si>
+    <t>kg P/ha</t>
+  </si>
+  <si>
+    <t>manure_P_max</t>
+  </si>
+  <si>
+    <t>Chapter 2.2.4.1 in Rekommendationer för gödsling och kalkning 2023</t>
+  </si>
+  <si>
     <r>
-      <t xml:space="preserve">N recommendation [kg plant available N / ha] as a function of yield [tonnes] </t>
+      <t xml:space="preserve">TAN recommendation [kg plant available N / ha] as a function of yield [tonnes] </t>
     </r>
     <r>
       <rPr>
@@ -311,7 +392,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">N application adjustment factor as a function of ley in region </t>
+      <t xml:space="preserve">TAN application adjustment factor as a function of ley in region </t>
     </r>
     <r>
       <rPr>
@@ -325,70 +406,16 @@
     </r>
   </si>
   <si>
-    <t>4 Svealands slättbygder</t>
-  </si>
-  <si>
-    <t>5 Götalands skogsbygder</t>
-  </si>
-  <si>
-    <t>3 Götalands norra slättbygder</t>
-  </si>
-  <si>
-    <t>6 Mellersta Sveriges skogsbygder</t>
-  </si>
-  <si>
-    <t>2 Götalands mellanbygder</t>
-  </si>
-  <si>
-    <t>1 Götalands södra slättbygder</t>
-  </si>
-  <si>
-    <t>7 Nedre Norrland</t>
-  </si>
-  <si>
-    <t>8 Övre Norrland</t>
-  </si>
-  <si>
-    <t>po8</t>
-  </si>
-  <si>
-    <t>f_po8</t>
-  </si>
-  <si>
-    <t>Höstvete foder/bröd, södra götaland</t>
-  </si>
-  <si>
-    <t>Höstevete foder/bröd norra götaland och svealand</t>
-  </si>
-  <si>
-    <t>Rågvete/höstkorn, södra götaland</t>
-  </si>
-  <si>
-    <t>Råg, södra götaland</t>
-  </si>
-  <si>
-    <t>Korn foder, södra götaland</t>
-  </si>
-  <si>
-    <t>Korn, malt södra götaland</t>
-  </si>
-  <si>
-    <t>Havre södra götaland</t>
-  </si>
-  <si>
-    <t>Korn, norrland</t>
-  </si>
-  <si>
-    <t>Potatis</t>
-  </si>
-  <si>
-    <t>Assume same as apples</t>
-  </si>
-  <si>
-    <t>Assume same as carrots</t>
-  </si>
-  <si>
-    <t>Assume same as lettuce</t>
+    <t>max P allowed on cropland on regional level</t>
+  </si>
+  <si>
+    <t>manure_TAN_max</t>
+  </si>
+  <si>
+    <t>Share of TAN requirements covered by manure. Based on 20,000 tonnes N from manure (incl. digested) of 22,000 tonnes N in total applied on organic areas.</t>
+  </si>
+  <si>
+    <t>Specialbearbetning av stallgödselundersökningen till Einarsson et al 2022. The nitrogen footprint of Swedish food consumption.</t>
   </si>
 </sst>
 </file>
@@ -777,14 +804,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L226"/>
+  <dimension ref="A1:L231"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.42578125" customWidth="1"/>
     <col min="2" max="2" width="7.28515625" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="31.42578125" customWidth="1"/>
-    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="5" max="5" width="23.7109375" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
     <col min="7" max="7" width="8.140625" customWidth="1"/>
     <col min="8" max="8" width="35.42578125" customWidth="1"/>
@@ -802,7 +829,7 @@
         <v>90</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
@@ -820,184 +847,140 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F3">
         <v>91</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E3" s="6" t="s">
+      <c r="G3" t="s">
+        <v>113</v>
+      </c>
+      <c r="H3" t="s">
+        <v>122</v>
+      </c>
+      <c r="I3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E5" t="s">
+        <v>116</v>
+      </c>
+      <c r="F5">
+        <v>22</v>
+      </c>
+      <c r="G5" t="s">
+        <v>115</v>
+      </c>
+      <c r="H5" t="s">
+        <v>120</v>
+      </c>
+      <c r="I5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E8" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F8" s="6">
         <v>0</v>
       </c>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6" t="s">
+      <c r="G8" s="6"/>
+      <c r="H8" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E4" s="6" t="s">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F9" s="6">
         <v>0</v>
       </c>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6" t="s">
+      <c r="G9" s="6"/>
+      <c r="H9" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="6">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E10" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="6">
         <v>0</v>
       </c>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6" t="s">
+      <c r="G10" s="6"/>
+      <c r="H10" s="6" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6">
-        <v>-0.80359999999999998</v>
-      </c>
-      <c r="H6" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7">
-        <v>24.088999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8">
-        <v>50.213999999999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9">
-        <v>55.213999999999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" t="s">
-        <v>98</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10">
-        <v>-0.71430000000000005</v>
-      </c>
-      <c r="H10" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>7</v>
       </c>
-      <c r="D11" t="s">
-        <v>98</v>
-      </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F11">
-        <v>23.143000000000001</v>
+        <v>-0.80359999999999998</v>
+      </c>
+      <c r="H11" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>7</v>
       </c>
-      <c r="D12" t="s">
-        <v>98</v>
-      </c>
       <c r="E12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F12">
-        <v>42.570999999999998</v>
+        <v>24.088999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>7</v>
       </c>
-      <c r="B13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" t="s">
-        <v>98</v>
-      </c>
       <c r="E13" t="s">
         <v>12</v>
       </c>
       <c r="F13">
-        <v>47.570999999999998</v>
+        <v>50.213999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>7</v>
       </c>
-      <c r="D14" t="s">
-        <v>97</v>
+      <c r="B14" t="s">
+        <v>9</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" s="9">
-        <f>F10</f>
-        <v>-0.71430000000000005</v>
-      </c>
-      <c r="H14" s="9" t="str">
-        <f>H10</f>
-        <v>Höstvete foder/bröd, södra götaland</v>
+        <v>12</v>
+      </c>
+      <c r="F14">
+        <v>55.213999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -1005,14 +988,16 @@
         <v>7</v>
       </c>
       <c r="D15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E15" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="9">
-        <f t="shared" ref="F15:F17" si="0">F11</f>
-        <v>23.143000000000001</v>
+        <v>10</v>
+      </c>
+      <c r="F15">
+        <v>-0.71430000000000005</v>
+      </c>
+      <c r="H15" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -1020,293 +1005,293 @@
         <v>7</v>
       </c>
       <c r="D16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E16" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" s="9">
-        <f t="shared" si="0"/>
-        <v>42.570999999999998</v>
+        <v>11</v>
+      </c>
+      <c r="F16">
+        <v>23.143000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>7</v>
       </c>
-      <c r="B17" t="s">
+      <c r="D17" t="s">
+        <v>96</v>
+      </c>
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17">
+        <v>42.570999999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" t="s">
         <v>9</v>
       </c>
-      <c r="D17" t="s">
-        <v>97</v>
-      </c>
-      <c r="E17" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="9">
+      <c r="D18" t="s">
+        <v>96</v>
+      </c>
+      <c r="E18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18">
+        <v>47.570999999999998</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" t="s">
+        <v>95</v>
+      </c>
+      <c r="E19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" s="9">
+        <f>F15</f>
+        <v>-0.71430000000000005</v>
+      </c>
+      <c r="H19" s="9" t="str">
+        <f>H15</f>
+        <v>Höstvete foder/bröd, södra götaland</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" t="s">
+        <v>95</v>
+      </c>
+      <c r="E20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="9">
+        <f t="shared" ref="F20:F22" si="0">F16</f>
+        <v>23.143000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" t="s">
+        <v>95</v>
+      </c>
+      <c r="E21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="9">
+        <f t="shared" si="0"/>
+        <v>42.570999999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" t="s">
+        <v>95</v>
+      </c>
+      <c r="E22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" s="9">
         <f t="shared" si="0"/>
         <v>47.570999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>16</v>
-      </c>
-      <c r="E18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>16</v>
-      </c>
-      <c r="E19" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20">
-        <v>-1.7857000000000001</v>
-      </c>
-      <c r="H20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>27</v>
-      </c>
-      <c r="E21" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21">
-        <v>30.786000000000001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>27</v>
-      </c>
-      <c r="E22" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22">
-        <v>25</v>
-      </c>
-    </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>27</v>
-      </c>
-      <c r="D23" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="E23" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F23">
-        <v>-1.25</v>
-      </c>
-      <c r="H23" t="s">
-        <v>106</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>27</v>
-      </c>
-      <c r="D24" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="E24" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F24">
-        <v>27.75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>27</v>
       </c>
-      <c r="D25" t="s">
-        <v>98</v>
-      </c>
       <c r="E25" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F25">
-        <v>18.25</v>
+        <v>-1.7857000000000001</v>
+      </c>
+      <c r="H25" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>27</v>
       </c>
-      <c r="D26" t="s">
-        <v>97</v>
-      </c>
       <c r="E26" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" s="9">
-        <f>F23</f>
-        <v>-1.25</v>
-      </c>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9" t="str">
-        <f>H23</f>
-        <v>Råg, södra götaland</v>
+        <v>11</v>
+      </c>
+      <c r="F26">
+        <v>30.786000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>27</v>
       </c>
-      <c r="D27" t="s">
-        <v>97</v>
-      </c>
       <c r="E27" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" s="9">
-        <f>F24</f>
-        <v>27.75</v>
-      </c>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
+        <v>12</v>
+      </c>
+      <c r="F27">
+        <v>25</v>
+      </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>27</v>
       </c>
       <c r="D28" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E28" t="s">
-        <v>12</v>
-      </c>
-      <c r="F28" s="9">
-        <f>F25</f>
-        <v>18.25</v>
-      </c>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
+        <v>10</v>
+      </c>
+      <c r="F28">
+        <v>-1.25</v>
+      </c>
+      <c r="H28" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>23</v>
+        <v>27</v>
+      </c>
+      <c r="D29" t="s">
+        <v>96</v>
       </c>
       <c r="E29" t="s">
         <v>11</v>
       </c>
       <c r="F29">
-        <v>16.856999999999999</v>
-      </c>
-      <c r="H29" t="s">
-        <v>22</v>
+        <v>27.75</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>23</v>
+        <v>27</v>
+      </c>
+      <c r="D30" t="s">
+        <v>96</v>
       </c>
       <c r="E30" t="s">
         <v>12</v>
       </c>
       <c r="F30">
-        <v>59.143000000000001</v>
+        <v>18.25</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D31" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E31" t="s">
         <v>10</v>
       </c>
-      <c r="F31">
-        <v>-0.71430000000000005</v>
-      </c>
-      <c r="H31" t="s">
-        <v>105</v>
+      <c r="F31" s="9">
+        <f>F28</f>
+        <v>-1.25</v>
+      </c>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9" t="str">
+        <f>H28</f>
+        <v>Råg, södra götaland</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D32" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E32" t="s">
         <v>11</v>
       </c>
-      <c r="F32">
-        <v>23.143000000000001</v>
-      </c>
+      <c r="F32" s="9">
+        <f>F29</f>
+        <v>27.75</v>
+      </c>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D33" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E33" t="s">
         <v>12</v>
       </c>
-      <c r="F33">
-        <v>37.570999999999998</v>
-      </c>
+      <c r="F33" s="9">
+        <f>F30</f>
+        <v>18.25</v>
+      </c>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>23</v>
       </c>
-      <c r="D34" t="s">
-        <v>97</v>
-      </c>
       <c r="E34" t="s">
-        <v>10</v>
-      </c>
-      <c r="F34" s="9">
-        <f>F31</f>
-        <v>-0.71430000000000005</v>
-      </c>
-      <c r="H34" s="9" t="str">
-        <f>H31</f>
-        <v>Rågvete/höstkorn, södra götaland</v>
+        <v>11</v>
+      </c>
+      <c r="F34">
+        <v>16.856999999999999</v>
+      </c>
+      <c r="H34" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>23</v>
       </c>
-      <c r="D35" t="s">
-        <v>97</v>
-      </c>
       <c r="E35" t="s">
-        <v>11</v>
-      </c>
-      <c r="F35" s="9">
-        <f>F32</f>
-        <v>23.143000000000001</v>
+        <v>12</v>
+      </c>
+      <c r="F35">
+        <v>59.143000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
@@ -1314,140 +1299,146 @@
         <v>23</v>
       </c>
       <c r="D36" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E36" t="s">
-        <v>12</v>
-      </c>
-      <c r="F36" s="9">
-        <f>F33</f>
-        <v>37.570999999999998</v>
+        <v>10</v>
+      </c>
+      <c r="F36">
+        <v>-0.71430000000000005</v>
+      </c>
+      <c r="H36" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>17</v>
+        <v>23</v>
+      </c>
+      <c r="D37" t="s">
+        <v>96</v>
       </c>
       <c r="E37" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F37">
-        <v>-1.0713999999999999</v>
-      </c>
-      <c r="H37" t="s">
-        <v>18</v>
+        <v>23.143000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>17</v>
+        <v>23</v>
+      </c>
+      <c r="D38" t="s">
+        <v>96</v>
       </c>
       <c r="E38" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F38">
-        <v>23.928999999999998</v>
+        <v>37.570999999999998</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>17</v>
+        <v>23</v>
+      </c>
+      <c r="D39" t="s">
+        <v>95</v>
       </c>
       <c r="E39" t="s">
-        <v>12</v>
-      </c>
-      <c r="F39">
-        <v>32</v>
+        <v>10</v>
+      </c>
+      <c r="F39" s="9">
+        <f>F36</f>
+        <v>-0.71430000000000005</v>
+      </c>
+      <c r="H39" s="9" t="str">
+        <f>H36</f>
+        <v>Rågvete/höstkorn, södra götaland</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>17</v>
-      </c>
-      <c r="B40" t="s">
-        <v>9</v>
+        <v>23</v>
+      </c>
+      <c r="D40" t="s">
+        <v>95</v>
       </c>
       <c r="E40" t="s">
-        <v>10</v>
-      </c>
-      <c r="F40" s="8">
-        <v>1E-13</v>
-      </c>
-      <c r="H40" t="s">
-        <v>19</v>
+        <v>11</v>
+      </c>
+      <c r="F40" s="9">
+        <f>F37</f>
+        <v>23.143000000000001</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>17</v>
-      </c>
-      <c r="B41" t="s">
-        <v>9</v>
+        <v>23</v>
+      </c>
+      <c r="D41" t="s">
+        <v>95</v>
       </c>
       <c r="E41" t="s">
-        <v>11</v>
-      </c>
-      <c r="F41">
-        <v>15</v>
+        <v>12</v>
+      </c>
+      <c r="F41" s="9">
+        <f>F38</f>
+        <v>37.570999999999998</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>17</v>
       </c>
-      <c r="B42" t="s">
-        <v>9</v>
-      </c>
       <c r="E42" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F42">
-        <v>45</v>
+        <v>-1.0713999999999999</v>
+      </c>
+      <c r="H42" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>17</v>
       </c>
-      <c r="D43" t="s">
-        <v>98</v>
-      </c>
       <c r="E43" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F43">
-        <v>-1.25</v>
-      </c>
-      <c r="H43" t="s">
-        <v>107</v>
+        <v>23.928999999999998</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>17</v>
       </c>
-      <c r="D44" t="s">
-        <v>98</v>
-      </c>
       <c r="E44" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F44">
-        <v>25.25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>17</v>
       </c>
-      <c r="D45" t="s">
-        <v>98</v>
+      <c r="B45" t="s">
+        <v>9</v>
       </c>
       <c r="E45" t="s">
-        <v>12</v>
-      </c>
-      <c r="F45">
-        <v>19.75</v>
+        <v>10</v>
+      </c>
+      <c r="F45" s="8">
+        <v>1E-13</v>
+      </c>
+      <c r="H45" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -1457,17 +1448,11 @@
       <c r="B46" t="s">
         <v>9</v>
       </c>
-      <c r="D46" t="s">
-        <v>98</v>
-      </c>
       <c r="E46" t="s">
-        <v>10</v>
-      </c>
-      <c r="F46" s="8">
-        <v>-2E-12</v>
-      </c>
-      <c r="H46" t="s">
-        <v>108</v>
+        <v>11</v>
+      </c>
+      <c r="F46">
+        <v>15</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
@@ -1477,31 +1462,28 @@
       <c r="B47" t="s">
         <v>9</v>
       </c>
-      <c r="D47" t="s">
-        <v>98</v>
-      </c>
       <c r="E47" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F47">
-        <v>15</v>
+        <v>45</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>17</v>
       </c>
-      <c r="B48" t="s">
-        <v>9</v>
-      </c>
       <c r="D48" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E48" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F48">
-        <v>45</v>
+        <v>-1.25</v>
+      </c>
+      <c r="H48" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -1509,18 +1491,13 @@
         <v>17</v>
       </c>
       <c r="D49" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E49" t="s">
-        <v>10</v>
-      </c>
-      <c r="F49" s="9">
-        <f t="shared" ref="F49:F54" si="1">F43</f>
-        <v>-1.25</v>
-      </c>
-      <c r="H49" s="9" t="str">
-        <f>H43</f>
-        <v>Korn foder, södra götaland</v>
+        <v>11</v>
+      </c>
+      <c r="F49">
+        <v>25.25</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
@@ -1528,29 +1505,33 @@
         <v>17</v>
       </c>
       <c r="D50" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E50" t="s">
-        <v>11</v>
-      </c>
-      <c r="F50" s="9">
-        <f t="shared" si="1"/>
-        <v>25.25</v>
+        <v>12</v>
+      </c>
+      <c r="F50">
+        <v>19.75</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>17</v>
       </c>
+      <c r="B51" t="s">
+        <v>9</v>
+      </c>
       <c r="D51" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E51" t="s">
-        <v>12</v>
-      </c>
-      <c r="F51" s="9">
-        <f t="shared" si="1"/>
-        <v>19.75</v>
+        <v>10</v>
+      </c>
+      <c r="F51" s="8">
+        <v>-2E-12</v>
+      </c>
+      <c r="H51" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
@@ -1561,18 +1542,13 @@
         <v>9</v>
       </c>
       <c r="D52" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E52" t="s">
-        <v>10</v>
-      </c>
-      <c r="F52" s="9">
-        <f t="shared" si="1"/>
-        <v>-2E-12</v>
-      </c>
-      <c r="H52" s="9" t="str">
-        <f>H46</f>
-        <v>Korn, malt södra götaland</v>
+        <v>11</v>
+      </c>
+      <c r="F52">
+        <v>15</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
@@ -1583,32 +1559,32 @@
         <v>9</v>
       </c>
       <c r="D53" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E53" t="s">
-        <v>11</v>
-      </c>
-      <c r="F53" s="9">
-        <f t="shared" si="1"/>
-        <v>15</v>
+        <v>12</v>
+      </c>
+      <c r="F53">
+        <v>45</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>17</v>
       </c>
-      <c r="B54" t="s">
-        <v>9</v>
-      </c>
       <c r="D54" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E54" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F54" s="9">
-        <f t="shared" si="1"/>
-        <v>45</v>
+        <f t="shared" ref="F54:F59" si="1">F48</f>
+        <v>-1.25</v>
+      </c>
+      <c r="H54" s="9" t="str">
+        <f>H48</f>
+        <v>Korn foder, södra götaland</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
@@ -1616,16 +1592,14 @@
         <v>17</v>
       </c>
       <c r="D55" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E55" t="s">
-        <v>10</v>
-      </c>
-      <c r="F55" s="5">
-        <v>0</v>
-      </c>
-      <c r="H55" t="s">
-        <v>110</v>
+        <v>11</v>
+      </c>
+      <c r="F55" s="9">
+        <f t="shared" si="1"/>
+        <v>25.25</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
@@ -1633,27 +1607,36 @@
         <v>17</v>
       </c>
       <c r="D56" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E56" t="s">
-        <v>11</v>
-      </c>
-      <c r="F56" s="5">
-        <v>20</v>
+        <v>12</v>
+      </c>
+      <c r="F56" s="9">
+        <f t="shared" si="1"/>
+        <v>19.75</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>17</v>
       </c>
+      <c r="B57" t="s">
+        <v>9</v>
+      </c>
       <c r="D57" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E57" t="s">
-        <v>12</v>
-      </c>
-      <c r="F57" s="5">
-        <v>35</v>
+        <v>10</v>
+      </c>
+      <c r="F57" s="9">
+        <f t="shared" si="1"/>
+        <v>-2E-12</v>
+      </c>
+      <c r="H57" s="9" t="str">
+        <f>H51</f>
+        <v>Korn, malt södra götaland</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -1664,18 +1647,14 @@
         <v>9</v>
       </c>
       <c r="D58" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E58" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F58" s="9">
-        <f t="shared" ref="F58:F66" si="2">F55</f>
-        <v>0</v>
-      </c>
-      <c r="H58" s="9" t="str">
-        <f>H55</f>
-        <v>Korn, norrland</v>
+        <f t="shared" si="1"/>
+        <v>15</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
@@ -1686,32 +1665,31 @@
         <v>9</v>
       </c>
       <c r="D59" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E59" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F59" s="9">
-        <f t="shared" si="2"/>
-        <v>20</v>
+        <f t="shared" si="1"/>
+        <v>45</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>17</v>
       </c>
-      <c r="B60" t="s">
-        <v>9</v>
-      </c>
       <c r="D60" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E60" t="s">
-        <v>12</v>
-      </c>
-      <c r="F60" s="9">
-        <f t="shared" si="2"/>
-        <v>35</v>
+        <v>10</v>
+      </c>
+      <c r="F60" s="5">
+        <v>0</v>
+      </c>
+      <c r="H60" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
@@ -1719,18 +1697,13 @@
         <v>17</v>
       </c>
       <c r="D61" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E61" t="s">
-        <v>10</v>
-      </c>
-      <c r="F61" s="9">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H61" s="9" t="str">
-        <f>H58</f>
-        <v>Korn, norrland</v>
+        <v>11</v>
+      </c>
+      <c r="F61" s="5">
+        <v>20</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
@@ -1738,29 +1711,35 @@
         <v>17</v>
       </c>
       <c r="D62" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E62" t="s">
-        <v>11</v>
-      </c>
-      <c r="F62" s="9">
-        <f t="shared" si="2"/>
-        <v>20</v>
+        <v>12</v>
+      </c>
+      <c r="F62" s="5">
+        <v>35</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>17</v>
       </c>
+      <c r="B63" t="s">
+        <v>9</v>
+      </c>
       <c r="D63" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E63" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F63" s="9">
-        <f t="shared" si="2"/>
-        <v>35</v>
+        <f t="shared" ref="F63:F71" si="2">F60</f>
+        <v>0</v>
+      </c>
+      <c r="H63" s="9" t="str">
+        <f>H60</f>
+        <v>Korn, norrland</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
@@ -1771,18 +1750,14 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E64" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F64" s="9">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H64" s="9" t="str">
-        <f>H61</f>
-        <v>Korn, norrland</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -1793,147 +1768,157 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E65" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F65" s="9">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>35</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>17</v>
       </c>
-      <c r="B66" t="s">
-        <v>9</v>
-      </c>
       <c r="D66" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E66" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F66" s="9">
         <f t="shared" si="2"/>
-        <v>35</v>
+        <v>0</v>
+      </c>
+      <c r="H66" s="9" t="str">
+        <f>H63</f>
+        <v>Korn, norrland</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>21</v>
+        <v>17</v>
+      </c>
+      <c r="D67" t="s">
+        <v>98</v>
       </c>
       <c r="E67" t="s">
-        <v>10</v>
-      </c>
-      <c r="F67">
-        <v>-1.0713999999999999</v>
-      </c>
-      <c r="H67" t="s">
+        <v>11</v>
+      </c>
+      <c r="F67" s="9">
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>21</v>
+        <v>17</v>
+      </c>
+      <c r="D68" t="s">
+        <v>98</v>
       </c>
       <c r="E68" t="s">
-        <v>11</v>
-      </c>
-      <c r="F68">
-        <v>23.928999999999998</v>
+        <v>12</v>
+      </c>
+      <c r="F68" s="9">
+        <f t="shared" si="2"/>
+        <v>35</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>21</v>
+        <v>17</v>
+      </c>
+      <c r="B69" t="s">
+        <v>9</v>
+      </c>
+      <c r="D69" t="s">
+        <v>98</v>
       </c>
       <c r="E69" t="s">
-        <v>12</v>
-      </c>
-      <c r="F69">
-        <v>22</v>
+        <v>10</v>
+      </c>
+      <c r="F69" s="9">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H69" s="9" t="str">
+        <f>H66</f>
+        <v>Korn, norrland</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>21</v>
+        <v>17</v>
+      </c>
+      <c r="B70" t="s">
+        <v>9</v>
       </c>
       <c r="D70" t="s">
         <v>98</v>
       </c>
       <c r="E70" t="s">
-        <v>10</v>
-      </c>
-      <c r="F70">
-        <v>-1.25</v>
-      </c>
-      <c r="H70" t="s">
-        <v>109</v>
+        <v>11</v>
+      </c>
+      <c r="F70" s="9">
+        <f t="shared" si="2"/>
+        <v>20</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>21</v>
+        <v>17</v>
+      </c>
+      <c r="B71" t="s">
+        <v>9</v>
       </c>
       <c r="D71" t="s">
         <v>98</v>
       </c>
       <c r="E71" t="s">
-        <v>11</v>
-      </c>
-      <c r="F71">
-        <v>25.25</v>
+        <v>12</v>
+      </c>
+      <c r="F71" s="9">
+        <f t="shared" si="2"/>
+        <v>35</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>21</v>
       </c>
-      <c r="D72" t="s">
-        <v>98</v>
-      </c>
       <c r="E72" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F72">
-        <v>9.75</v>
+        <v>-1.0713999999999999</v>
+      </c>
+      <c r="H72" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>21</v>
       </c>
-      <c r="D73" t="s">
-        <v>97</v>
-      </c>
       <c r="E73" t="s">
-        <v>10</v>
-      </c>
-      <c r="F73" s="9">
-        <f>F70</f>
-        <v>-1.25</v>
-      </c>
-      <c r="H73" s="9" t="str">
-        <f>H70</f>
-        <v>Havre södra götaland</v>
+        <v>11</v>
+      </c>
+      <c r="F73">
+        <v>23.928999999999998</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>21</v>
       </c>
-      <c r="D74" t="s">
-        <v>97</v>
-      </c>
       <c r="E74" t="s">
-        <v>11</v>
-      </c>
-      <c r="F74" s="9">
-        <f>F71</f>
-        <v>25.25</v>
+        <v>12</v>
+      </c>
+      <c r="F74">
+        <v>22</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
@@ -1941,125 +1926,121 @@
         <v>21</v>
       </c>
       <c r="D75" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E75" t="s">
-        <v>12</v>
-      </c>
-      <c r="F75" s="9">
-        <f>F72</f>
-        <v>9.75</v>
+        <v>10</v>
+      </c>
+      <c r="F75">
+        <v>-1.25</v>
+      </c>
+      <c r="H75" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>25</v>
+        <v>21</v>
+      </c>
+      <c r="D76" t="s">
+        <v>96</v>
       </c>
       <c r="E76" t="s">
         <v>11</v>
       </c>
-      <c r="F76" s="9">
-        <f>F29</f>
-        <v>16.856999999999999</v>
-      </c>
-      <c r="H76" s="9" t="str">
-        <f>H29</f>
-        <v>Rågvete/höstkorn, norra  götaland och svealand</v>
+      <c r="F76">
+        <v>25.25</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>25</v>
+        <v>21</v>
+      </c>
+      <c r="D77" t="s">
+        <v>96</v>
       </c>
       <c r="E77" t="s">
         <v>12</v>
       </c>
-      <c r="F77" s="9">
-        <f>F30</f>
-        <v>59.143000000000001</v>
+      <c r="F77">
+        <v>9.75</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D78" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E78" t="s">
         <v>10</v>
       </c>
       <c r="F78" s="9">
-        <f>F34</f>
-        <v>-0.71430000000000005</v>
+        <f>F75</f>
+        <v>-1.25</v>
       </c>
       <c r="H78" s="9" t="str">
-        <f>H34</f>
-        <v>Rågvete/höstkorn, södra götaland</v>
+        <f>H75</f>
+        <v>Havre södra götaland</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D79" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E79" t="s">
         <v>11</v>
       </c>
       <c r="F79" s="9">
-        <f>F35</f>
-        <v>23.143000000000001</v>
+        <f>F76</f>
+        <v>25.25</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D80" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E80" t="s">
         <v>12</v>
       </c>
       <c r="F80" s="9">
-        <f>F36</f>
-        <v>37.570999999999998</v>
+        <f>F77</f>
+        <v>9.75</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>25</v>
       </c>
-      <c r="D81" t="s">
-        <v>97</v>
-      </c>
       <c r="E81" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F81" s="9">
         <f>F34</f>
-        <v>-0.71430000000000005</v>
+        <v>16.856999999999999</v>
       </c>
       <c r="H81" s="9" t="str">
         <f>H34</f>
-        <v>Rågvete/höstkorn, södra götaland</v>
+        <v>Rågvete/höstkorn, norra  götaland och svealand</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>25</v>
       </c>
-      <c r="D82" t="s">
-        <v>97</v>
-      </c>
       <c r="E82" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F82" s="9">
         <f>F35</f>
-        <v>23.143000000000001</v>
+        <v>59.143000000000001</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
@@ -2067,128 +2048,125 @@
         <v>25</v>
       </c>
       <c r="D83" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E83" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F83" s="9">
-        <f>F36</f>
-        <v>37.570999999999998</v>
+        <f>F39</f>
+        <v>-0.71430000000000005</v>
+      </c>
+      <c r="H83" s="9" t="str">
+        <f>H39</f>
+        <v>Rågvete/höstkorn, södra götaland</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="D84" t="s">
+        <v>96</v>
       </c>
       <c r="E84" t="s">
         <v>11</v>
       </c>
       <c r="F84" s="9">
-        <f>F29</f>
-        <v>16.856999999999999</v>
-      </c>
-      <c r="H84" s="9" t="str">
-        <f>H29</f>
-        <v>Rågvete/höstkorn, norra  götaland och svealand</v>
+        <f>F40</f>
+        <v>23.143000000000001</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="D85" t="s">
+        <v>96</v>
       </c>
       <c r="E85" t="s">
         <v>12</v>
       </c>
       <c r="F85" s="9">
-        <f>F30</f>
-        <v>59.143000000000001</v>
-      </c>
-      <c r="H85" s="9"/>
+        <f>F41</f>
+        <v>37.570999999999998</v>
+      </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D86" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E86" t="s">
         <v>10</v>
       </c>
       <c r="F86" s="9">
-        <f>F34</f>
+        <f>F39</f>
         <v>-0.71430000000000005</v>
       </c>
       <c r="H86" s="9" t="str">
-        <f>H34</f>
+        <f>H39</f>
         <v>Rågvete/höstkorn, södra götaland</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D87" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E87" t="s">
         <v>11</v>
       </c>
       <c r="F87" s="9">
-        <f>F35</f>
+        <f>F40</f>
         <v>23.143000000000001</v>
       </c>
-      <c r="H87" s="9"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D88" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E88" t="s">
         <v>12</v>
       </c>
       <c r="F88" s="9">
-        <f>F36</f>
+        <f>F41</f>
         <v>37.570999999999998</v>
       </c>
-      <c r="H88" s="9"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>24</v>
       </c>
-      <c r="D89" t="s">
-        <v>97</v>
-      </c>
       <c r="E89" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F89" s="9">
         <f>F34</f>
-        <v>-0.71430000000000005</v>
+        <v>16.856999999999999</v>
       </c>
       <c r="H89" s="9" t="str">
         <f>H34</f>
-        <v>Rågvete/höstkorn, södra götaland</v>
+        <v>Rågvete/höstkorn, norra  götaland och svealand</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>24</v>
       </c>
-      <c r="D90" t="s">
-        <v>97</v>
-      </c>
       <c r="E90" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F90" s="9">
         <f>F35</f>
-        <v>23.143000000000001</v>
+        <v>59.143000000000001</v>
       </c>
       <c r="H90" s="9"/>
     </row>
@@ -2197,1110 +2175,1132 @@
         <v>24</v>
       </c>
       <c r="D91" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E91" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F91" s="9">
-        <f>F36</f>
-        <v>37.570999999999998</v>
-      </c>
-      <c r="H91" s="9"/>
+        <f>F39</f>
+        <v>-0.71430000000000005</v>
+      </c>
+      <c r="H91" s="9" t="str">
+        <f>H39</f>
+        <v>Rågvete/höstkorn, södra götaland</v>
+      </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E92" s="7"/>
-      <c r="F92" s="7"/>
-      <c r="H92" s="7"/>
+      <c r="A92" t="s">
+        <v>24</v>
+      </c>
+      <c r="D92" t="s">
+        <v>96</v>
+      </c>
+      <c r="E92" t="s">
+        <v>11</v>
+      </c>
+      <c r="F92" s="9">
+        <f>F40</f>
+        <v>23.143000000000001</v>
+      </c>
+      <c r="H92" s="9"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>28</v>
+        <v>24</v>
+      </c>
+      <c r="D93" t="s">
+        <v>96</v>
       </c>
       <c r="E93" t="s">
         <v>12</v>
       </c>
-      <c r="F93">
-        <v>50</v>
-      </c>
-      <c r="H93" t="s">
-        <v>76</v>
-      </c>
+      <c r="F93" s="9">
+        <f>F41</f>
+        <v>37.570999999999998</v>
+      </c>
+      <c r="H93" s="9"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>30</v>
+        <v>24</v>
+      </c>
+      <c r="D94" t="s">
+        <v>95</v>
       </c>
       <c r="E94" t="s">
-        <v>12</v>
-      </c>
-      <c r="F94">
-        <v>0</v>
-      </c>
-      <c r="H94" t="s">
-        <v>75</v>
+        <v>10</v>
+      </c>
+      <c r="F94" s="9">
+        <f>F39</f>
+        <v>-0.71430000000000005</v>
+      </c>
+      <c r="H94" s="9" t="str">
+        <f>H39</f>
+        <v>Rågvete/höstkorn, södra götaland</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>31</v>
+        <v>24</v>
+      </c>
+      <c r="D95" t="s">
+        <v>95</v>
       </c>
       <c r="E95" t="s">
-        <v>12</v>
-      </c>
-      <c r="F95">
-        <v>0</v>
-      </c>
-      <c r="H95" t="s">
-        <v>75</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="F95" s="9">
+        <f>F40</f>
+        <v>23.143000000000001</v>
+      </c>
+      <c r="H95" s="9"/>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>32</v>
+        <v>24</v>
+      </c>
+      <c r="D96" t="s">
+        <v>95</v>
       </c>
       <c r="E96" t="s">
         <v>12</v>
       </c>
-      <c r="F96">
-        <v>0</v>
-      </c>
-      <c r="H96" t="s">
-        <v>75</v>
-      </c>
+      <c r="F96" s="9">
+        <f>F41</f>
+        <v>37.570999999999998</v>
+      </c>
+      <c r="H96" s="9"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>33</v>
-      </c>
-      <c r="E97" t="s">
-        <v>12</v>
-      </c>
-      <c r="F97">
-        <v>30</v>
-      </c>
-      <c r="H97" t="s">
-        <v>77</v>
-      </c>
+      <c r="A97" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E97" s="7"/>
+      <c r="F97" s="7"/>
+      <c r="H97" s="7"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E98" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F98">
-        <v>20</v>
+        <v>50</v>
+      </c>
+      <c r="H98" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E99" t="s">
         <v>12</v>
       </c>
       <c r="F99">
-        <v>65</v>
+        <v>0</v>
+      </c>
+      <c r="H99" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E100" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F100">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="H100" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E101" t="s">
         <v>12</v>
       </c>
       <c r="F101">
-        <v>70</v>
+        <v>0</v>
+      </c>
+      <c r="H101" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E102" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F102">
-        <v>-2.5000000000000001E-2</v>
+        <v>30</v>
       </c>
       <c r="H102" t="s">
-        <v>111</v>
+        <v>77</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E103" t="s">
         <v>11</v>
       </c>
       <c r="F103">
-        <v>4.95</v>
+        <v>20</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E104" t="s">
         <v>12</v>
       </c>
       <c r="F104">
-        <v>-31.5</v>
+        <v>65</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E105" t="s">
-        <v>10</v>
-      </c>
-      <c r="F105" s="9">
-        <f>F102</f>
-        <v>-2.5000000000000001E-2</v>
-      </c>
-      <c r="H105" s="9" t="str">
-        <f>H102</f>
-        <v>Potatis</v>
+        <v>11</v>
+      </c>
+      <c r="F105">
+        <v>20</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E106" t="s">
-        <v>11</v>
-      </c>
-      <c r="F106" s="9">
-        <f t="shared" ref="F106:F107" si="3">F103</f>
-        <v>4.95</v>
+        <v>12</v>
+      </c>
+      <c r="F106">
+        <v>70</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
+        <v>36</v>
+      </c>
+      <c r="E107" t="s">
+        <v>10</v>
+      </c>
+      <c r="F107">
+        <v>-2.5000000000000001E-2</v>
+      </c>
+      <c r="H107" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>36</v>
+      </c>
+      <c r="E108" t="s">
+        <v>11</v>
+      </c>
+      <c r="F108">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>36</v>
+      </c>
+      <c r="E109" t="s">
+        <v>12</v>
+      </c>
+      <c r="F109">
+        <v>-31.5</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
         <v>37</v>
       </c>
-      <c r="E107" t="s">
-        <v>12</v>
-      </c>
-      <c r="F107" s="9">
+      <c r="E110" t="s">
+        <v>10</v>
+      </c>
+      <c r="F110" s="9">
+        <f>F107</f>
+        <v>-2.5000000000000001E-2</v>
+      </c>
+      <c r="H110" s="9" t="str">
+        <f>H107</f>
+        <v>Potatis</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>37</v>
+      </c>
+      <c r="E111" t="s">
+        <v>11</v>
+      </c>
+      <c r="F111" s="9">
+        <f t="shared" ref="F111:F112" si="3">F108</f>
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>37</v>
+      </c>
+      <c r="E112" t="s">
+        <v>12</v>
+      </c>
+      <c r="F112" s="9">
         <f t="shared" si="3"/>
         <v>-31.5</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
         <v>38</v>
       </c>
-      <c r="E108" t="s">
-        <v>12</v>
-      </c>
-      <c r="F108">
+      <c r="E113" t="s">
+        <v>12</v>
+      </c>
+      <c r="F113">
         <v>110</v>
       </c>
-      <c r="H108" t="s">
+      <c r="H113" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A109" s="7" t="s">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A114" s="7" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A110" s="10" t="s">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A115" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="E110" t="s">
+      <c r="E115" t="s">
         <v>10</v>
       </c>
-      <c r="F110">
+      <c r="F115">
         <v>-1.4286000000000001</v>
       </c>
-      <c r="H110" t="s">
+      <c r="H115" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A111" s="10" t="s">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A116" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="E111" t="s">
+      <c r="E116" t="s">
         <v>11</v>
       </c>
-      <c r="F111">
+      <c r="F116">
         <v>40.713999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A112" s="10" t="s">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A117" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="E112" t="s">
-        <v>12</v>
-      </c>
-      <c r="F112">
+      <c r="E117" t="s">
+        <v>12</v>
+      </c>
+      <c r="F117">
         <v>-74.856999999999999</v>
       </c>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A113" s="11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A114" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="E114" t="s">
-        <v>12</v>
-      </c>
-      <c r="F114">
-        <v>0</v>
-      </c>
-      <c r="H114" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A115" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B115" s="5"/>
-      <c r="C115" s="5"/>
-      <c r="D115" s="5"/>
-      <c r="E115" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F115" s="5">
-        <v>-1.7857000000000001</v>
-      </c>
-      <c r="H115" s="7"/>
-    </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A116" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B116" s="5"/>
-      <c r="C116" s="5"/>
-      <c r="D116" s="5"/>
-      <c r="E116" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F116" s="5">
-        <v>43.570999999999998</v>
-      </c>
-      <c r="H116" s="7"/>
-    </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A117" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B117" s="5"/>
-      <c r="C117" s="5"/>
-      <c r="D117" s="5"/>
-      <c r="E117" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F117" s="5">
-        <v>-112.5</v>
-      </c>
-      <c r="H117" s="7"/>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A119" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E119" t="s">
+        <v>12</v>
+      </c>
+      <c r="F119">
+        <v>0</v>
+      </c>
+      <c r="H119" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A120" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B120" s="5"/>
+      <c r="C120" s="5"/>
+      <c r="D120" s="5"/>
+      <c r="E120" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F120" s="5">
+        <v>-1.7857000000000001</v>
+      </c>
+      <c r="H120" s="7"/>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A121" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B121" s="5"/>
+      <c r="C121" s="5"/>
+      <c r="D121" s="5"/>
+      <c r="E121" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F121" s="5">
+        <v>43.570999999999998</v>
+      </c>
+      <c r="H121" s="7"/>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A122" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B122" s="5"/>
+      <c r="C122" s="5"/>
+      <c r="D122" s="5"/>
+      <c r="E122" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F122" s="5">
+        <v>-112.5</v>
+      </c>
+      <c r="H122" s="7"/>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A123" s="11" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A119" s="11" t="s">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A124" s="11" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A120" s="10" t="s">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A125" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="E120" t="s">
-        <v>12</v>
-      </c>
-      <c r="F120">
+      <c r="E125" t="s">
+        <v>12</v>
+      </c>
+      <c r="F125">
         <v>0</v>
       </c>
-      <c r="H120" t="s">
+      <c r="H125" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A121" s="10" t="s">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A126" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="E121" t="s">
-        <v>12</v>
-      </c>
-      <c r="F121">
+      <c r="E126" t="s">
+        <v>12</v>
+      </c>
+      <c r="F126">
         <v>0</v>
       </c>
-      <c r="H121" t="s">
+      <c r="H126" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
         <v>47</v>
       </c>
-      <c r="E122" t="s">
+      <c r="E127" t="s">
         <v>11</v>
       </c>
-      <c r="F122">
+      <c r="F127">
         <v>2.5</v>
       </c>
-      <c r="H122" t="s">
+      <c r="H127" t="s">
         <v>85</v>
       </c>
-      <c r="I122" t="s">
+      <c r="I127" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
         <v>47</v>
       </c>
-      <c r="E123" t="s">
-        <v>12</v>
-      </c>
-      <c r="F123">
+      <c r="E128" t="s">
+        <v>12</v>
+      </c>
+      <c r="F128">
         <v>25</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
         <v>48</v>
       </c>
-      <c r="E124" t="s">
+      <c r="E129" t="s">
         <v>11</v>
       </c>
-      <c r="F124">
+      <c r="F129">
         <v>1.3846000000000001</v>
       </c>
-      <c r="H124" t="s">
+      <c r="H129" t="s">
         <v>85</v>
       </c>
-      <c r="I124" t="s">
+      <c r="I129" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
         <v>48</v>
       </c>
-      <c r="E125" t="s">
-        <v>12</v>
-      </c>
-      <c r="F125">
+      <c r="E130" t="s">
+        <v>12</v>
+      </c>
+      <c r="F130">
         <v>11.538</v>
-      </c>
-    </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A126" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E126" t="s">
-        <v>11</v>
-      </c>
-      <c r="F126" s="9">
-        <f>F124</f>
-        <v>1.3846000000000001</v>
-      </c>
-      <c r="H126" s="7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A127" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E127" t="s">
-        <v>12</v>
-      </c>
-      <c r="F127" s="9">
-        <f>F125</f>
-        <v>11.538</v>
-      </c>
-    </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A128" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E128" t="s">
-        <v>11</v>
-      </c>
-      <c r="F128">
-        <v>3.3332999999999999</v>
-      </c>
-      <c r="H128" t="s">
-        <v>87</v>
-      </c>
-      <c r="I128" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A129" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E129" t="s">
-        <v>12</v>
-      </c>
-      <c r="F129">
-        <v>33.332999999999998</v>
-      </c>
-    </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A130" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E130" t="s">
-        <v>11</v>
-      </c>
-      <c r="F130">
-        <v>3</v>
-      </c>
-      <c r="H130" t="s">
-        <v>88</v>
-      </c>
-      <c r="I130" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E131" t="s">
-        <v>12</v>
-      </c>
-      <c r="F131">
-        <v>90</v>
+        <v>11</v>
+      </c>
+      <c r="F131" s="9">
+        <f>F129</f>
+        <v>1.3846000000000001</v>
+      </c>
+      <c r="H131" s="7" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="E132" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F132">
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="H132" t="s">
-        <v>89</v>
-      </c>
-      <c r="I132" t="s">
-        <v>86</v>
+        <v>49</v>
+      </c>
+      <c r="E132" t="s">
+        <v>12</v>
+      </c>
+      <c r="F132" s="9">
+        <f>F130</f>
+        <v>11.538</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E133" t="s">
         <v>11</v>
       </c>
       <c r="F133">
-        <v>1.2583</v>
+        <v>3.3332999999999999</v>
+      </c>
+      <c r="H133" t="s">
+        <v>87</v>
+      </c>
+      <c r="I133" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E134" t="s">
         <v>12</v>
       </c>
       <c r="F134">
-        <v>0</v>
+        <v>33.332999999999998</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E135" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F135" s="9">
-        <f>F132</f>
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="H135" s="9" t="str">
-        <f>H132</f>
-        <v xml:space="preserve">yield in fresh weight 5% DM </v>
-      </c>
-      <c r="I135" s="9" t="str">
-        <f>I132</f>
-        <v>Yara (2018)</v>
+        <v>51</v>
+      </c>
+      <c r="E135" t="s">
+        <v>11</v>
+      </c>
+      <c r="F135">
+        <v>3</v>
+      </c>
+      <c r="H135" t="s">
+        <v>88</v>
+      </c>
+      <c r="I135" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E136" t="s">
-        <v>11</v>
-      </c>
-      <c r="F136" s="9">
-        <f>F133</f>
-        <v>1.2583</v>
-      </c>
-      <c r="G136" s="9"/>
-      <c r="H136" s="9"/>
-      <c r="I136" s="9"/>
+        <v>12</v>
+      </c>
+      <c r="F136">
+        <v>90</v>
+      </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E137" t="s">
-        <v>12</v>
-      </c>
-      <c r="F137" s="9">
-        <f>F134</f>
-        <v>0</v>
-      </c>
-      <c r="G137" s="9"/>
-      <c r="H137" s="9"/>
-      <c r="I137" s="9"/>
+        <v>52</v>
+      </c>
+      <c r="E137" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F137">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="H137" t="s">
+        <v>89</v>
+      </c>
+      <c r="I137" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E138" t="s">
         <v>11</v>
       </c>
-      <c r="F138" s="9">
-        <f>F128</f>
-        <v>3.3332999999999999</v>
-      </c>
-      <c r="H138" s="7" t="s">
-        <v>114</v>
+      <c r="F138">
+        <v>1.2583</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E139" t="s">
         <v>12</v>
       </c>
-      <c r="F139" s="9">
-        <f>F129</f>
-        <v>33.332999999999998</v>
+      <c r="F139">
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A140" s="7" t="s">
-        <v>55</v>
+      <c r="A140" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E140" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F140" s="9">
+        <f>F137</f>
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="H140" s="9" t="str">
+        <f>H137</f>
+        <v xml:space="preserve">yield in fresh weight 5% DM </v>
+      </c>
+      <c r="I140" s="9" t="str">
+        <f>I137</f>
+        <v>Yara (2018)</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E141" t="s">
-        <v>12</v>
-      </c>
-      <c r="F141">
-        <v>65</v>
-      </c>
-      <c r="H141" t="s">
-        <v>82</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="F141" s="9">
+        <f>F138</f>
+        <v>1.2583</v>
+      </c>
+      <c r="G141" s="9"/>
+      <c r="H141" s="9"/>
+      <c r="I141" s="9"/>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A142" s="7" t="s">
-        <v>57</v>
-      </c>
+      <c r="A142" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E142" t="s">
+        <v>12</v>
+      </c>
+      <c r="F142" s="9">
+        <f>F139</f>
+        <v>0</v>
+      </c>
+      <c r="G142" s="9"/>
+      <c r="H142" s="9"/>
+      <c r="I142" s="9"/>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E143" t="s">
-        <v>12</v>
-      </c>
-      <c r="F143">
-        <v>65</v>
-      </c>
-      <c r="H143" t="s">
-        <v>83</v>
+        <v>11</v>
+      </c>
+      <c r="F143" s="9">
+        <f>F133</f>
+        <v>3.3332999999999999</v>
+      </c>
+      <c r="H143" s="7" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E144" t="s">
+        <v>12</v>
+      </c>
+      <c r="F144" s="9">
+        <f>F134</f>
+        <v>33.332999999999998</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A145" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A146" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E146" t="s">
+        <v>12</v>
+      </c>
+      <c r="F146">
+        <v>65</v>
+      </c>
+      <c r="H146" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A147" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A148" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E148" t="s">
+        <v>12</v>
+      </c>
+      <c r="F148">
+        <v>65</v>
+      </c>
+      <c r="H148" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A149" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E144" t="s">
-        <v>12</v>
-      </c>
-      <c r="F144">
+      <c r="E149" t="s">
+        <v>12</v>
+      </c>
+      <c r="F149">
         <v>100</v>
       </c>
-      <c r="H144" t="s">
+      <c r="H149" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A145" s="5" t="s">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A150" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E145" t="s">
-        <v>12</v>
-      </c>
-      <c r="F145">
+      <c r="E150" t="s">
+        <v>12</v>
+      </c>
+      <c r="F150">
         <v>110</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A146" s="5" t="s">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A151" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="E146" t="s">
-        <v>12</v>
-      </c>
-      <c r="F146" s="9">
-        <f>F144</f>
+      <c r="E151" t="s">
+        <v>12</v>
+      </c>
+      <c r="F151" s="9">
+        <f>F149</f>
         <v>100</v>
       </c>
-      <c r="H146" s="7" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A147" s="7" t="s">
+      <c r="H151" s="7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A152" s="7" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A148" s="7" t="s">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A153" s="7" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A149" s="7" t="s">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A154" s="7" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A150" s="7" t="s">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A155" s="7" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A151" s="7" t="s">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A156" s="7" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A152" s="7" t="s">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A157" s="7" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A153" s="7" t="s">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A158" s="7" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A154" s="5" t="s">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A159" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E154" t="s">
-        <v>12</v>
-      </c>
-      <c r="F154">
+      <c r="E159" t="s">
+        <v>12</v>
+      </c>
+      <c r="F159">
         <v>0</v>
       </c>
-      <c r="H154" t="s">
+      <c r="H159" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A155" s="7" t="s">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A160" s="7" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A156" s="7" t="s">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A161" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A157" s="5" t="s">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A162" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E157" t="s">
-        <v>12</v>
-      </c>
-      <c r="F157">
+      <c r="E162" t="s">
+        <v>12</v>
+      </c>
+      <c r="F162">
         <v>0</v>
       </c>
-      <c r="H157" t="s">
+      <c r="H162" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A159" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B159" s="2"/>
-      <c r="C159" s="2"/>
-      <c r="D159" s="2"/>
-      <c r="E159" s="2"/>
-      <c r="F159" s="2"/>
-      <c r="G159" s="2"/>
-      <c r="H159" s="3"/>
-      <c r="I159" s="3"/>
-    </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E160" s="6" t="s">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A164" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B164" s="2"/>
+      <c r="C164" s="2"/>
+      <c r="D164" s="2"/>
+      <c r="E164" s="2"/>
+      <c r="F164" s="2"/>
+      <c r="G164" s="2"/>
+      <c r="H164" s="3"/>
+      <c r="I164" s="3"/>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E165" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F160" s="6">
+      <c r="F165" s="6">
         <v>0</v>
       </c>
-      <c r="G160" s="6"/>
-      <c r="H160" s="6" t="s">
+      <c r="G165" s="6"/>
+      <c r="H165" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E161" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F161" s="6">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E166" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F166" s="6">
         <v>1</v>
       </c>
-      <c r="G161" s="6"/>
-      <c r="H161" s="6" t="s">
+      <c r="G166" s="6"/>
+      <c r="H166" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A162" t="s">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
         <v>7</v>
       </c>
-      <c r="E162" t="s">
+      <c r="E167" t="s">
         <v>13</v>
       </c>
-      <c r="F162">
+      <c r="F167">
         <v>-0.32340000000000002</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A163" t="s">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
         <v>7</v>
       </c>
-      <c r="E163" t="s">
-        <v>14</v>
-      </c>
-      <c r="F163">
+      <c r="E168" t="s">
+        <v>14</v>
+      </c>
+      <c r="F168">
         <v>0.97240000000000004</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A164" t="s">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
         <v>16</v>
       </c>
-      <c r="E164" t="s">
+      <c r="E169" t="s">
         <v>13</v>
       </c>
-      <c r="F164">
+      <c r="F169">
         <v>-0.32500000000000001</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A165" t="s">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
         <v>16</v>
       </c>
-      <c r="E165" t="s">
-        <v>14</v>
-      </c>
-      <c r="F165">
+      <c r="E170" t="s">
+        <v>14</v>
+      </c>
+      <c r="F170">
         <v>0.81369999999999998</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A166" t="s">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
         <v>27</v>
       </c>
-      <c r="E166" t="s">
+      <c r="E171" t="s">
         <v>13</v>
       </c>
-      <c r="F166">
+      <c r="F171">
         <v>-0.58699999999999997</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A167" t="s">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
         <v>27</v>
       </c>
-      <c r="E167" t="s">
-        <v>14</v>
-      </c>
-      <c r="F167">
+      <c r="E172" t="s">
+        <v>14</v>
+      </c>
+      <c r="F172">
         <v>0.82350000000000001</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A168" t="s">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
         <v>23</v>
       </c>
-      <c r="E168" t="s">
+      <c r="E173" t="s">
         <v>13</v>
       </c>
-      <c r="F168">
+      <c r="F173">
         <v>-0.35070000000000001</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A169" t="s">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
         <v>23</v>
       </c>
-      <c r="E169" t="s">
-        <v>14</v>
-      </c>
-      <c r="F169">
+      <c r="E174" t="s">
+        <v>14</v>
+      </c>
+      <c r="F174">
         <v>0.9234</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A170" t="s">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
         <v>17</v>
       </c>
-      <c r="E170" t="s">
+      <c r="E175" t="s">
         <v>13</v>
       </c>
-      <c r="F170">
+      <c r="F175">
         <v>-0.41710000000000003</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A171" t="s">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
         <v>17</v>
       </c>
-      <c r="E171" t="s">
-        <v>14</v>
-      </c>
-      <c r="F171">
+      <c r="E176" t="s">
+        <v>14</v>
+      </c>
+      <c r="F176">
         <v>0.91610000000000003</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A172" t="s">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
         <v>21</v>
       </c>
-      <c r="E172" t="s">
+      <c r="E177" t="s">
         <v>13</v>
       </c>
-      <c r="F172">
+      <c r="F177">
         <v>-0.74150000000000005</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A173" t="s">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
         <v>21</v>
       </c>
-      <c r="E173" t="s">
-        <v>14</v>
-      </c>
-      <c r="F173">
+      <c r="E178" t="s">
+        <v>14</v>
+      </c>
+      <c r="F178">
         <v>0.96550000000000002</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A174" t="s">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
         <v>25</v>
       </c>
-      <c r="E174" t="s">
+      <c r="E179" t="s">
         <v>13</v>
       </c>
-      <c r="F174" s="9">
-        <f>F176</f>
+      <c r="F179" s="9">
+        <f>F181</f>
         <v>-0.58699999999999997</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A175" t="s">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
         <v>25</v>
       </c>
-      <c r="E175" t="s">
-        <v>14</v>
-      </c>
-      <c r="F175" s="9">
-        <f>F177</f>
+      <c r="E180" t="s">
+        <v>14</v>
+      </c>
+      <c r="F180" s="9">
+        <f>F182</f>
         <v>0.82350000000000001</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A176" t="s">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
         <v>24</v>
       </c>
-      <c r="E176" t="s">
+      <c r="E181" t="s">
         <v>13</v>
       </c>
-      <c r="F176">
+      <c r="F181">
         <v>-0.58699999999999997</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A177" t="s">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
         <v>24</v>
       </c>
-      <c r="E177" t="s">
-        <v>14</v>
-      </c>
-      <c r="F177">
+      <c r="E182" t="s">
+        <v>14</v>
+      </c>
+      <c r="F182">
         <v>0.82350000000000001</v>
       </c>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A178" s="7" t="s">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A183" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="F178" s="9"/>
-      <c r="H178" s="7"/>
-    </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A179" s="5" t="s">
+      <c r="F183" s="9"/>
+      <c r="H183" s="7"/>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A184" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E179" t="s">
-        <v>14</v>
-      </c>
-      <c r="F179" s="5">
+      <c r="E184" t="s">
+        <v>14</v>
+      </c>
+      <c r="F184" s="5">
         <v>1</v>
       </c>
-      <c r="G179" s="5"/>
-      <c r="H179" s="5" t="s">
+      <c r="G184" s="5"/>
+      <c r="H184" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A180" t="s">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
         <v>30</v>
       </c>
-      <c r="E180" t="s">
-        <v>14</v>
-      </c>
-      <c r="F180">
+      <c r="E185" t="s">
+        <v>14</v>
+      </c>
+      <c r="F185">
         <v>1</v>
       </c>
-      <c r="H180" s="5" t="s">
+      <c r="H185" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A181" t="s">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
         <v>31</v>
       </c>
-      <c r="E181" t="s">
-        <v>14</v>
-      </c>
-      <c r="F181">
+      <c r="E186" t="s">
+        <v>14</v>
+      </c>
+      <c r="F186">
         <v>1</v>
       </c>
-      <c r="H181" s="5" t="s">
+      <c r="H186" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A182" t="s">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
         <v>32</v>
-      </c>
-      <c r="E182" t="s">
-        <v>14</v>
-      </c>
-      <c r="F182">
-        <v>1</v>
-      </c>
-      <c r="H182" s="5" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A183" t="s">
-        <v>33</v>
-      </c>
-      <c r="E183" t="s">
-        <v>14</v>
-      </c>
-      <c r="F183">
-        <v>1</v>
-      </c>
-      <c r="H183" s="5" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A184" t="s">
-        <v>34</v>
-      </c>
-      <c r="E184" t="s">
-        <v>13</v>
-      </c>
-      <c r="F184">
-        <v>-9.2499999999999999E-2</v>
-      </c>
-    </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A185" t="s">
-        <v>34</v>
-      </c>
-      <c r="E185" t="s">
-        <v>14</v>
-      </c>
-      <c r="F185">
-        <v>1.2939000000000001</v>
-      </c>
-    </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A186" t="s">
-        <v>35</v>
-      </c>
-      <c r="E186" t="s">
-        <v>14</v>
-      </c>
-      <c r="F186">
-        <v>0.94</v>
-      </c>
-      <c r="H186" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A187" t="s">
-        <v>36</v>
       </c>
       <c r="E187" t="s">
         <v>14</v>
@@ -3312,9 +3312,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E188" t="s">
         <v>14</v>
@@ -3326,56 +3326,73 @@
         <v>78</v>
       </c>
     </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
+        <v>34</v>
+      </c>
+      <c r="E189" t="s">
+        <v>13</v>
+      </c>
+      <c r="F189">
+        <v>-9.2499999999999999E-2</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>34</v>
+      </c>
+      <c r="E190" t="s">
+        <v>14</v>
+      </c>
+      <c r="F190">
+        <v>1.2939000000000001</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>35</v>
+      </c>
+      <c r="E191" t="s">
+        <v>14</v>
+      </c>
+      <c r="F191">
+        <v>0.94</v>
+      </c>
+      <c r="H191" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>36</v>
+      </c>
+      <c r="E192" t="s">
+        <v>14</v>
+      </c>
+      <c r="F192">
+        <v>1</v>
+      </c>
+      <c r="H192" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>37</v>
+      </c>
+      <c r="E193" t="s">
+        <v>14</v>
+      </c>
+      <c r="F193">
+        <v>1</v>
+      </c>
+      <c r="H193" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
         <v>38</v>
-      </c>
-      <c r="E189" t="s">
-        <v>14</v>
-      </c>
-      <c r="F189">
-        <v>1</v>
-      </c>
-      <c r="H189" s="5" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A190" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="L190" s="4"/>
-    </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A191" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="E191" t="s">
-        <v>13</v>
-      </c>
-      <c r="F191">
-        <v>-8.2500000000000004E-2</v>
-      </c>
-    </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A192" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="E192" t="s">
-        <v>14</v>
-      </c>
-      <c r="F192">
-        <v>0.72799999999999998</v>
-      </c>
-    </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A193" s="11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A194" s="5" t="s">
-        <v>73</v>
       </c>
       <c r="E194" t="s">
         <v>14</v>
@@ -3387,43 +3404,42 @@
         <v>78</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A195" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="E195" t="s">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A195" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="L195" s="4"/>
+    </row>
+    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A196" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="E196" t="s">
         <v>13</v>
       </c>
-      <c r="F195">
-        <v>-3.2399999999999998E-2</v>
-      </c>
-      <c r="H195" s="7"/>
-    </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A196" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="E196" t="s">
-        <v>14</v>
-      </c>
       <c r="F196">
-        <v>0.82120000000000004</v>
-      </c>
-      <c r="H196" s="7"/>
-    </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A197" s="11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+        <v>-8.2500000000000004E-2</v>
+      </c>
+    </row>
+    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A197" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="E197" t="s">
+        <v>14</v>
+      </c>
+      <c r="F197">
+        <v>0.72799999999999998</v>
+      </c>
+    </row>
+    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A198" s="11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A199" s="10" t="s">
-        <v>45</v>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A199" s="5" t="s">
+        <v>73</v>
       </c>
       <c r="E199" t="s">
         <v>14</v>
@@ -3435,65 +3451,43 @@
         <v>78</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A200" s="10" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E200" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F200">
-        <v>1</v>
-      </c>
-      <c r="H200" s="5" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A201" t="s">
-        <v>47</v>
+        <v>-3.2399999999999998E-2</v>
+      </c>
+      <c r="H200" s="7"/>
+    </row>
+    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A201" s="10" t="s">
+        <v>42</v>
       </c>
       <c r="E201" t="s">
         <v>14</v>
       </c>
       <c r="F201">
-        <v>1</v>
-      </c>
-      <c r="H201" s="5" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A202" t="s">
-        <v>48</v>
-      </c>
-      <c r="E202" t="s">
-        <v>14</v>
-      </c>
-      <c r="F202">
-        <v>1</v>
-      </c>
-      <c r="H202" s="5" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A203" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E203" t="s">
-        <v>14</v>
-      </c>
-      <c r="F203">
-        <v>1</v>
-      </c>
-      <c r="H203" s="5" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A204" s="5" t="s">
-        <v>50</v>
+        <v>0.82120000000000004</v>
+      </c>
+      <c r="H201" s="7"/>
+    </row>
+    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A202" s="11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A203" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="204" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A204" s="10" t="s">
+        <v>45</v>
       </c>
       <c r="E204" t="s">
         <v>14</v>
@@ -3505,9 +3499,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A205" s="5" t="s">
-        <v>51</v>
+    <row r="205" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A205" s="10" t="s">
+        <v>46</v>
       </c>
       <c r="E205" t="s">
         <v>14</v>
@@ -3519,9 +3513,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A206" s="5" t="s">
-        <v>52</v>
+    <row r="206" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>47</v>
       </c>
       <c r="E206" t="s">
         <v>14</v>
@@ -3533,9 +3527,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A207" s="5" t="s">
-        <v>53</v>
+    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>48</v>
       </c>
       <c r="E207" t="s">
         <v>14</v>
@@ -3547,9 +3541,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A208" s="5" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E208" t="s">
         <v>14</v>
@@ -3563,7 +3557,7 @@
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" s="5" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E209" t="s">
         <v>14</v>
@@ -3577,7 +3571,7 @@
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" s="5" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E210" t="s">
         <v>14</v>
@@ -3591,7 +3585,7 @@
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" s="5" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E211" t="s">
         <v>14</v>
@@ -3605,7 +3599,7 @@
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" s="5" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E212" t="s">
         <v>14</v>
@@ -3619,7 +3613,7 @@
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" s="5" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E213" t="s">
         <v>14</v>
@@ -3633,7 +3627,7 @@
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" s="5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E214" t="s">
         <v>14</v>
@@ -3647,7 +3641,7 @@
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" s="5" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E215" t="s">
         <v>14</v>
@@ -3661,7 +3655,7 @@
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" s="5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E216" t="s">
         <v>14</v>
@@ -3675,7 +3669,7 @@
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217" s="5" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E217" t="s">
         <v>14</v>
@@ -3689,7 +3683,7 @@
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" s="5" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E218" t="s">
         <v>14</v>
@@ -3703,7 +3697,7 @@
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" s="5" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E219" t="s">
         <v>14</v>
@@ -3717,7 +3711,7 @@
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" s="5" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E220" t="s">
         <v>14</v>
@@ -3731,7 +3725,7 @@
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" s="5" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E221" t="s">
         <v>14</v>
@@ -3745,7 +3739,7 @@
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222" s="5" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E222" t="s">
         <v>14</v>
@@ -3759,7 +3753,7 @@
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223" s="5" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E223" t="s">
         <v>14</v>
@@ -3773,7 +3767,7 @@
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" s="5" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E224" t="s">
         <v>14</v>
@@ -3787,7 +3781,7 @@
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" s="5" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E225" t="s">
         <v>14</v>
@@ -3801,7 +3795,7 @@
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" s="5" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E226" t="s">
         <v>14</v>
@@ -3810,6 +3804,76 @@
         <v>1</v>
       </c>
       <c r="H226" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A227" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E227" t="s">
+        <v>14</v>
+      </c>
+      <c r="F227">
+        <v>1</v>
+      </c>
+      <c r="H227" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A228" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E228" t="s">
+        <v>14</v>
+      </c>
+      <c r="F228">
+        <v>1</v>
+      </c>
+      <c r="H228" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A229" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E229" t="s">
+        <v>14</v>
+      </c>
+      <c r="F229">
+        <v>1</v>
+      </c>
+      <c r="H229" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A230" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E230" t="s">
+        <v>14</v>
+      </c>
+      <c r="F230">
+        <v>1</v>
+      </c>
+      <c r="H230" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A231" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E231" t="s">
+        <v>14</v>
+      </c>
+      <c r="F231">
+        <v>1</v>
+      </c>
+      <c r="H231" s="5" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3829,7 +3893,7 @@
         <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -3837,7 +3901,7 @@
         <v>111</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -3845,7 +3909,7 @@
         <v>112</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3853,7 +3917,7 @@
         <v>311</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -3861,7 +3925,7 @@
         <v>312</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -3869,7 +3933,7 @@
         <v>321</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -3877,7 +3941,7 @@
         <v>322</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -3885,7 +3949,7 @@
         <v>411</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -3893,7 +3957,7 @@
         <v>421</v>
       </c>
       <c r="B9" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -3901,7 +3965,7 @@
         <v>422</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -3909,7 +3973,7 @@
         <v>431</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -3917,7 +3981,7 @@
         <v>511</v>
       </c>
       <c r="B12" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -3925,7 +3989,7 @@
         <v>512</v>
       </c>
       <c r="B13" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -3933,7 +3997,7 @@
         <v>513</v>
       </c>
       <c r="B14" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -3941,7 +4005,7 @@
         <v>514</v>
       </c>
       <c r="B15" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -3949,7 +4013,7 @@
         <v>515</v>
       </c>
       <c r="B16" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -3957,7 +4021,7 @@
         <v>521</v>
       </c>
       <c r="B17" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -3965,7 +4029,7 @@
         <v>611</v>
       </c>
       <c r="B18" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -3973,7 +4037,7 @@
         <v>612</v>
       </c>
       <c r="B19" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -3981,7 +4045,7 @@
         <v>621</v>
       </c>
       <c r="B20" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -3989,7 +4053,7 @@
         <v>622</v>
       </c>
       <c r="B21" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -3997,7 +4061,7 @@
         <v>711</v>
       </c>
       <c r="B22" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -4005,7 +4069,7 @@
         <v>731</v>
       </c>
       <c r="B23" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -4013,7 +4077,7 @@
         <v>811</v>
       </c>
       <c r="B24" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -4021,7 +4085,7 @@
         <v>812</v>
       </c>
       <c r="B25" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -4029,7 +4093,7 @@
         <v>813</v>
       </c>
       <c r="B26" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -4037,7 +4101,7 @@
         <v>814</v>
       </c>
       <c r="B27" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -4045,7 +4109,7 @@
         <v>821</v>
       </c>
       <c r="B28" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -4053,7 +4117,7 @@
         <v>831</v>
       </c>
       <c r="B29" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -4061,7 +4125,7 @@
         <v>911</v>
       </c>
       <c r="B30" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -4069,7 +4133,7 @@
         <v>912</v>
       </c>
       <c r="B31" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -4077,7 +4141,7 @@
         <v>913</v>
       </c>
       <c r="B32" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -4085,7 +4149,7 @@
         <v>1011</v>
       </c>
       <c r="B33" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -4093,7 +4157,7 @@
         <v>1111</v>
       </c>
       <c r="B34" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -4101,7 +4165,7 @@
         <v>1112</v>
       </c>
       <c r="B35" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -4109,7 +4173,7 @@
         <v>1121</v>
       </c>
       <c r="B36" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -4117,7 +4181,7 @@
         <v>1122</v>
       </c>
       <c r="B37" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -4125,7 +4189,7 @@
         <v>1123</v>
       </c>
       <c r="B38" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -4133,7 +4197,7 @@
         <v>1124</v>
       </c>
       <c r="B39" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -4141,7 +4205,7 @@
         <v>1131</v>
       </c>
       <c r="B40" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -4149,7 +4213,7 @@
         <v>1211</v>
       </c>
       <c r="B41" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -4157,7 +4221,7 @@
         <v>1212</v>
       </c>
       <c r="B42" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -4165,7 +4229,7 @@
         <v>1213</v>
       </c>
       <c r="B43" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -4173,7 +4237,7 @@
         <v>1214</v>
       </c>
       <c r="B44" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -4181,7 +4245,7 @@
         <v>1215</v>
       </c>
       <c r="B45" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -4189,7 +4253,7 @@
         <v>1216</v>
       </c>
       <c r="B46" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -4197,7 +4261,7 @@
         <v>1221</v>
       </c>
       <c r="B47" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -4205,7 +4269,7 @@
         <v>1222</v>
       </c>
       <c r="B48" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -4213,7 +4277,7 @@
         <v>1311</v>
       </c>
       <c r="B49" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -4221,7 +4285,7 @@
         <v>1321</v>
       </c>
       <c r="B50" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -4229,7 +4293,7 @@
         <v>1322</v>
       </c>
       <c r="B51" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -4237,7 +4301,7 @@
         <v>1331</v>
       </c>
       <c r="B52" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -4245,7 +4309,7 @@
         <v>1411</v>
       </c>
       <c r="B53" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -4253,7 +4317,7 @@
         <v>1412</v>
       </c>
       <c r="B54" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -4261,7 +4325,7 @@
         <v>1421</v>
       </c>
       <c r="B55" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -4269,7 +4333,7 @@
         <v>1511</v>
       </c>
       <c r="B56" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -4277,7 +4341,7 @@
         <v>1512</v>
       </c>
       <c r="B57" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -4285,7 +4349,7 @@
         <v>1521</v>
       </c>
       <c r="B58" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -4293,7 +4357,7 @@
         <v>1522</v>
       </c>
       <c r="B59" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -4301,7 +4365,7 @@
         <v>1611</v>
       </c>
       <c r="B60" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -4309,7 +4373,7 @@
         <v>1612</v>
       </c>
       <c r="B61" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -4317,7 +4381,7 @@
         <v>1613</v>
       </c>
       <c r="B62" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -4325,7 +4389,7 @@
         <v>1614</v>
       </c>
       <c r="B63" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -4333,7 +4397,7 @@
         <v>1615</v>
       </c>
       <c r="B64" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -4341,7 +4405,7 @@
         <v>1616</v>
       </c>
       <c r="B65" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -4349,7 +4413,7 @@
         <v>1617</v>
       </c>
       <c r="B66" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -4357,7 +4421,7 @@
         <v>1621</v>
       </c>
       <c r="B67" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -4365,7 +4429,7 @@
         <v>1622</v>
       </c>
       <c r="B68" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -4373,7 +4437,7 @@
         <v>1623</v>
       </c>
       <c r="B69" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -4381,7 +4445,7 @@
         <v>1711</v>
       </c>
       <c r="B70" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -4389,7 +4453,7 @@
         <v>1712</v>
       </c>
       <c r="B71" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -4397,7 +4461,7 @@
         <v>1713</v>
       </c>
       <c r="B72" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -4405,7 +4469,7 @@
         <v>1721</v>
       </c>
       <c r="B73" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -4413,7 +4477,7 @@
         <v>1722</v>
       </c>
       <c r="B74" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -4421,7 +4485,7 @@
         <v>1723</v>
       </c>
       <c r="B75" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -4429,7 +4493,7 @@
         <v>1724</v>
       </c>
       <c r="B76" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -4437,7 +4501,7 @@
         <v>1811</v>
       </c>
       <c r="B77" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -4445,7 +4509,7 @@
         <v>1812</v>
       </c>
       <c r="B78" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -4453,7 +4517,7 @@
         <v>1813</v>
       </c>
       <c r="B79" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -4461,7 +4525,7 @@
         <v>1821</v>
       </c>
       <c r="B80" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
@@ -4469,7 +4533,7 @@
         <v>1911</v>
       </c>
       <c r="B81" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
@@ -4477,7 +4541,7 @@
         <v>1912</v>
       </c>
       <c r="B82" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
@@ -4485,7 +4549,7 @@
         <v>1921</v>
       </c>
       <c r="B83" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
@@ -4493,7 +4557,7 @@
         <v>1922</v>
       </c>
       <c r="B84" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
@@ -4501,7 +4565,7 @@
         <v>2011</v>
       </c>
       <c r="B85" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
@@ -4509,7 +4573,7 @@
         <v>2012</v>
       </c>
       <c r="B86" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
@@ -4517,7 +4581,7 @@
         <v>2019</v>
       </c>
       <c r="B87" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
@@ -4525,7 +4589,7 @@
         <v>2111</v>
       </c>
       <c r="B88" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
@@ -4533,7 +4597,7 @@
         <v>2121</v>
       </c>
       <c r="B89" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
@@ -4541,7 +4605,7 @@
         <v>2122</v>
       </c>
       <c r="B90" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
@@ -4549,7 +4613,7 @@
         <v>2211</v>
       </c>
       <c r="B91" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
@@ -4557,7 +4621,7 @@
         <v>2212</v>
       </c>
       <c r="B92" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
@@ -4565,7 +4629,7 @@
         <v>2221</v>
       </c>
       <c r="B93" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
@@ -4573,7 +4637,7 @@
         <v>2311</v>
       </c>
       <c r="B94" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
@@ -4581,7 +4645,7 @@
         <v>2312</v>
       </c>
       <c r="B95" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
@@ -4589,7 +4653,7 @@
         <v>2319</v>
       </c>
       <c r="B96" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
@@ -4597,7 +4661,7 @@
         <v>2331</v>
       </c>
       <c r="B97" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
@@ -4605,7 +4669,7 @@
         <v>2411</v>
       </c>
       <c r="B98" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
@@ -4613,7 +4677,7 @@
         <v>2412</v>
       </c>
       <c r="B99" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
@@ -4621,7 +4685,7 @@
         <v>2413</v>
       </c>
       <c r="B100" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
@@ -4629,7 +4693,7 @@
         <v>2414</v>
       </c>
       <c r="B101" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
@@ -4637,7 +4701,7 @@
         <v>2415</v>
       </c>
       <c r="B102" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
@@ -4645,7 +4709,7 @@
         <v>2419</v>
       </c>
       <c r="B103" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
@@ -4653,7 +4717,7 @@
         <v>2511</v>
       </c>
       <c r="B104" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
@@ -4661,7 +4725,7 @@
         <v>2512</v>
       </c>
       <c r="B105" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
@@ -4669,7 +4733,7 @@
         <v>2519</v>
       </c>
       <c r="B106" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
@@ -4677,7 +4741,7 @@
         <v>2521</v>
       </c>
       <c r="B107" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/data/prod_parameters/PlantNutrientMgmt.xlsx
+++ b/data/prod_parameters/PlantNutrientMgmt.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18240" windowHeight="10650"/>
   </bookViews>
   <sheets>
     <sheet name="default" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1036" uniqueCount="185">
   <si>
     <t>f_crop</t>
   </si>
@@ -417,15 +417,199 @@
   <si>
     <t>Specialbearbetning av stallgödselundersökningen till Einarsson et al 2022. The nitrogen footprint of Swedish food consumption.</t>
   </si>
+  <si>
+    <t>Manure distribution parameters</t>
+  </si>
+  <si>
+    <t>NPK mixtures</t>
+  </si>
+  <si>
+    <t>Calcium ammonium nitrate</t>
+  </si>
+  <si>
+    <t>Ammonium nitrate</t>
+  </si>
+  <si>
+    <t>% of N</t>
+  </si>
+  <si>
+    <t>Swedish IIR 2023. Table 5-23</t>
+  </si>
+  <si>
+    <t>Only three largest included for now</t>
+  </si>
+  <si>
+    <t>f_compound</t>
+  </si>
+  <si>
+    <t>NH3-N</t>
+  </si>
+  <si>
+    <t>% of TAN</t>
+  </si>
+  <si>
+    <t>Swedish IIR 2023. Table 5-24</t>
+  </si>
+  <si>
+    <t>Swedish IIR 2023. Table 5-25</t>
+  </si>
+  <si>
+    <t>Recalculated from gNH3/kgN</t>
+  </si>
+  <si>
+    <t>f_species</t>
+  </si>
+  <si>
+    <t>f_breed</t>
+  </si>
+  <si>
+    <t>f_animal</t>
+  </si>
+  <si>
+    <t>f_MMS</t>
+  </si>
+  <si>
+    <t>Ammonia emissions spreading fertiliser and manure</t>
+  </si>
+  <si>
+    <t>cattle</t>
+  </si>
+  <si>
+    <t>dairy</t>
+  </si>
+  <si>
+    <t>cows</t>
+  </si>
+  <si>
+    <t>beef</t>
+  </si>
+  <si>
+    <t>heifers</t>
+  </si>
+  <si>
+    <t>calves</t>
+  </si>
+  <si>
+    <t>pigs</t>
+  </si>
+  <si>
+    <t>sows</t>
+  </si>
+  <si>
+    <t>boars</t>
+  </si>
+  <si>
+    <t>piglets</t>
+  </si>
+  <si>
+    <t>gilts</t>
+  </si>
+  <si>
+    <t>poultry</t>
+  </si>
+  <si>
+    <t>broiler</t>
+  </si>
+  <si>
+    <t>liquid</t>
+  </si>
+  <si>
+    <t>solid</t>
+  </si>
+  <si>
+    <t>deep litter</t>
+  </si>
+  <si>
+    <t>bulls, steers and breeding bulls</t>
+  </si>
+  <si>
+    <t>growing and finishing pigs</t>
+  </si>
+  <si>
+    <t>same as sows</t>
+  </si>
+  <si>
+    <t>horses</t>
+  </si>
+  <si>
+    <t>mineral_N_fertiliser_share</t>
+  </si>
+  <si>
+    <t>f_fertiliser_type</t>
+  </si>
+  <si>
+    <t>application_losses</t>
+  </si>
+  <si>
+    <t>conventional</t>
+  </si>
+  <si>
+    <t>Mineral fertiliser shares</t>
+  </si>
+  <si>
+    <t>No mineral N for organic</t>
+  </si>
+  <si>
+    <t>fallback</t>
+  </si>
+  <si>
+    <t>Mineral fertilisers</t>
+  </si>
+  <si>
+    <t>Manure</t>
+  </si>
+  <si>
+    <t>Swedish IIR 2023. Table 5-13</t>
+  </si>
+  <si>
+    <t>Soil N2O emissions</t>
+  </si>
+  <si>
+    <t>N2O-N</t>
+  </si>
+  <si>
+    <t>mineral_EF</t>
+  </si>
+  <si>
+    <t>crop_resid_EF</t>
+  </si>
+  <si>
+    <t>grazing</t>
+  </si>
+  <si>
+    <t>Swedish NIR 2021. Table 5.18</t>
+  </si>
+  <si>
+    <t>Swedish NIR 2021. Table 5.20</t>
+  </si>
+  <si>
+    <t>organic_EF</t>
+  </si>
+  <si>
+    <t>applied manure/other organic</t>
+  </si>
+  <si>
+    <t>manure on pasture (cattle)</t>
+  </si>
+  <si>
+    <t>manure on pasture (other)</t>
+  </si>
+  <si>
+    <t>crop residues</t>
+  </si>
+  <si>
+    <t>mineral N fertiliser</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0E+00"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -484,6 +668,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="2" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -511,7 +702,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -524,6 +715,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -804,89 +998,129 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L231"/>
+  <dimension ref="A1:R287"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.42578125" customWidth="1"/>
-    <col min="2" max="2" width="7.28515625" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="31.42578125" customWidth="1"/>
-    <col min="5" max="5" width="23.7109375" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="8.140625" customWidth="1"/>
-    <col min="8" max="8" width="35.42578125" customWidth="1"/>
-    <col min="9" max="9" width="27.42578125" customWidth="1"/>
+    <col min="1" max="1" width="21" customWidth="1"/>
+    <col min="2" max="2" width="31.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="11.140625" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11" customWidth="1"/>
+    <col min="13" max="13" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="35.42578125" customWidth="1"/>
+    <col min="15" max="15" width="27.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C3" t="s">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
         <v>114</v>
       </c>
-      <c r="E3" t="s">
+      <c r="K4" t="s">
         <v>121</v>
       </c>
-      <c r="F3">
+      <c r="L4">
         <v>91</v>
       </c>
-      <c r="G3" t="s">
+      <c r="M4" t="s">
         <v>113</v>
       </c>
-      <c r="H3" t="s">
+      <c r="N4" t="s">
         <v>122</v>
       </c>
-      <c r="I3" t="s">
+      <c r="O4" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E5" t="s">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="K5" t="s">
         <v>116</v>
       </c>
-      <c r="F5">
+      <c r="L5">
         <v>22</v>
       </c>
-      <c r="G5" t="s">
+      <c r="M5" t="s">
         <v>115</v>
       </c>
-      <c r="H5" t="s">
+      <c r="N5" t="s">
         <v>120</v>
       </c>
-      <c r="I5" t="s">
+      <c r="O5" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>118</v>
+        <v>166</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -894,2987 +1128,4749 @@
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E8" s="6" t="s">
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K8" t="s">
+        <v>162</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8" t="s">
+        <v>128</v>
+      </c>
+      <c r="N8" s="5" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>165</v>
+      </c>
+      <c r="E9" t="s">
+        <v>126</v>
+      </c>
+      <c r="K9" t="s">
+        <v>162</v>
+      </c>
+      <c r="L9">
+        <v>59</v>
+      </c>
+      <c r="M9" t="s">
+        <v>128</v>
+      </c>
+      <c r="N9" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="O9" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
+        <v>165</v>
+      </c>
+      <c r="E10" t="s">
+        <v>127</v>
+      </c>
+      <c r="K10" t="s">
+        <v>162</v>
+      </c>
+      <c r="L10">
+        <v>7</v>
+      </c>
+      <c r="M10" t="s">
+        <v>128</v>
+      </c>
+      <c r="O10" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>165</v>
+      </c>
+      <c r="E11" t="s">
+        <v>125</v>
+      </c>
+      <c r="K11" t="s">
+        <v>162</v>
+      </c>
+      <c r="L11">
+        <v>34</v>
+      </c>
+      <c r="M11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O11" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="K14" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="6">
+      <c r="L14" s="6">
         <v>0</v>
       </c>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6" t="s">
+      <c r="M14" s="6"/>
+      <c r="N14" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E9" s="6" t="s">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="K15" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="6">
+      <c r="L15" s="6">
         <v>0</v>
       </c>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6" t="s">
+      <c r="M15" s="6"/>
+      <c r="N15" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E10" s="6" t="s">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="K16" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="6">
+      <c r="L16" s="6">
         <v>0</v>
       </c>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6" t="s">
+      <c r="M16" s="6"/>
+      <c r="N16" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11">
-        <v>-0.80359999999999998</v>
-      </c>
-      <c r="H11" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12">
-        <v>24.088999999999999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13">
-        <v>50.213999999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14">
-        <v>55.213999999999999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" t="s">
-        <v>96</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15">
-        <v>-0.71430000000000005</v>
-      </c>
-      <c r="H15" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16" t="s">
-        <v>96</v>
-      </c>
-      <c r="E16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16">
-        <v>23.143000000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>7</v>
       </c>
-      <c r="D17" t="s">
-        <v>96</v>
-      </c>
-      <c r="E17" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17">
-        <v>42.570999999999998</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K17" t="s">
+        <v>10</v>
+      </c>
+      <c r="L17">
+        <v>-0.80359999999999998</v>
+      </c>
+      <c r="N17" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>7</v>
       </c>
-      <c r="B18" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" t="s">
-        <v>96</v>
-      </c>
-      <c r="E18" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18">
-        <v>47.570999999999998</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K18" t="s">
+        <v>11</v>
+      </c>
+      <c r="L18">
+        <v>24.088999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>7</v>
       </c>
-      <c r="D19" t="s">
-        <v>95</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" s="9">
-        <f>F15</f>
-        <v>-0.71430000000000005</v>
-      </c>
-      <c r="H19" s="9" t="str">
-        <f>H15</f>
-        <v>Höstvete foder/bröd, södra götaland</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K19" t="s">
+        <v>12</v>
+      </c>
+      <c r="L19">
+        <v>50.213999999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>7</v>
       </c>
       <c r="D20" t="s">
-        <v>95</v>
-      </c>
-      <c r="E20" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" s="9">
-        <f t="shared" ref="F20:F22" si="0">F16</f>
-        <v>23.143000000000001</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="K20" t="s">
+        <v>12</v>
+      </c>
+      <c r="L20">
+        <v>55.213999999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>7</v>
       </c>
-      <c r="D21" t="s">
+      <c r="B21" t="s">
+        <v>96</v>
+      </c>
+      <c r="K21" t="s">
+        <v>10</v>
+      </c>
+      <c r="L21">
+        <v>-0.71430000000000005</v>
+      </c>
+      <c r="N21" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" t="s">
+        <v>96</v>
+      </c>
+      <c r="K22" t="s">
+        <v>11</v>
+      </c>
+      <c r="L22">
+        <v>23.143000000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" t="s">
+        <v>96</v>
+      </c>
+      <c r="K23" t="s">
+        <v>12</v>
+      </c>
+      <c r="L23">
+        <v>42.570999999999998</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" t="s">
+        <v>96</v>
+      </c>
+      <c r="D24" t="s">
+        <v>9</v>
+      </c>
+      <c r="K24" t="s">
+        <v>12</v>
+      </c>
+      <c r="L24">
+        <v>47.570999999999998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" t="s">
         <v>95</v>
       </c>
-      <c r="E21" t="s">
+      <c r="K25" t="s">
+        <v>10</v>
+      </c>
+      <c r="L25" s="9">
+        <f>L21</f>
+        <v>-0.71430000000000005</v>
+      </c>
+      <c r="N25" s="9" t="str">
+        <f>N21</f>
+        <v>Höstvete foder/bröd, södra götaland</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" t="s">
+        <v>95</v>
+      </c>
+      <c r="K26" t="s">
+        <v>11</v>
+      </c>
+      <c r="L26" s="9">
+        <f t="shared" ref="L26:L28" si="0">L22</f>
+        <v>23.143000000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" t="s">
+        <v>95</v>
+      </c>
+      <c r="K27" t="s">
         <v>12</v>
       </c>
-      <c r="F21" s="9">
+      <c r="L27" s="9">
         <f t="shared" si="0"/>
         <v>42.570999999999998</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>7</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B28" t="s">
+        <v>95</v>
+      </c>
+      <c r="D28" t="s">
         <v>9</v>
       </c>
-      <c r="D22" t="s">
-        <v>95</v>
-      </c>
-      <c r="E22" t="s">
+      <c r="K28" t="s">
         <v>12</v>
       </c>
-      <c r="F22" s="9">
+      <c r="L28" s="9">
         <f t="shared" si="0"/>
         <v>47.570999999999998</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>16</v>
       </c>
-      <c r="E23" t="s">
+      <c r="K29" t="s">
         <v>11</v>
       </c>
-      <c r="F23">
+      <c r="L29">
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>16</v>
       </c>
-      <c r="E24" t="s">
+      <c r="K30" t="s">
         <v>12</v>
       </c>
-      <c r="F24">
+      <c r="L30">
         <v>70</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25">
-        <v>-1.7857000000000001</v>
-      </c>
-      <c r="H25" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>27</v>
-      </c>
-      <c r="E26" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26">
-        <v>30.786000000000001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>27</v>
-      </c>
-      <c r="E27" t="s">
-        <v>12</v>
-      </c>
-      <c r="F27">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>27</v>
-      </c>
-      <c r="D28" t="s">
-        <v>96</v>
-      </c>
-      <c r="E28" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28">
-        <v>-1.25</v>
-      </c>
-      <c r="H28" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>27</v>
-      </c>
-      <c r="D29" t="s">
-        <v>96</v>
-      </c>
-      <c r="E29" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29">
-        <v>27.75</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>27</v>
-      </c>
-      <c r="D30" t="s">
-        <v>96</v>
-      </c>
-      <c r="E30" t="s">
-        <v>12</v>
-      </c>
-      <c r="F30">
-        <v>18.25</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>27</v>
       </c>
-      <c r="D31" t="s">
-        <v>95</v>
-      </c>
-      <c r="E31" t="s">
+      <c r="K31" t="s">
         <v>10</v>
       </c>
-      <c r="F31" s="9">
-        <f>F28</f>
-        <v>-1.25</v>
-      </c>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9" t="str">
-        <f>H28</f>
-        <v>Råg, södra götaland</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="L31">
+        <v>-1.7857000000000001</v>
+      </c>
+      <c r="N31" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>27</v>
       </c>
-      <c r="D32" t="s">
-        <v>95</v>
-      </c>
-      <c r="E32" t="s">
+      <c r="K32" t="s">
         <v>11</v>
       </c>
-      <c r="F32" s="9">
-        <f>F29</f>
-        <v>27.75</v>
-      </c>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="L32">
+        <v>30.786000000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>27</v>
       </c>
-      <c r="D33" t="s">
+      <c r="K33" t="s">
+        <v>12</v>
+      </c>
+      <c r="L33">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>27</v>
+      </c>
+      <c r="B34" t="s">
+        <v>96</v>
+      </c>
+      <c r="K34" t="s">
+        <v>10</v>
+      </c>
+      <c r="L34">
+        <v>-1.25</v>
+      </c>
+      <c r="N34" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>27</v>
+      </c>
+      <c r="B35" t="s">
+        <v>96</v>
+      </c>
+      <c r="K35" t="s">
+        <v>11</v>
+      </c>
+      <c r="L35">
+        <v>27.75</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>27</v>
+      </c>
+      <c r="B36" t="s">
+        <v>96</v>
+      </c>
+      <c r="K36" t="s">
+        <v>12</v>
+      </c>
+      <c r="L36">
+        <v>18.25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>27</v>
+      </c>
+      <c r="B37" t="s">
         <v>95</v>
       </c>
-      <c r="E33" t="s">
+      <c r="K37" t="s">
+        <v>10</v>
+      </c>
+      <c r="L37" s="9">
+        <f>L34</f>
+        <v>-1.25</v>
+      </c>
+      <c r="M37" s="9"/>
+      <c r="N37" s="9" t="str">
+        <f>N34</f>
+        <v>Råg, södra götaland</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>27</v>
+      </c>
+      <c r="B38" t="s">
+        <v>95</v>
+      </c>
+      <c r="K38" t="s">
+        <v>11</v>
+      </c>
+      <c r="L38" s="9">
+        <f>L35</f>
+        <v>27.75</v>
+      </c>
+      <c r="M38" s="9"/>
+      <c r="N38" s="9"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>27</v>
+      </c>
+      <c r="B39" t="s">
+        <v>95</v>
+      </c>
+      <c r="K39" t="s">
         <v>12</v>
       </c>
-      <c r="F33" s="9">
-        <f>F30</f>
+      <c r="L39" s="9">
+        <f>L36</f>
         <v>18.25</v>
       </c>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>23</v>
-      </c>
-      <c r="E34" t="s">
-        <v>11</v>
-      </c>
-      <c r="F34">
-        <v>16.856999999999999</v>
-      </c>
-      <c r="H34" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>23</v>
-      </c>
-      <c r="E35" t="s">
-        <v>12</v>
-      </c>
-      <c r="F35">
-        <v>59.143000000000001</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>23</v>
-      </c>
-      <c r="D36" t="s">
-        <v>96</v>
-      </c>
-      <c r="E36" t="s">
-        <v>10</v>
-      </c>
-      <c r="F36">
-        <v>-0.71430000000000005</v>
-      </c>
-      <c r="H36" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>23</v>
-      </c>
-      <c r="D37" t="s">
-        <v>96</v>
-      </c>
-      <c r="E37" t="s">
-        <v>11</v>
-      </c>
-      <c r="F37">
-        <v>23.143000000000001</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D38" t="s">
-        <v>96</v>
-      </c>
-      <c r="E38" t="s">
-        <v>12</v>
-      </c>
-      <c r="F38">
-        <v>37.570999999999998</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>23</v>
-      </c>
-      <c r="D39" t="s">
-        <v>95</v>
-      </c>
-      <c r="E39" t="s">
-        <v>10</v>
-      </c>
-      <c r="F39" s="9">
-        <f>F36</f>
-        <v>-0.71430000000000005</v>
-      </c>
-      <c r="H39" s="9" t="str">
-        <f>H36</f>
-        <v>Rågvete/höstkorn, södra götaland</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="M39" s="9"/>
+      <c r="N39" s="9"/>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>23</v>
       </c>
-      <c r="D40" t="s">
-        <v>95</v>
-      </c>
-      <c r="E40" t="s">
+      <c r="K40" t="s">
         <v>11</v>
       </c>
-      <c r="F40" s="9">
-        <f>F37</f>
-        <v>23.143000000000001</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="L40">
+        <v>16.856999999999999</v>
+      </c>
+      <c r="N40" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>23</v>
       </c>
-      <c r="D41" t="s">
+      <c r="K41" t="s">
+        <v>12</v>
+      </c>
+      <c r="L41">
+        <v>59.143000000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>23</v>
+      </c>
+      <c r="B42" t="s">
+        <v>96</v>
+      </c>
+      <c r="K42" t="s">
+        <v>10</v>
+      </c>
+      <c r="L42">
+        <v>-0.71430000000000005</v>
+      </c>
+      <c r="N42" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>23</v>
+      </c>
+      <c r="B43" t="s">
+        <v>96</v>
+      </c>
+      <c r="K43" t="s">
+        <v>11</v>
+      </c>
+      <c r="L43">
+        <v>23.143000000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>23</v>
+      </c>
+      <c r="B44" t="s">
+        <v>96</v>
+      </c>
+      <c r="K44" t="s">
+        <v>12</v>
+      </c>
+      <c r="L44">
+        <v>37.570999999999998</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>23</v>
+      </c>
+      <c r="B45" t="s">
         <v>95</v>
       </c>
-      <c r="E41" t="s">
+      <c r="K45" t="s">
+        <v>10</v>
+      </c>
+      <c r="L45" s="9">
+        <f>L42</f>
+        <v>-0.71430000000000005</v>
+      </c>
+      <c r="N45" s="9" t="str">
+        <f>N42</f>
+        <v>Rågvete/höstkorn, södra götaland</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>23</v>
+      </c>
+      <c r="B46" t="s">
+        <v>95</v>
+      </c>
+      <c r="K46" t="s">
+        <v>11</v>
+      </c>
+      <c r="L46" s="9">
+        <f>L43</f>
+        <v>23.143000000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>23</v>
+      </c>
+      <c r="B47" t="s">
+        <v>95</v>
+      </c>
+      <c r="K47" t="s">
         <v>12</v>
       </c>
-      <c r="F41" s="9">
-        <f>F38</f>
+      <c r="L47" s="9">
+        <f>L44</f>
         <v>37.570999999999998</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>17</v>
-      </c>
-      <c r="E42" t="s">
-        <v>10</v>
-      </c>
-      <c r="F42">
-        <v>-1.0713999999999999</v>
-      </c>
-      <c r="H42" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>17</v>
-      </c>
-      <c r="E43" t="s">
-        <v>11</v>
-      </c>
-      <c r="F43">
-        <v>23.928999999999998</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>17</v>
-      </c>
-      <c r="E44" t="s">
-        <v>12</v>
-      </c>
-      <c r="F44">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>17</v>
-      </c>
-      <c r="B45" t="s">
-        <v>9</v>
-      </c>
-      <c r="E45" t="s">
-        <v>10</v>
-      </c>
-      <c r="F45" s="8">
-        <v>1E-13</v>
-      </c>
-      <c r="H45" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>17</v>
-      </c>
-      <c r="B46" t="s">
-        <v>9</v>
-      </c>
-      <c r="E46" t="s">
-        <v>11</v>
-      </c>
-      <c r="F46">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>17</v>
-      </c>
-      <c r="B47" t="s">
-        <v>9</v>
-      </c>
-      <c r="E47" t="s">
-        <v>12</v>
-      </c>
-      <c r="F47">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>17</v>
       </c>
-      <c r="D48" t="s">
-        <v>96</v>
-      </c>
-      <c r="E48" t="s">
+      <c r="K48" t="s">
         <v>10</v>
       </c>
-      <c r="F48">
-        <v>-1.25</v>
-      </c>
-      <c r="H48" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="L48">
+        <v>-1.0713999999999999</v>
+      </c>
+      <c r="N48" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>17</v>
       </c>
-      <c r="D49" t="s">
-        <v>96</v>
-      </c>
-      <c r="E49" t="s">
+      <c r="K49" t="s">
         <v>11</v>
       </c>
-      <c r="F49">
-        <v>25.25</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="L49">
+        <v>23.928999999999998</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>17</v>
       </c>
-      <c r="D50" t="s">
-        <v>96</v>
-      </c>
-      <c r="E50" t="s">
+      <c r="K50" t="s">
         <v>12</v>
       </c>
-      <c r="F50">
-        <v>19.75</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="L50">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>17</v>
       </c>
-      <c r="B51" t="s">
+      <c r="D51" t="s">
         <v>9</v>
       </c>
-      <c r="D51" t="s">
-        <v>96</v>
-      </c>
-      <c r="E51" t="s">
+      <c r="K51" t="s">
         <v>10</v>
       </c>
-      <c r="F51" s="8">
-        <v>-2E-12</v>
-      </c>
-      <c r="H51" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="L51" s="8">
+        <v>1E-13</v>
+      </c>
+      <c r="N51" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>17</v>
       </c>
-      <c r="B52" t="s">
+      <c r="D52" t="s">
         <v>9</v>
       </c>
-      <c r="D52" t="s">
-        <v>96</v>
-      </c>
-      <c r="E52" t="s">
+      <c r="K52" t="s">
         <v>11</v>
       </c>
-      <c r="F52">
+      <c r="L52">
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>17</v>
       </c>
-      <c r="B53" t="s">
+      <c r="D53" t="s">
         <v>9</v>
       </c>
-      <c r="D53" t="s">
-        <v>96</v>
-      </c>
-      <c r="E53" t="s">
+      <c r="K53" t="s">
         <v>12</v>
       </c>
-      <c r="F53">
+      <c r="L53">
         <v>45</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>17</v>
       </c>
-      <c r="D54" t="s">
-        <v>95</v>
-      </c>
-      <c r="E54" t="s">
+      <c r="B54" t="s">
+        <v>96</v>
+      </c>
+      <c r="K54" t="s">
         <v>10</v>
       </c>
-      <c r="F54" s="9">
-        <f t="shared" ref="F54:F59" si="1">F48</f>
+      <c r="L54">
         <v>-1.25</v>
       </c>
-      <c r="H54" s="9" t="str">
-        <f>H48</f>
-        <v>Korn foder, södra götaland</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="N54" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>17</v>
       </c>
-      <c r="D55" t="s">
+      <c r="B55" t="s">
+        <v>96</v>
+      </c>
+      <c r="K55" t="s">
+        <v>11</v>
+      </c>
+      <c r="L55">
+        <v>25.25</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>17</v>
+      </c>
+      <c r="B56" t="s">
+        <v>96</v>
+      </c>
+      <c r="K56" t="s">
+        <v>12</v>
+      </c>
+      <c r="L56">
+        <v>19.75</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>17</v>
+      </c>
+      <c r="B57" t="s">
+        <v>96</v>
+      </c>
+      <c r="D57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K57" t="s">
+        <v>10</v>
+      </c>
+      <c r="L57" s="8">
+        <v>-2E-12</v>
+      </c>
+      <c r="N57" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>17</v>
+      </c>
+      <c r="B58" t="s">
+        <v>96</v>
+      </c>
+      <c r="D58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K58" t="s">
+        <v>11</v>
+      </c>
+      <c r="L58">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>17</v>
+      </c>
+      <c r="B59" t="s">
+        <v>96</v>
+      </c>
+      <c r="D59" t="s">
+        <v>9</v>
+      </c>
+      <c r="K59" t="s">
+        <v>12</v>
+      </c>
+      <c r="L59">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>17</v>
+      </c>
+      <c r="B60" t="s">
         <v>95</v>
       </c>
-      <c r="E55" t="s">
+      <c r="K60" t="s">
+        <v>10</v>
+      </c>
+      <c r="L60" s="9">
+        <f t="shared" ref="L60:L65" si="1">L54</f>
+        <v>-1.25</v>
+      </c>
+      <c r="N60" s="9" t="str">
+        <f>N54</f>
+        <v>Korn foder, södra götaland</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>17</v>
+      </c>
+      <c r="B61" t="s">
+        <v>95</v>
+      </c>
+      <c r="K61" t="s">
         <v>11</v>
       </c>
-      <c r="F55" s="9">
+      <c r="L61" s="9">
         <f t="shared" si="1"/>
         <v>25.25</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
         <v>17</v>
       </c>
-      <c r="D56" t="s">
+      <c r="B62" t="s">
         <v>95</v>
       </c>
-      <c r="E56" t="s">
+      <c r="K62" t="s">
         <v>12</v>
       </c>
-      <c r="F56" s="9">
+      <c r="L62" s="9">
         <f t="shared" si="1"/>
         <v>19.75</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
         <v>17</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B63" t="s">
+        <v>95</v>
+      </c>
+      <c r="D63" t="s">
         <v>9</v>
       </c>
-      <c r="D57" t="s">
-        <v>95</v>
-      </c>
-      <c r="E57" t="s">
+      <c r="K63" t="s">
         <v>10</v>
       </c>
-      <c r="F57" s="9">
+      <c r="L63" s="9">
         <f t="shared" si="1"/>
         <v>-2E-12</v>
       </c>
-      <c r="H57" s="9" t="str">
-        <f>H51</f>
+      <c r="N63" s="9" t="str">
+        <f>N57</f>
         <v>Korn, malt södra götaland</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
         <v>17</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B64" t="s">
+        <v>95</v>
+      </c>
+      <c r="D64" t="s">
         <v>9</v>
       </c>
-      <c r="D58" t="s">
-        <v>95</v>
-      </c>
-      <c r="E58" t="s">
+      <c r="K64" t="s">
         <v>11</v>
       </c>
-      <c r="F58" s="9">
+      <c r="L64" s="9">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
         <v>17</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B65" t="s">
+        <v>95</v>
+      </c>
+      <c r="D65" t="s">
         <v>9</v>
       </c>
-      <c r="D59" t="s">
-        <v>95</v>
-      </c>
-      <c r="E59" t="s">
+      <c r="K65" t="s">
         <v>12</v>
       </c>
-      <c r="F59" s="9">
+      <c r="L65" s="9">
         <f t="shared" si="1"/>
         <v>45</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
         <v>17</v>
       </c>
-      <c r="D60" t="s">
+      <c r="B66" t="s">
         <v>97</v>
       </c>
-      <c r="E60" t="s">
+      <c r="K66" t="s">
         <v>10</v>
       </c>
-      <c r="F60" s="5">
+      <c r="L66" s="5">
         <v>0</v>
       </c>
-      <c r="H60" t="s">
+      <c r="N66" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
         <v>17</v>
       </c>
-      <c r="D61" t="s">
+      <c r="B67" t="s">
         <v>97</v>
       </c>
-      <c r="E61" t="s">
+      <c r="K67" t="s">
         <v>11</v>
       </c>
-      <c r="F61" s="5">
+      <c r="L67" s="5">
         <v>20</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
         <v>17</v>
       </c>
-      <c r="D62" t="s">
+      <c r="B68" t="s">
         <v>97</v>
       </c>
-      <c r="E62" t="s">
+      <c r="K68" t="s">
         <v>12</v>
       </c>
-      <c r="F62" s="5">
+      <c r="L68" s="5">
         <v>35</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
         <v>17</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B69" t="s">
+        <v>97</v>
+      </c>
+      <c r="D69" t="s">
         <v>9</v>
       </c>
-      <c r="D63" t="s">
+      <c r="K69" t="s">
+        <v>10</v>
+      </c>
+      <c r="L69" s="9">
+        <f t="shared" ref="L69:L77" si="2">L66</f>
+        <v>0</v>
+      </c>
+      <c r="N69" s="9" t="str">
+        <f>N66</f>
+        <v>Korn, norrland</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>17</v>
+      </c>
+      <c r="B70" t="s">
         <v>97</v>
       </c>
-      <c r="E63" t="s">
-        <v>10</v>
-      </c>
-      <c r="F63" s="9">
-        <f t="shared" ref="F63:F71" si="2">F60</f>
-        <v>0</v>
-      </c>
-      <c r="H63" s="9" t="str">
-        <f>H60</f>
-        <v>Korn, norrland</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>17</v>
-      </c>
-      <c r="B64" t="s">
+      <c r="D70" t="s">
         <v>9</v>
       </c>
-      <c r="D64" t="s">
-        <v>97</v>
-      </c>
-      <c r="E64" t="s">
+      <c r="K70" t="s">
         <v>11</v>
       </c>
-      <c r="F64" s="9">
+      <c r="L70" s="9">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
         <v>17</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B71" t="s">
+        <v>97</v>
+      </c>
+      <c r="D71" t="s">
         <v>9</v>
       </c>
-      <c r="D65" t="s">
-        <v>97</v>
-      </c>
-      <c r="E65" t="s">
+      <c r="K71" t="s">
         <v>12</v>
       </c>
-      <c r="F65" s="9">
+      <c r="L71" s="9">
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
         <v>17</v>
       </c>
-      <c r="D66" t="s">
+      <c r="B72" t="s">
         <v>98</v>
       </c>
-      <c r="E66" t="s">
+      <c r="K72" t="s">
         <v>10</v>
       </c>
-      <c r="F66" s="9">
+      <c r="L72" s="9">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H66" s="9" t="str">
-        <f>H63</f>
+      <c r="N72" s="9" t="str">
+        <f>N69</f>
         <v>Korn, norrland</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
         <v>17</v>
       </c>
-      <c r="D67" t="s">
+      <c r="B73" t="s">
         <v>98</v>
       </c>
-      <c r="E67" t="s">
+      <c r="K73" t="s">
         <v>11</v>
       </c>
-      <c r="F67" s="9">
+      <c r="L73" s="9">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
         <v>17</v>
       </c>
-      <c r="D68" t="s">
+      <c r="B74" t="s">
         <v>98</v>
       </c>
-      <c r="E68" t="s">
+      <c r="K74" t="s">
         <v>12</v>
       </c>
-      <c r="F68" s="9">
+      <c r="L74" s="9">
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
         <v>17</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B75" t="s">
+        <v>98</v>
+      </c>
+      <c r="D75" t="s">
         <v>9</v>
       </c>
-      <c r="D69" t="s">
-        <v>98</v>
-      </c>
-      <c r="E69" t="s">
+      <c r="K75" t="s">
         <v>10</v>
       </c>
-      <c r="F69" s="9">
+      <c r="L75" s="9">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H69" s="9" t="str">
-        <f>H66</f>
+      <c r="N75" s="9" t="str">
+        <f>N72</f>
         <v>Korn, norrland</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
         <v>17</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B76" t="s">
+        <v>98</v>
+      </c>
+      <c r="D76" t="s">
         <v>9</v>
       </c>
-      <c r="D70" t="s">
-        <v>98</v>
-      </c>
-      <c r="E70" t="s">
+      <c r="K76" t="s">
         <v>11</v>
       </c>
-      <c r="F70" s="9">
+      <c r="L76" s="9">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
         <v>17</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B77" t="s">
+        <v>98</v>
+      </c>
+      <c r="D77" t="s">
         <v>9</v>
       </c>
-      <c r="D71" t="s">
-        <v>98</v>
-      </c>
-      <c r="E71" t="s">
+      <c r="K77" t="s">
         <v>12</v>
       </c>
-      <c r="F71" s="9">
+      <c r="L77" s="9">
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>21</v>
-      </c>
-      <c r="E72" t="s">
-        <v>10</v>
-      </c>
-      <c r="F72">
-        <v>-1.0713999999999999</v>
-      </c>
-      <c r="H72" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>21</v>
-      </c>
-      <c r="E73" t="s">
-        <v>11</v>
-      </c>
-      <c r="F73">
-        <v>23.928999999999998</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>21</v>
-      </c>
-      <c r="E74" t="s">
-        <v>12</v>
-      </c>
-      <c r="F74">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>21</v>
-      </c>
-      <c r="D75" t="s">
-        <v>96</v>
-      </c>
-      <c r="E75" t="s">
-        <v>10</v>
-      </c>
-      <c r="F75">
-        <v>-1.25</v>
-      </c>
-      <c r="H75" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>21</v>
-      </c>
-      <c r="D76" t="s">
-        <v>96</v>
-      </c>
-      <c r="E76" t="s">
-        <v>11</v>
-      </c>
-      <c r="F76">
-        <v>25.25</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>21</v>
-      </c>
-      <c r="D77" t="s">
-        <v>96</v>
-      </c>
-      <c r="E77" t="s">
-        <v>12</v>
-      </c>
-      <c r="F77">
-        <v>9.75</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>21</v>
       </c>
-      <c r="D78" t="s">
-        <v>95</v>
-      </c>
-      <c r="E78" t="s">
+      <c r="K78" t="s">
         <v>10</v>
       </c>
-      <c r="F78" s="9">
-        <f>F75</f>
-        <v>-1.25</v>
-      </c>
-      <c r="H78" s="9" t="str">
-        <f>H75</f>
-        <v>Havre södra götaland</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="L78">
+        <v>-1.0713999999999999</v>
+      </c>
+      <c r="N78" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>21</v>
       </c>
-      <c r="D79" t="s">
-        <v>95</v>
-      </c>
-      <c r="E79" t="s">
+      <c r="K79" t="s">
         <v>11</v>
       </c>
-      <c r="F79" s="9">
-        <f>F76</f>
-        <v>25.25</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="L79">
+        <v>23.928999999999998</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>21</v>
       </c>
-      <c r="D80" t="s">
+      <c r="K80" t="s">
+        <v>12</v>
+      </c>
+      <c r="L80">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>21</v>
+      </c>
+      <c r="B81" t="s">
+        <v>96</v>
+      </c>
+      <c r="K81" t="s">
+        <v>10</v>
+      </c>
+      <c r="L81">
+        <v>-1.25</v>
+      </c>
+      <c r="N81" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>21</v>
+      </c>
+      <c r="B82" t="s">
+        <v>96</v>
+      </c>
+      <c r="K82" t="s">
+        <v>11</v>
+      </c>
+      <c r="L82">
+        <v>25.25</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>21</v>
+      </c>
+      <c r="B83" t="s">
+        <v>96</v>
+      </c>
+      <c r="K83" t="s">
+        <v>12</v>
+      </c>
+      <c r="L83">
+        <v>9.75</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>21</v>
+      </c>
+      <c r="B84" t="s">
         <v>95</v>
       </c>
-      <c r="E80" t="s">
+      <c r="K84" t="s">
+        <v>10</v>
+      </c>
+      <c r="L84" s="9">
+        <f>L81</f>
+        <v>-1.25</v>
+      </c>
+      <c r="N84" s="9" t="str">
+        <f>N81</f>
+        <v>Havre södra götaland</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>21</v>
+      </c>
+      <c r="B85" t="s">
+        <v>95</v>
+      </c>
+      <c r="K85" t="s">
+        <v>11</v>
+      </c>
+      <c r="L85" s="9">
+        <f>L82</f>
+        <v>25.25</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>21</v>
+      </c>
+      <c r="B86" t="s">
+        <v>95</v>
+      </c>
+      <c r="K86" t="s">
         <v>12</v>
       </c>
-      <c r="F80" s="9">
-        <f>F77</f>
+      <c r="L86" s="9">
+        <f>L83</f>
         <v>9.75</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>25</v>
-      </c>
-      <c r="E81" t="s">
-        <v>11</v>
-      </c>
-      <c r="F81" s="9">
-        <f>F34</f>
-        <v>16.856999999999999</v>
-      </c>
-      <c r="H81" s="9" t="str">
-        <f>H34</f>
-        <v>Rågvete/höstkorn, norra  götaland och svealand</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>25</v>
-      </c>
-      <c r="E82" t="s">
-        <v>12</v>
-      </c>
-      <c r="F82" s="9">
-        <f>F35</f>
-        <v>59.143000000000001</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>25</v>
-      </c>
-      <c r="D83" t="s">
-        <v>96</v>
-      </c>
-      <c r="E83" t="s">
-        <v>10</v>
-      </c>
-      <c r="F83" s="9">
-        <f>F39</f>
-        <v>-0.71430000000000005</v>
-      </c>
-      <c r="H83" s="9" t="str">
-        <f>H39</f>
-        <v>Rågvete/höstkorn, södra götaland</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>25</v>
-      </c>
-      <c r="D84" t="s">
-        <v>96</v>
-      </c>
-      <c r="E84" t="s">
-        <v>11</v>
-      </c>
-      <c r="F84" s="9">
-        <f>F40</f>
-        <v>23.143000000000001</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>25</v>
-      </c>
-      <c r="D85" t="s">
-        <v>96</v>
-      </c>
-      <c r="E85" t="s">
-        <v>12</v>
-      </c>
-      <c r="F85" s="9">
-        <f>F41</f>
-        <v>37.570999999999998</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>25</v>
-      </c>
-      <c r="D86" t="s">
-        <v>95</v>
-      </c>
-      <c r="E86" t="s">
-        <v>10</v>
-      </c>
-      <c r="F86" s="9">
-        <f>F39</f>
-        <v>-0.71430000000000005</v>
-      </c>
-      <c r="H86" s="9" t="str">
-        <f>H39</f>
-        <v>Rågvete/höstkorn, södra götaland</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>25</v>
       </c>
-      <c r="D87" t="s">
-        <v>95</v>
-      </c>
-      <c r="E87" t="s">
+      <c r="K87" t="s">
         <v>11</v>
       </c>
-      <c r="F87" s="9">
-        <f>F40</f>
-        <v>23.143000000000001</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="L87" s="9">
+        <f>L40</f>
+        <v>16.856999999999999</v>
+      </c>
+      <c r="N87" s="9" t="str">
+        <f>N40</f>
+        <v>Rågvete/höstkorn, norra  götaland och svealand</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>25</v>
       </c>
-      <c r="D88" t="s">
+      <c r="K88" t="s">
+        <v>12</v>
+      </c>
+      <c r="L88" s="9">
+        <f>L41</f>
+        <v>59.143000000000001</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>25</v>
+      </c>
+      <c r="B89" t="s">
+        <v>96</v>
+      </c>
+      <c r="K89" t="s">
+        <v>10</v>
+      </c>
+      <c r="L89" s="9">
+        <f>L45</f>
+        <v>-0.71430000000000005</v>
+      </c>
+      <c r="N89" s="9" t="str">
+        <f>N45</f>
+        <v>Rågvete/höstkorn, södra götaland</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>25</v>
+      </c>
+      <c r="B90" t="s">
+        <v>96</v>
+      </c>
+      <c r="K90" t="s">
+        <v>11</v>
+      </c>
+      <c r="L90" s="9">
+        <f>L46</f>
+        <v>23.143000000000001</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>25</v>
+      </c>
+      <c r="B91" t="s">
+        <v>96</v>
+      </c>
+      <c r="K91" t="s">
+        <v>12</v>
+      </c>
+      <c r="L91" s="9">
+        <f>L47</f>
+        <v>37.570999999999998</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>25</v>
+      </c>
+      <c r="B92" t="s">
         <v>95</v>
       </c>
-      <c r="E88" t="s">
+      <c r="K92" t="s">
+        <v>10</v>
+      </c>
+      <c r="L92" s="9">
+        <f>L45</f>
+        <v>-0.71430000000000005</v>
+      </c>
+      <c r="N92" s="9" t="str">
+        <f>N45</f>
+        <v>Rågvete/höstkorn, södra götaland</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>25</v>
+      </c>
+      <c r="B93" t="s">
+        <v>95</v>
+      </c>
+      <c r="K93" t="s">
+        <v>11</v>
+      </c>
+      <c r="L93" s="9">
+        <f>L46</f>
+        <v>23.143000000000001</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>25</v>
+      </c>
+      <c r="B94" t="s">
+        <v>95</v>
+      </c>
+      <c r="K94" t="s">
         <v>12</v>
       </c>
-      <c r="F88" s="9">
-        <f>F41</f>
+      <c r="L94" s="9">
+        <f>L47</f>
         <v>37.570999999999998</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>24</v>
-      </c>
-      <c r="E89" t="s">
-        <v>11</v>
-      </c>
-      <c r="F89" s="9">
-        <f>F34</f>
-        <v>16.856999999999999</v>
-      </c>
-      <c r="H89" s="9" t="str">
-        <f>H34</f>
-        <v>Rågvete/höstkorn, norra  götaland och svealand</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>24</v>
-      </c>
-      <c r="E90" t="s">
-        <v>12</v>
-      </c>
-      <c r="F90" s="9">
-        <f>F35</f>
-        <v>59.143000000000001</v>
-      </c>
-      <c r="H90" s="9"/>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>24</v>
-      </c>
-      <c r="D91" t="s">
-        <v>96</v>
-      </c>
-      <c r="E91" t="s">
-        <v>10</v>
-      </c>
-      <c r="F91" s="9">
-        <f>F39</f>
-        <v>-0.71430000000000005</v>
-      </c>
-      <c r="H91" s="9" t="str">
-        <f>H39</f>
-        <v>Rågvete/höstkorn, södra götaland</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>24</v>
-      </c>
-      <c r="D92" t="s">
-        <v>96</v>
-      </c>
-      <c r="E92" t="s">
-        <v>11</v>
-      </c>
-      <c r="F92" s="9">
-        <f>F40</f>
-        <v>23.143000000000001</v>
-      </c>
-      <c r="H92" s="9"/>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>24</v>
-      </c>
-      <c r="D93" t="s">
-        <v>96</v>
-      </c>
-      <c r="E93" t="s">
-        <v>12</v>
-      </c>
-      <c r="F93" s="9">
-        <f>F41</f>
-        <v>37.570999999999998</v>
-      </c>
-      <c r="H93" s="9"/>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>24</v>
-      </c>
-      <c r="D94" t="s">
-        <v>95</v>
-      </c>
-      <c r="E94" t="s">
-        <v>10</v>
-      </c>
-      <c r="F94" s="9">
-        <f>F39</f>
-        <v>-0.71430000000000005</v>
-      </c>
-      <c r="H94" s="9" t="str">
-        <f>H39</f>
-        <v>Rågvete/höstkorn, södra götaland</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>24</v>
       </c>
-      <c r="D95" t="s">
-        <v>95</v>
-      </c>
-      <c r="E95" t="s">
+      <c r="K95" t="s">
         <v>11</v>
       </c>
-      <c r="F95" s="9">
-        <f>F40</f>
-        <v>23.143000000000001</v>
-      </c>
-      <c r="H95" s="9"/>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="L95" s="9">
+        <f>L40</f>
+        <v>16.856999999999999</v>
+      </c>
+      <c r="N95" s="9" t="str">
+        <f>N40</f>
+        <v>Rågvete/höstkorn, norra  götaland och svealand</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>24</v>
       </c>
-      <c r="D96" t="s">
+      <c r="K96" t="s">
+        <v>12</v>
+      </c>
+      <c r="L96" s="9">
+        <f>L41</f>
+        <v>59.143000000000001</v>
+      </c>
+      <c r="N96" s="9"/>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>24</v>
+      </c>
+      <c r="B97" t="s">
+        <v>96</v>
+      </c>
+      <c r="K97" t="s">
+        <v>10</v>
+      </c>
+      <c r="L97" s="9">
+        <f>L45</f>
+        <v>-0.71430000000000005</v>
+      </c>
+      <c r="N97" s="9" t="str">
+        <f>N45</f>
+        <v>Rågvete/höstkorn, södra götaland</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>24</v>
+      </c>
+      <c r="B98" t="s">
+        <v>96</v>
+      </c>
+      <c r="K98" t="s">
+        <v>11</v>
+      </c>
+      <c r="L98" s="9">
+        <f>L46</f>
+        <v>23.143000000000001</v>
+      </c>
+      <c r="N98" s="9"/>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>24</v>
+      </c>
+      <c r="B99" t="s">
+        <v>96</v>
+      </c>
+      <c r="K99" t="s">
+        <v>12</v>
+      </c>
+      <c r="L99" s="9">
+        <f>L47</f>
+        <v>37.570999999999998</v>
+      </c>
+      <c r="N99" s="9"/>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>24</v>
+      </c>
+      <c r="B100" t="s">
         <v>95</v>
       </c>
-      <c r="E96" t="s">
+      <c r="K100" t="s">
+        <v>10</v>
+      </c>
+      <c r="L100" s="9">
+        <f>L45</f>
+        <v>-0.71430000000000005</v>
+      </c>
+      <c r="N100" s="9" t="str">
+        <f>N45</f>
+        <v>Rågvete/höstkorn, södra götaland</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>24</v>
+      </c>
+      <c r="B101" t="s">
+        <v>95</v>
+      </c>
+      <c r="K101" t="s">
+        <v>11</v>
+      </c>
+      <c r="L101" s="9">
+        <f>L46</f>
+        <v>23.143000000000001</v>
+      </c>
+      <c r="N101" s="9"/>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>24</v>
+      </c>
+      <c r="B102" t="s">
+        <v>95</v>
+      </c>
+      <c r="K102" t="s">
         <v>12</v>
       </c>
-      <c r="F96" s="9">
-        <f>F41</f>
+      <c r="L102" s="9">
+        <f>L47</f>
         <v>37.570999999999998</v>
       </c>
-      <c r="H96" s="9"/>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97" s="7" t="s">
+      <c r="N102" s="9"/>
+    </row>
+    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A103" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E97" s="7"/>
-      <c r="F97" s="7"/>
-      <c r="H97" s="7"/>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
+      <c r="E103" s="7"/>
+      <c r="F103" s="7"/>
+      <c r="G103" s="7"/>
+      <c r="H103" s="7"/>
+      <c r="I103" s="7"/>
+      <c r="J103" s="7"/>
+      <c r="K103" s="7"/>
+      <c r="L103" s="7"/>
+      <c r="N103" s="7"/>
+    </row>
+    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
         <v>28</v>
       </c>
-      <c r="E98" t="s">
+      <c r="K104" t="s">
         <v>12</v>
       </c>
-      <c r="F98">
+      <c r="L104">
         <v>50</v>
       </c>
-      <c r="H98" t="s">
+      <c r="N104" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
         <v>30</v>
       </c>
-      <c r="E99" t="s">
+      <c r="K105" t="s">
         <v>12</v>
       </c>
-      <c r="F99">
+      <c r="L105">
         <v>0</v>
       </c>
-      <c r="H99" t="s">
+      <c r="N105" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
         <v>31</v>
       </c>
-      <c r="E100" t="s">
+      <c r="K106" t="s">
         <v>12</v>
       </c>
-      <c r="F100">
+      <c r="L106">
         <v>0</v>
       </c>
-      <c r="H100" t="s">
+      <c r="N106" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
         <v>32</v>
       </c>
-      <c r="E101" t="s">
+      <c r="K107" t="s">
         <v>12</v>
       </c>
-      <c r="F101">
+      <c r="L107">
         <v>0</v>
       </c>
-      <c r="H101" t="s">
+      <c r="N107" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
         <v>33</v>
       </c>
-      <c r="E102" t="s">
+      <c r="K108" t="s">
         <v>12</v>
       </c>
-      <c r="F102">
+      <c r="L108">
         <v>30</v>
       </c>
-      <c r="H102" t="s">
+      <c r="N108" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
         <v>34</v>
       </c>
-      <c r="E103" t="s">
+      <c r="K109" t="s">
         <v>11</v>
       </c>
-      <c r="F103">
+      <c r="L109">
         <v>20</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
         <v>34</v>
       </c>
-      <c r="E104" t="s">
+      <c r="K110" t="s">
         <v>12</v>
       </c>
-      <c r="F104">
+      <c r="L110">
         <v>65</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
         <v>35</v>
       </c>
-      <c r="E105" t="s">
+      <c r="K111" t="s">
         <v>11</v>
       </c>
-      <c r="F105">
+      <c r="L111">
         <v>20</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
         <v>35</v>
       </c>
-      <c r="E106" t="s">
+      <c r="K112" t="s">
         <v>12</v>
       </c>
-      <c r="F106">
+      <c r="L112">
         <v>70</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
         <v>36</v>
       </c>
-      <c r="E107" t="s">
+      <c r="K113" t="s">
         <v>10</v>
       </c>
-      <c r="F107">
+      <c r="L113">
         <v>-2.5000000000000001E-2</v>
       </c>
-      <c r="H107" t="s">
+      <c r="N113" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
         <v>36</v>
       </c>
-      <c r="E108" t="s">
+      <c r="K114" t="s">
         <v>11</v>
       </c>
-      <c r="F108">
+      <c r="L114">
         <v>4.95</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
         <v>36</v>
       </c>
-      <c r="E109" t="s">
+      <c r="K115" t="s">
         <v>12</v>
       </c>
-      <c r="F109">
+      <c r="L115">
         <v>-31.5</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
         <v>37</v>
       </c>
-      <c r="E110" t="s">
+      <c r="K116" t="s">
         <v>10</v>
       </c>
-      <c r="F110" s="9">
-        <f>F107</f>
+      <c r="L116" s="9">
+        <f>L113</f>
         <v>-2.5000000000000001E-2</v>
       </c>
-      <c r="H110" s="9" t="str">
-        <f>H107</f>
+      <c r="N116" s="9" t="str">
+        <f>N113</f>
         <v>Potatis</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
         <v>37</v>
       </c>
-      <c r="E111" t="s">
+      <c r="K117" t="s">
         <v>11</v>
       </c>
-      <c r="F111" s="9">
-        <f t="shared" ref="F111:F112" si="3">F108</f>
+      <c r="L117" s="9">
+        <f t="shared" ref="L117:L118" si="3">L114</f>
         <v>4.95</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
         <v>37</v>
       </c>
-      <c r="E112" t="s">
+      <c r="K118" t="s">
         <v>12</v>
       </c>
-      <c r="F112" s="9">
+      <c r="L118" s="9">
         <f t="shared" si="3"/>
         <v>-31.5</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
         <v>38</v>
       </c>
-      <c r="E113" t="s">
+      <c r="K119" t="s">
         <v>12</v>
       </c>
-      <c r="F113">
+      <c r="L119">
         <v>110</v>
       </c>
-      <c r="H113" t="s">
+      <c r="N119" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A114" s="7" t="s">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A120" s="7" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A115" s="10" t="s">
+      <c r="E120" s="7"/>
+      <c r="F120" s="7"/>
+      <c r="G120" s="7"/>
+      <c r="H120" s="7"/>
+      <c r="I120" s="7"/>
+      <c r="J120" s="7"/>
+    </row>
+    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A121" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="E115" t="s">
+      <c r="E121" s="10"/>
+      <c r="F121" s="10"/>
+      <c r="G121" s="10"/>
+      <c r="H121" s="10"/>
+      <c r="I121" s="10"/>
+      <c r="J121" s="10"/>
+      <c r="K121" t="s">
         <v>10</v>
       </c>
-      <c r="F115">
+      <c r="L121">
         <v>-1.4286000000000001</v>
       </c>
-      <c r="H115" t="s">
+      <c r="N121" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A116" s="10" t="s">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A122" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="E116" t="s">
+      <c r="E122" s="10"/>
+      <c r="F122" s="10"/>
+      <c r="G122" s="10"/>
+      <c r="H122" s="10"/>
+      <c r="I122" s="10"/>
+      <c r="J122" s="10"/>
+      <c r="K122" t="s">
         <v>11</v>
       </c>
-      <c r="F116">
+      <c r="L122">
         <v>40.713999999999999</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A117" s="10" t="s">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A123" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="E117" t="s">
+      <c r="E123" s="10"/>
+      <c r="F123" s="10"/>
+      <c r="G123" s="10"/>
+      <c r="H123" s="10"/>
+      <c r="I123" s="10"/>
+      <c r="J123" s="10"/>
+      <c r="K123" t="s">
         <v>12</v>
       </c>
-      <c r="F117">
+      <c r="L123">
         <v>-74.856999999999999</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A118" s="11" t="s">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A124" s="11" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A119" s="5" t="s">
+      <c r="E124" s="11"/>
+      <c r="F124" s="11"/>
+      <c r="G124" s="11"/>
+      <c r="H124" s="11"/>
+      <c r="I124" s="11"/>
+      <c r="J124" s="11"/>
+    </row>
+    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A125" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="E119" t="s">
+      <c r="E125" s="5"/>
+      <c r="F125" s="5"/>
+      <c r="G125" s="5"/>
+      <c r="H125" s="5"/>
+      <c r="I125" s="5"/>
+      <c r="J125" s="5"/>
+      <c r="K125" t="s">
         <v>12</v>
       </c>
-      <c r="F119">
+      <c r="L125">
         <v>0</v>
       </c>
-      <c r="H119" t="s">
+      <c r="N125" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A120" s="5" t="s">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A126" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B120" s="5"/>
-      <c r="C120" s="5"/>
-      <c r="D120" s="5"/>
-      <c r="E120" s="5" t="s">
+      <c r="B126" s="5"/>
+      <c r="C126" s="5"/>
+      <c r="D126" s="5"/>
+      <c r="E126" s="5"/>
+      <c r="F126" s="5"/>
+      <c r="G126" s="5"/>
+      <c r="H126" s="5"/>
+      <c r="I126" s="5"/>
+      <c r="J126" s="5"/>
+      <c r="K126" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F120" s="5">
+      <c r="L126" s="5">
         <v>-1.7857000000000001</v>
       </c>
-      <c r="H120" s="7"/>
-    </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A121" s="5" t="s">
+      <c r="N126" s="7"/>
+    </row>
+    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A127" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B121" s="5"/>
-      <c r="C121" s="5"/>
-      <c r="D121" s="5"/>
-      <c r="E121" s="5" t="s">
+      <c r="B127" s="5"/>
+      <c r="C127" s="5"/>
+      <c r="D127" s="5"/>
+      <c r="E127" s="5"/>
+      <c r="F127" s="5"/>
+      <c r="G127" s="5"/>
+      <c r="H127" s="5"/>
+      <c r="I127" s="5"/>
+      <c r="J127" s="5"/>
+      <c r="K127" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F121" s="5">
+      <c r="L127" s="5">
         <v>43.570999999999998</v>
       </c>
-      <c r="H121" s="7"/>
-    </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A122" s="5" t="s">
+      <c r="N127" s="7"/>
+    </row>
+    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A128" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B122" s="5"/>
-      <c r="C122" s="5"/>
-      <c r="D122" s="5"/>
-      <c r="E122" s="5" t="s">
+      <c r="B128" s="5"/>
+      <c r="C128" s="5"/>
+      <c r="D128" s="5"/>
+      <c r="E128" s="5"/>
+      <c r="F128" s="5"/>
+      <c r="G128" s="5"/>
+      <c r="H128" s="5"/>
+      <c r="I128" s="5"/>
+      <c r="J128" s="5"/>
+      <c r="K128" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F122" s="5">
+      <c r="L128" s="5">
         <v>-112.5</v>
       </c>
-      <c r="H122" s="7"/>
-    </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A123" s="11" t="s">
+      <c r="N128" s="7"/>
+    </row>
+    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A129" s="11" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A124" s="11" t="s">
+      <c r="E129" s="11"/>
+      <c r="F129" s="11"/>
+      <c r="G129" s="11"/>
+      <c r="H129" s="11"/>
+      <c r="I129" s="11"/>
+      <c r="J129" s="11"/>
+    </row>
+    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A130" s="11" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A125" s="10" t="s">
+      <c r="E130" s="11"/>
+      <c r="F130" s="11"/>
+      <c r="G130" s="11"/>
+      <c r="H130" s="11"/>
+      <c r="I130" s="11"/>
+      <c r="J130" s="11"/>
+    </row>
+    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A131" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="E125" t="s">
+      <c r="E131" s="10"/>
+      <c r="F131" s="10"/>
+      <c r="G131" s="10"/>
+      <c r="H131" s="10"/>
+      <c r="I131" s="10"/>
+      <c r="J131" s="10"/>
+      <c r="K131" t="s">
         <v>12</v>
       </c>
-      <c r="F125">
+      <c r="L131">
         <v>0</v>
       </c>
-      <c r="H125" t="s">
+      <c r="N131" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A126" s="10" t="s">
+    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A132" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="E126" t="s">
+      <c r="E132" s="10"/>
+      <c r="F132" s="10"/>
+      <c r="G132" s="10"/>
+      <c r="H132" s="10"/>
+      <c r="I132" s="10"/>
+      <c r="J132" s="10"/>
+      <c r="K132" t="s">
         <v>12</v>
       </c>
-      <c r="F126">
+      <c r="L132">
         <v>0</v>
       </c>
-      <c r="H126" t="s">
+      <c r="N132" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
+    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
         <v>47</v>
       </c>
-      <c r="E127" t="s">
+      <c r="K133" t="s">
         <v>11</v>
       </c>
-      <c r="F127">
+      <c r="L133">
         <v>2.5</v>
       </c>
-      <c r="H127" t="s">
+      <c r="N133" t="s">
         <v>85</v>
       </c>
-      <c r="I127" t="s">
+      <c r="O133" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
+    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
         <v>47</v>
       </c>
-      <c r="E128" t="s">
+      <c r="K134" t="s">
         <v>12</v>
       </c>
-      <c r="F128">
+      <c r="L134">
         <v>25</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
+    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
         <v>48</v>
       </c>
-      <c r="E129" t="s">
+      <c r="K135" t="s">
         <v>11</v>
       </c>
-      <c r="F129">
+      <c r="L135">
         <v>1.3846000000000001</v>
       </c>
-      <c r="H129" t="s">
+      <c r="N135" t="s">
         <v>85</v>
       </c>
-      <c r="I129" t="s">
+      <c r="O135" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
+    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
         <v>48</v>
       </c>
-      <c r="E130" t="s">
+      <c r="K136" t="s">
         <v>12</v>
       </c>
-      <c r="F130">
+      <c r="L136">
         <v>11.538</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A131" s="5" t="s">
+    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A137" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E131" t="s">
+      <c r="E137" s="5"/>
+      <c r="F137" s="5"/>
+      <c r="G137" s="5"/>
+      <c r="H137" s="5"/>
+      <c r="I137" s="5"/>
+      <c r="J137" s="5"/>
+      <c r="K137" t="s">
         <v>11</v>
       </c>
-      <c r="F131" s="9">
-        <f>F129</f>
+      <c r="L137" s="9">
+        <f>L135</f>
         <v>1.3846000000000001</v>
       </c>
-      <c r="H131" s="7" t="s">
+      <c r="N137" s="7" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A132" s="5" t="s">
+    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A138" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E132" t="s">
+      <c r="E138" s="5"/>
+      <c r="F138" s="5"/>
+      <c r="G138" s="5"/>
+      <c r="H138" s="5"/>
+      <c r="I138" s="5"/>
+      <c r="J138" s="5"/>
+      <c r="K138" t="s">
         <v>12</v>
       </c>
-      <c r="F132" s="9">
-        <f>F130</f>
+      <c r="L138" s="9">
+        <f>L136</f>
         <v>11.538</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A133" s="5" t="s">
+    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A139" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E133" t="s">
+      <c r="E139" s="5"/>
+      <c r="F139" s="5"/>
+      <c r="G139" s="5"/>
+      <c r="H139" s="5"/>
+      <c r="I139" s="5"/>
+      <c r="J139" s="5"/>
+      <c r="K139" t="s">
         <v>11</v>
       </c>
-      <c r="F133">
+      <c r="L139">
         <v>3.3332999999999999</v>
       </c>
-      <c r="H133" t="s">
+      <c r="N139" t="s">
         <v>87</v>
       </c>
-      <c r="I133" t="s">
+      <c r="O139" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A134" s="5" t="s">
+    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A140" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E134" t="s">
+      <c r="E140" s="5"/>
+      <c r="F140" s="5"/>
+      <c r="G140" s="5"/>
+      <c r="H140" s="5"/>
+      <c r="I140" s="5"/>
+      <c r="J140" s="5"/>
+      <c r="K140" t="s">
         <v>12</v>
       </c>
-      <c r="F134">
+      <c r="L140">
         <v>33.332999999999998</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A135" s="5" t="s">
+    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A141" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E135" t="s">
+      <c r="E141" s="5"/>
+      <c r="F141" s="5"/>
+      <c r="G141" s="5"/>
+      <c r="H141" s="5"/>
+      <c r="I141" s="5"/>
+      <c r="J141" s="5"/>
+      <c r="K141" t="s">
         <v>11</v>
       </c>
-      <c r="F135">
+      <c r="L141">
         <v>3</v>
       </c>
-      <c r="H135" t="s">
+      <c r="N141" t="s">
         <v>88</v>
       </c>
-      <c r="I135" t="s">
+      <c r="O141" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A136" s="5" t="s">
+    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A142" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E136" t="s">
+      <c r="E142" s="5"/>
+      <c r="F142" s="5"/>
+      <c r="G142" s="5"/>
+      <c r="H142" s="5"/>
+      <c r="I142" s="5"/>
+      <c r="J142" s="5"/>
+      <c r="K142" t="s">
         <v>12</v>
       </c>
-      <c r="F136">
+      <c r="L142">
         <v>90</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A137" s="5" t="s">
+    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A143" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E137" s="5" t="s">
+      <c r="E143" s="5"/>
+      <c r="F143" s="5"/>
+      <c r="G143" s="5"/>
+      <c r="H143" s="5"/>
+      <c r="I143" s="5"/>
+      <c r="J143" s="5"/>
+      <c r="K143" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F137">
+      <c r="L143">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="H137" t="s">
+      <c r="N143" t="s">
         <v>89</v>
       </c>
-      <c r="I137" t="s">
+      <c r="O143" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A138" s="5" t="s">
+    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A144" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E138" t="s">
+      <c r="E144" s="5"/>
+      <c r="F144" s="5"/>
+      <c r="G144" s="5"/>
+      <c r="H144" s="5"/>
+      <c r="I144" s="5"/>
+      <c r="J144" s="5"/>
+      <c r="K144" t="s">
         <v>11</v>
       </c>
-      <c r="F138">
+      <c r="L144">
         <v>1.2583</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A139" s="5" t="s">
+    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A145" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E139" t="s">
+      <c r="E145" s="5"/>
+      <c r="F145" s="5"/>
+      <c r="G145" s="5"/>
+      <c r="H145" s="5"/>
+      <c r="I145" s="5"/>
+      <c r="J145" s="5"/>
+      <c r="K145" t="s">
         <v>12</v>
       </c>
-      <c r="F139">
+      <c r="L145">
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A140" s="5" t="s">
+    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A146" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E140" s="5" t="s">
+      <c r="E146" s="5"/>
+      <c r="F146" s="5"/>
+      <c r="G146" s="5"/>
+      <c r="H146" s="5"/>
+      <c r="I146" s="5"/>
+      <c r="J146" s="5"/>
+      <c r="K146" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F140" s="9">
-        <f>F137</f>
+      <c r="L146" s="9">
+        <f>L143</f>
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="H140" s="9" t="str">
-        <f>H137</f>
+      <c r="N146" s="9" t="str">
+        <f>N143</f>
         <v xml:space="preserve">yield in fresh weight 5% DM </v>
       </c>
-      <c r="I140" s="9" t="str">
-        <f>I137</f>
+      <c r="O146" s="9" t="str">
+        <f>O143</f>
         <v>Yara (2018)</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A141" s="5" t="s">
+    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A147" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E141" t="s">
+      <c r="E147" s="5"/>
+      <c r="F147" s="5"/>
+      <c r="G147" s="5"/>
+      <c r="H147" s="5"/>
+      <c r="I147" s="5"/>
+      <c r="J147" s="5"/>
+      <c r="K147" t="s">
         <v>11</v>
       </c>
-      <c r="F141" s="9">
-        <f>F138</f>
+      <c r="L147" s="9">
+        <f>L144</f>
         <v>1.2583</v>
       </c>
-      <c r="G141" s="9"/>
-      <c r="H141" s="9"/>
-      <c r="I141" s="9"/>
-    </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A142" s="5" t="s">
+      <c r="M147" s="9"/>
+      <c r="N147" s="9"/>
+      <c r="O147" s="9"/>
+    </row>
+    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A148" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E142" t="s">
+      <c r="E148" s="5"/>
+      <c r="F148" s="5"/>
+      <c r="G148" s="5"/>
+      <c r="H148" s="5"/>
+      <c r="I148" s="5"/>
+      <c r="J148" s="5"/>
+      <c r="K148" t="s">
         <v>12</v>
       </c>
-      <c r="F142" s="9">
-        <f>F139</f>
+      <c r="L148" s="9">
+        <f>L145</f>
         <v>0</v>
       </c>
-      <c r="G142" s="9"/>
-      <c r="H142" s="9"/>
-      <c r="I142" s="9"/>
-    </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A143" s="5" t="s">
+      <c r="M148" s="9"/>
+      <c r="N148" s="9"/>
+      <c r="O148" s="9"/>
+    </row>
+    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A149" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E143" t="s">
+      <c r="E149" s="5"/>
+      <c r="F149" s="5"/>
+      <c r="G149" s="5"/>
+      <c r="H149" s="5"/>
+      <c r="I149" s="5"/>
+      <c r="J149" s="5"/>
+      <c r="K149" t="s">
         <v>11</v>
       </c>
-      <c r="F143" s="9">
-        <f>F133</f>
+      <c r="L149" s="9">
+        <f>L139</f>
         <v>3.3332999999999999</v>
       </c>
-      <c r="H143" s="7" t="s">
+      <c r="N149" s="7" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A144" s="5" t="s">
+    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A150" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E144" t="s">
+      <c r="E150" s="5"/>
+      <c r="F150" s="5"/>
+      <c r="G150" s="5"/>
+      <c r="H150" s="5"/>
+      <c r="I150" s="5"/>
+      <c r="J150" s="5"/>
+      <c r="K150" t="s">
         <v>12</v>
       </c>
-      <c r="F144" s="9">
-        <f>F134</f>
+      <c r="L150" s="9">
+        <f>L140</f>
         <v>33.332999999999998</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A145" s="7" t="s">
+    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A151" s="7" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A146" s="5" t="s">
+      <c r="E151" s="7"/>
+      <c r="F151" s="7"/>
+      <c r="G151" s="7"/>
+      <c r="H151" s="7"/>
+      <c r="I151" s="7"/>
+      <c r="J151" s="7"/>
+    </row>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A152" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E146" t="s">
+      <c r="E152" s="5"/>
+      <c r="F152" s="5"/>
+      <c r="G152" s="5"/>
+      <c r="H152" s="5"/>
+      <c r="I152" s="5"/>
+      <c r="J152" s="5"/>
+      <c r="K152" t="s">
         <v>12</v>
       </c>
-      <c r="F146">
+      <c r="L152">
         <v>65</v>
       </c>
-      <c r="H146" t="s">
+      <c r="N152" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A147" s="7" t="s">
+    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A153" s="7" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A148" s="5" t="s">
+      <c r="E153" s="7"/>
+      <c r="F153" s="7"/>
+      <c r="G153" s="7"/>
+      <c r="H153" s="7"/>
+      <c r="I153" s="7"/>
+      <c r="J153" s="7"/>
+    </row>
+    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A154" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E148" t="s">
+      <c r="E154" s="5"/>
+      <c r="F154" s="5"/>
+      <c r="G154" s="5"/>
+      <c r="H154" s="5"/>
+      <c r="I154" s="5"/>
+      <c r="J154" s="5"/>
+      <c r="K154" t="s">
         <v>12</v>
       </c>
-      <c r="F148">
+      <c r="L154">
         <v>65</v>
       </c>
-      <c r="H148" t="s">
+      <c r="N154" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A149" s="5" t="s">
+    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A155" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E149" t="s">
+      <c r="E155" s="5"/>
+      <c r="F155" s="5"/>
+      <c r="G155" s="5"/>
+      <c r="H155" s="5"/>
+      <c r="I155" s="5"/>
+      <c r="J155" s="5"/>
+      <c r="K155" t="s">
         <v>12</v>
       </c>
-      <c r="F149">
+      <c r="L155">
         <v>100</v>
       </c>
-      <c r="H149" t="s">
+      <c r="N155" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A150" s="5" t="s">
+    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A156" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E150" t="s">
+      <c r="E156" s="5"/>
+      <c r="F156" s="5"/>
+      <c r="G156" s="5"/>
+      <c r="H156" s="5"/>
+      <c r="I156" s="5"/>
+      <c r="J156" s="5"/>
+      <c r="K156" t="s">
         <v>12</v>
       </c>
-      <c r="F150">
+      <c r="L156">
         <v>110</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A151" s="5" t="s">
+    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A157" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="E151" t="s">
+      <c r="E157" s="5"/>
+      <c r="F157" s="5"/>
+      <c r="G157" s="5"/>
+      <c r="H157" s="5"/>
+      <c r="I157" s="5"/>
+      <c r="J157" s="5"/>
+      <c r="K157" t="s">
         <v>12</v>
       </c>
-      <c r="F151" s="9">
-        <f>F149</f>
+      <c r="L157" s="9">
+        <f>L155</f>
         <v>100</v>
       </c>
-      <c r="H151" s="7" t="s">
+      <c r="N157" s="7" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A152" s="7" t="s">
+    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A158" s="7" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A153" s="7" t="s">
+      <c r="E158" s="7"/>
+      <c r="F158" s="7"/>
+      <c r="G158" s="7"/>
+      <c r="H158" s="7"/>
+      <c r="I158" s="7"/>
+      <c r="J158" s="7"/>
+    </row>
+    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A159" s="7" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A154" s="7" t="s">
+      <c r="E159" s="7"/>
+      <c r="F159" s="7"/>
+      <c r="G159" s="7"/>
+      <c r="H159" s="7"/>
+      <c r="I159" s="7"/>
+      <c r="J159" s="7"/>
+    </row>
+    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A160" s="7" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A155" s="7" t="s">
+      <c r="E160" s="7"/>
+      <c r="F160" s="7"/>
+      <c r="G160" s="7"/>
+      <c r="H160" s="7"/>
+      <c r="I160" s="7"/>
+      <c r="J160" s="7"/>
+    </row>
+    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A161" s="7" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A156" s="7" t="s">
+      <c r="E161" s="7"/>
+      <c r="F161" s="7"/>
+      <c r="G161" s="7"/>
+      <c r="H161" s="7"/>
+      <c r="I161" s="7"/>
+      <c r="J161" s="7"/>
+    </row>
+    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A162" s="7" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A157" s="7" t="s">
+      <c r="E162" s="7"/>
+      <c r="F162" s="7"/>
+      <c r="G162" s="7"/>
+      <c r="H162" s="7"/>
+      <c r="I162" s="7"/>
+      <c r="J162" s="7"/>
+    </row>
+    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A163" s="7" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A158" s="7" t="s">
+      <c r="E163" s="7"/>
+      <c r="F163" s="7"/>
+      <c r="G163" s="7"/>
+      <c r="H163" s="7"/>
+      <c r="I163" s="7"/>
+      <c r="J163" s="7"/>
+    </row>
+    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A164" s="7" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A159" s="5" t="s">
+      <c r="E164" s="7"/>
+      <c r="F164" s="7"/>
+      <c r="G164" s="7"/>
+      <c r="H164" s="7"/>
+      <c r="I164" s="7"/>
+      <c r="J164" s="7"/>
+    </row>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A165" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E159" t="s">
+      <c r="E165" s="5"/>
+      <c r="F165" s="5"/>
+      <c r="G165" s="5"/>
+      <c r="H165" s="5"/>
+      <c r="I165" s="5"/>
+      <c r="J165" s="5"/>
+      <c r="K165" t="s">
         <v>12</v>
       </c>
-      <c r="F159">
+      <c r="L165">
         <v>0</v>
       </c>
-      <c r="H159" t="s">
+      <c r="N165" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A160" s="7" t="s">
+    <row r="166" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A166" s="7" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A161" s="7" t="s">
+      <c r="E166" s="7"/>
+      <c r="F166" s="7"/>
+      <c r="G166" s="7"/>
+      <c r="H166" s="7"/>
+      <c r="I166" s="7"/>
+      <c r="J166" s="7"/>
+    </row>
+    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A167" s="7" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A162" s="5" t="s">
+      <c r="E167" s="7"/>
+      <c r="F167" s="7"/>
+      <c r="G167" s="7"/>
+      <c r="H167" s="7"/>
+      <c r="I167" s="7"/>
+      <c r="J167" s="7"/>
+    </row>
+    <row r="168" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A168" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E162" t="s">
+      <c r="E168" s="5"/>
+      <c r="F168" s="5"/>
+      <c r="G168" s="5"/>
+      <c r="H168" s="5"/>
+      <c r="I168" s="5"/>
+      <c r="J168" s="5"/>
+      <c r="K168" t="s">
         <v>12</v>
       </c>
-      <c r="F162">
+      <c r="L168">
         <v>0</v>
       </c>
-      <c r="H162" t="s">
+      <c r="N168" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A164" s="2" t="s">
+    <row r="170" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A170" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B164" s="2"/>
-      <c r="C164" s="2"/>
-      <c r="D164" s="2"/>
-      <c r="E164" s="2"/>
-      <c r="F164" s="2"/>
-      <c r="G164" s="2"/>
-      <c r="H164" s="3"/>
-      <c r="I164" s="3"/>
-    </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E165" s="6" t="s">
+      <c r="B170" s="2"/>
+      <c r="C170" s="2"/>
+      <c r="D170" s="2"/>
+      <c r="E170" s="2"/>
+      <c r="F170" s="2"/>
+      <c r="G170" s="2"/>
+      <c r="H170" s="2"/>
+      <c r="I170" s="2"/>
+      <c r="J170" s="2"/>
+      <c r="K170" s="2"/>
+      <c r="L170" s="2"/>
+      <c r="M170" s="2"/>
+      <c r="N170" s="3"/>
+      <c r="O170" s="3"/>
+    </row>
+    <row r="171" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="K171" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F165" s="6">
+      <c r="L171" s="6">
         <v>0</v>
       </c>
-      <c r="G165" s="6"/>
-      <c r="H165" s="6" t="s">
+      <c r="M171" s="6"/>
+      <c r="N171" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E166" s="6" t="s">
+    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="K172" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F166" s="6">
+      <c r="L172" s="6">
         <v>1</v>
       </c>
-      <c r="G166" s="6"/>
-      <c r="H166" s="6" t="s">
+      <c r="M172" s="6"/>
+      <c r="N172" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A167" t="s">
+    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
         <v>7</v>
       </c>
-      <c r="E167" t="s">
+      <c r="K173" t="s">
         <v>13</v>
       </c>
-      <c r="F167">
+      <c r="L173">
         <v>-0.32340000000000002</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A168" t="s">
+    <row r="174" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
         <v>7</v>
       </c>
-      <c r="E168" t="s">
+      <c r="K174" t="s">
         <v>14</v>
       </c>
-      <c r="F168">
+      <c r="L174">
         <v>0.97240000000000004</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A169" t="s">
+    <row r="175" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
         <v>16</v>
       </c>
-      <c r="E169" t="s">
+      <c r="K175" t="s">
         <v>13</v>
       </c>
-      <c r="F169">
+      <c r="L175">
         <v>-0.32500000000000001</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A170" t="s">
+    <row r="176" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
         <v>16</v>
       </c>
-      <c r="E170" t="s">
+      <c r="K176" t="s">
         <v>14</v>
       </c>
-      <c r="F170">
+      <c r="L176">
         <v>0.81369999999999998</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A171" t="s">
+    <row r="177" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
         <v>27</v>
       </c>
-      <c r="E171" t="s">
+      <c r="K177" t="s">
         <v>13</v>
       </c>
-      <c r="F171">
+      <c r="L177">
         <v>-0.58699999999999997</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A172" t="s">
+    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
         <v>27</v>
       </c>
-      <c r="E172" t="s">
+      <c r="K178" t="s">
         <v>14</v>
       </c>
-      <c r="F172">
+      <c r="L178">
         <v>0.82350000000000001</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A173" t="s">
+    <row r="179" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
         <v>23</v>
       </c>
-      <c r="E173" t="s">
+      <c r="K179" t="s">
         <v>13</v>
       </c>
-      <c r="F173">
+      <c r="L179">
         <v>-0.35070000000000001</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A174" t="s">
+    <row r="180" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
         <v>23</v>
       </c>
-      <c r="E174" t="s">
+      <c r="K180" t="s">
         <v>14</v>
       </c>
-      <c r="F174">
+      <c r="L180">
         <v>0.9234</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A175" t="s">
+    <row r="181" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
         <v>17</v>
       </c>
-      <c r="E175" t="s">
+      <c r="K181" t="s">
         <v>13</v>
       </c>
-      <c r="F175">
+      <c r="L181">
         <v>-0.41710000000000003</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A176" t="s">
+    <row r="182" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
         <v>17</v>
       </c>
-      <c r="E176" t="s">
+      <c r="K182" t="s">
         <v>14</v>
       </c>
-      <c r="F176">
+      <c r="L182">
         <v>0.91610000000000003</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A177" t="s">
+    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
         <v>21</v>
       </c>
-      <c r="E177" t="s">
+      <c r="K183" t="s">
         <v>13</v>
       </c>
-      <c r="F177">
+      <c r="L183">
         <v>-0.74150000000000005</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A178" t="s">
+    <row r="184" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
         <v>21</v>
       </c>
-      <c r="E178" t="s">
+      <c r="K184" t="s">
         <v>14</v>
       </c>
-      <c r="F178">
+      <c r="L184">
         <v>0.96550000000000002</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A179" t="s">
+    <row r="185" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
         <v>25</v>
       </c>
-      <c r="E179" t="s">
+      <c r="K185" t="s">
         <v>13</v>
       </c>
-      <c r="F179" s="9">
-        <f>F181</f>
+      <c r="L185" s="9">
+        <f>L187</f>
         <v>-0.58699999999999997</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A180" t="s">
+    <row r="186" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
         <v>25</v>
       </c>
-      <c r="E180" t="s">
+      <c r="K186" t="s">
         <v>14</v>
       </c>
-      <c r="F180" s="9">
-        <f>F182</f>
+      <c r="L186" s="9">
+        <f>L188</f>
         <v>0.82350000000000001</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A181" t="s">
+    <row r="187" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
         <v>24</v>
       </c>
-      <c r="E181" t="s">
+      <c r="K187" t="s">
         <v>13</v>
       </c>
-      <c r="F181">
+      <c r="L187">
         <v>-0.58699999999999997</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A182" t="s">
+    <row r="188" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
         <v>24</v>
       </c>
-      <c r="E182" t="s">
+      <c r="K188" t="s">
         <v>14</v>
       </c>
-      <c r="F182">
+      <c r="L188">
         <v>0.82350000000000001</v>
       </c>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A183" s="7" t="s">
+    <row r="189" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A189" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="F183" s="9"/>
-      <c r="H183" s="7"/>
-    </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A184" s="5" t="s">
+      <c r="E189" s="7"/>
+      <c r="F189" s="7"/>
+      <c r="G189" s="7"/>
+      <c r="H189" s="7"/>
+      <c r="I189" s="7"/>
+      <c r="J189" s="7"/>
+      <c r="L189" s="9"/>
+      <c r="N189" s="7"/>
+    </row>
+    <row r="190" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A190" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E184" t="s">
+      <c r="E190" s="5"/>
+      <c r="F190" s="5"/>
+      <c r="G190" s="5"/>
+      <c r="H190" s="5"/>
+      <c r="I190" s="5"/>
+      <c r="J190" s="5"/>
+      <c r="K190" t="s">
         <v>14</v>
       </c>
-      <c r="F184" s="5">
+      <c r="L190" s="5">
         <v>1</v>
       </c>
-      <c r="G184" s="5"/>
-      <c r="H184" s="5" t="s">
+      <c r="M190" s="5"/>
+      <c r="N190" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A185" t="s">
+    <row r="191" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
         <v>30</v>
       </c>
-      <c r="E185" t="s">
+      <c r="K191" t="s">
         <v>14</v>
       </c>
-      <c r="F185">
+      <c r="L191">
         <v>1</v>
       </c>
-      <c r="H185" s="5" t="s">
+      <c r="N191" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A186" t="s">
+    <row r="192" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
         <v>31</v>
       </c>
-      <c r="E186" t="s">
+      <c r="K192" t="s">
         <v>14</v>
       </c>
-      <c r="F186">
+      <c r="L192">
         <v>1</v>
       </c>
-      <c r="H186" s="5" t="s">
+      <c r="N192" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A187" t="s">
+    <row r="193" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
         <v>32</v>
       </c>
-      <c r="E187" t="s">
+      <c r="K193" t="s">
         <v>14</v>
       </c>
-      <c r="F187">
+      <c r="L193">
         <v>1</v>
       </c>
-      <c r="H187" s="5" t="s">
+      <c r="N193" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A188" t="s">
+    <row r="194" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
         <v>33</v>
       </c>
-      <c r="E188" t="s">
+      <c r="K194" t="s">
         <v>14</v>
       </c>
-      <c r="F188">
+      <c r="L194">
         <v>1</v>
       </c>
-      <c r="H188" s="5" t="s">
+      <c r="N194" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A189" t="s">
+    <row r="195" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
         <v>34</v>
       </c>
-      <c r="E189" t="s">
+      <c r="K195" t="s">
         <v>13</v>
       </c>
-      <c r="F189">
+      <c r="L195">
         <v>-9.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A190" t="s">
+    <row r="196" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
         <v>34</v>
       </c>
-      <c r="E190" t="s">
+      <c r="K196" t="s">
         <v>14</v>
       </c>
-      <c r="F190">
+      <c r="L196">
         <v>1.2939000000000001</v>
       </c>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A191" t="s">
+    <row r="197" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
         <v>35</v>
       </c>
-      <c r="E191" t="s">
+      <c r="K197" t="s">
         <v>14</v>
       </c>
-      <c r="F191">
+      <c r="L197">
         <v>0.94</v>
       </c>
-      <c r="H191" s="5" t="s">
+      <c r="N197" s="5" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A192" t="s">
+    <row r="198" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
         <v>36</v>
       </c>
-      <c r="E192" t="s">
+      <c r="K198" t="s">
         <v>14</v>
       </c>
-      <c r="F192">
+      <c r="L198">
         <v>1</v>
       </c>
-      <c r="H192" s="5" t="s">
+      <c r="N198" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A193" t="s">
+    <row r="199" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
         <v>37</v>
       </c>
-      <c r="E193" t="s">
+      <c r="K199" t="s">
         <v>14</v>
       </c>
-      <c r="F193">
+      <c r="L199">
         <v>1</v>
       </c>
-      <c r="H193" s="5" t="s">
+      <c r="N199" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A194" t="s">
+    <row r="200" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
         <v>38</v>
       </c>
-      <c r="E194" t="s">
+      <c r="K200" t="s">
         <v>14</v>
       </c>
-      <c r="F194">
+      <c r="L200">
         <v>1</v>
       </c>
-      <c r="H194" s="5" t="s">
+      <c r="N200" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A195" s="7" t="s">
+    <row r="201" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A201" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="L195" s="4"/>
-    </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A196" s="10" t="s">
+      <c r="E201" s="7"/>
+      <c r="F201" s="7"/>
+      <c r="G201" s="7"/>
+      <c r="H201" s="7"/>
+      <c r="I201" s="7"/>
+      <c r="J201" s="7"/>
+      <c r="R201" s="4"/>
+    </row>
+    <row r="202" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A202" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="E196" t="s">
+      <c r="E202" s="10"/>
+      <c r="F202" s="10"/>
+      <c r="G202" s="10"/>
+      <c r="H202" s="10"/>
+      <c r="I202" s="10"/>
+      <c r="J202" s="10"/>
+      <c r="K202" t="s">
         <v>13</v>
       </c>
-      <c r="F196">
+      <c r="L202">
         <v>-8.2500000000000004E-2</v>
       </c>
     </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A197" s="10" t="s">
+    <row r="203" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A203" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="E197" t="s">
+      <c r="E203" s="10"/>
+      <c r="F203" s="10"/>
+      <c r="G203" s="10"/>
+      <c r="H203" s="10"/>
+      <c r="I203" s="10"/>
+      <c r="J203" s="10"/>
+      <c r="K203" t="s">
         <v>14</v>
       </c>
-      <c r="F197">
+      <c r="L203">
         <v>0.72799999999999998</v>
       </c>
     </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A198" s="11" t="s">
+    <row r="204" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A204" s="11" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A199" s="5" t="s">
+      <c r="E204" s="11"/>
+      <c r="F204" s="11"/>
+      <c r="G204" s="11"/>
+      <c r="H204" s="11"/>
+      <c r="I204" s="11"/>
+      <c r="J204" s="11"/>
+    </row>
+    <row r="205" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A205" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="E199" t="s">
+      <c r="E205" s="5"/>
+      <c r="F205" s="5"/>
+      <c r="G205" s="5"/>
+      <c r="H205" s="5"/>
+      <c r="I205" s="5"/>
+      <c r="J205" s="5"/>
+      <c r="K205" t="s">
         <v>14</v>
       </c>
-      <c r="F199">
+      <c r="L205">
         <v>1</v>
       </c>
-      <c r="H199" s="5" t="s">
+      <c r="N205" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A200" s="10" t="s">
+    <row r="206" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A206" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E200" t="s">
+      <c r="E206" s="10"/>
+      <c r="F206" s="10"/>
+      <c r="G206" s="10"/>
+      <c r="H206" s="10"/>
+      <c r="I206" s="10"/>
+      <c r="J206" s="10"/>
+      <c r="K206" t="s">
         <v>13</v>
       </c>
-      <c r="F200">
+      <c r="L206">
         <v>-3.2399999999999998E-2</v>
       </c>
-      <c r="H200" s="7"/>
-    </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A201" s="10" t="s">
+      <c r="N206" s="7"/>
+    </row>
+    <row r="207" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A207" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E201" t="s">
+      <c r="E207" s="10"/>
+      <c r="F207" s="10"/>
+      <c r="G207" s="10"/>
+      <c r="H207" s="10"/>
+      <c r="I207" s="10"/>
+      <c r="J207" s="10"/>
+      <c r="K207" t="s">
         <v>14</v>
       </c>
-      <c r="F201">
+      <c r="L207">
         <v>0.82120000000000004</v>
       </c>
-      <c r="H201" s="7"/>
-    </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A202" s="11" t="s">
+      <c r="N207" s="7"/>
+    </row>
+    <row r="208" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A208" s="11" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A203" s="11" t="s">
+      <c r="E208" s="11"/>
+      <c r="F208" s="11"/>
+      <c r="G208" s="11"/>
+      <c r="H208" s="11"/>
+      <c r="I208" s="11"/>
+      <c r="J208" s="11"/>
+    </row>
+    <row r="209" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A209" s="11" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A204" s="10" t="s">
+      <c r="E209" s="11"/>
+      <c r="F209" s="11"/>
+      <c r="G209" s="11"/>
+      <c r="H209" s="11"/>
+      <c r="I209" s="11"/>
+      <c r="J209" s="11"/>
+    </row>
+    <row r="210" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A210" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="E204" t="s">
+      <c r="E210" s="10"/>
+      <c r="F210" s="10"/>
+      <c r="G210" s="10"/>
+      <c r="H210" s="10"/>
+      <c r="I210" s="10"/>
+      <c r="J210" s="10"/>
+      <c r="K210" t="s">
         <v>14</v>
       </c>
-      <c r="F204">
+      <c r="L210">
         <v>1</v>
       </c>
-      <c r="H204" s="5" t="s">
+      <c r="N210" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A205" s="10" t="s">
+    <row r="211" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A211" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="E205" t="s">
+      <c r="E211" s="10"/>
+      <c r="F211" s="10"/>
+      <c r="G211" s="10"/>
+      <c r="H211" s="10"/>
+      <c r="I211" s="10"/>
+      <c r="J211" s="10"/>
+      <c r="K211" t="s">
         <v>14</v>
       </c>
-      <c r="F205">
+      <c r="L211">
         <v>1</v>
       </c>
-      <c r="H205" s="5" t="s">
+      <c r="N211" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A206" t="s">
+    <row r="212" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
         <v>47</v>
       </c>
-      <c r="E206" t="s">
+      <c r="K212" t="s">
         <v>14</v>
       </c>
-      <c r="F206">
+      <c r="L212">
         <v>1</v>
       </c>
-      <c r="H206" s="5" t="s">
+      <c r="N212" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A207" t="s">
+    <row r="213" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
         <v>48</v>
       </c>
-      <c r="E207" t="s">
+      <c r="K213" t="s">
         <v>14</v>
       </c>
-      <c r="F207">
+      <c r="L213">
         <v>1</v>
       </c>
-      <c r="H207" s="5" t="s">
+      <c r="N213" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A208" s="5" t="s">
+    <row r="214" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A214" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E208" t="s">
+      <c r="E214" s="5"/>
+      <c r="F214" s="5"/>
+      <c r="G214" s="5"/>
+      <c r="H214" s="5"/>
+      <c r="I214" s="5"/>
+      <c r="J214" s="5"/>
+      <c r="K214" t="s">
         <v>14</v>
       </c>
-      <c r="F208">
+      <c r="L214">
         <v>1</v>
       </c>
-      <c r="H208" s="5" t="s">
+      <c r="N214" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A209" s="5" t="s">
+    <row r="215" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A215" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E209" t="s">
+      <c r="E215" s="5"/>
+      <c r="F215" s="5"/>
+      <c r="G215" s="5"/>
+      <c r="H215" s="5"/>
+      <c r="I215" s="5"/>
+      <c r="J215" s="5"/>
+      <c r="K215" t="s">
         <v>14</v>
       </c>
-      <c r="F209">
+      <c r="L215">
         <v>1</v>
       </c>
-      <c r="H209" s="5" t="s">
+      <c r="N215" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A210" s="5" t="s">
+    <row r="216" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A216" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E210" t="s">
+      <c r="E216" s="5"/>
+      <c r="F216" s="5"/>
+      <c r="G216" s="5"/>
+      <c r="H216" s="5"/>
+      <c r="I216" s="5"/>
+      <c r="J216" s="5"/>
+      <c r="K216" t="s">
         <v>14</v>
       </c>
-      <c r="F210">
+      <c r="L216">
         <v>1</v>
       </c>
-      <c r="H210" s="5" t="s">
+      <c r="N216" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A211" s="5" t="s">
+    <row r="217" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A217" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E211" t="s">
+      <c r="E217" s="5"/>
+      <c r="F217" s="5"/>
+      <c r="G217" s="5"/>
+      <c r="H217" s="5"/>
+      <c r="I217" s="5"/>
+      <c r="J217" s="5"/>
+      <c r="K217" t="s">
         <v>14</v>
       </c>
-      <c r="F211">
+      <c r="L217">
         <v>1</v>
       </c>
-      <c r="H211" s="5" t="s">
+      <c r="N217" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A212" s="5" t="s">
+    <row r="218" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A218" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E212" t="s">
+      <c r="E218" s="5"/>
+      <c r="F218" s="5"/>
+      <c r="G218" s="5"/>
+      <c r="H218" s="5"/>
+      <c r="I218" s="5"/>
+      <c r="J218" s="5"/>
+      <c r="K218" t="s">
         <v>14</v>
       </c>
-      <c r="F212">
+      <c r="L218">
         <v>1</v>
       </c>
-      <c r="H212" s="5" t="s">
+      <c r="N218" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A213" s="5" t="s">
+    <row r="219" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A219" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E213" t="s">
+      <c r="E219" s="5"/>
+      <c r="F219" s="5"/>
+      <c r="G219" s="5"/>
+      <c r="H219" s="5"/>
+      <c r="I219" s="5"/>
+      <c r="J219" s="5"/>
+      <c r="K219" t="s">
         <v>14</v>
       </c>
-      <c r="F213">
+      <c r="L219">
         <v>1</v>
       </c>
-      <c r="H213" s="5" t="s">
+      <c r="N219" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A214" s="5" t="s">
+    <row r="220" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A220" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="E214" t="s">
+      <c r="E220" s="5"/>
+      <c r="F220" s="5"/>
+      <c r="G220" s="5"/>
+      <c r="H220" s="5"/>
+      <c r="I220" s="5"/>
+      <c r="J220" s="5"/>
+      <c r="K220" t="s">
         <v>14</v>
       </c>
-      <c r="F214">
+      <c r="L220">
         <v>1</v>
       </c>
-      <c r="H214" s="5" t="s">
+      <c r="N220" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A215" s="5" t="s">
+    <row r="221" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A221" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E215" t="s">
+      <c r="E221" s="5"/>
+      <c r="F221" s="5"/>
+      <c r="G221" s="5"/>
+      <c r="H221" s="5"/>
+      <c r="I221" s="5"/>
+      <c r="J221" s="5"/>
+      <c r="K221" t="s">
         <v>14</v>
       </c>
-      <c r="F215">
+      <c r="L221">
         <v>1</v>
       </c>
-      <c r="H215" s="5" t="s">
+      <c r="N221" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A216" s="5" t="s">
+    <row r="222" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A222" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E216" t="s">
+      <c r="E222" s="5"/>
+      <c r="F222" s="5"/>
+      <c r="G222" s="5"/>
+      <c r="H222" s="5"/>
+      <c r="I222" s="5"/>
+      <c r="J222" s="5"/>
+      <c r="K222" t="s">
         <v>14</v>
       </c>
-      <c r="F216">
+      <c r="L222">
         <v>1</v>
       </c>
-      <c r="H216" s="5" t="s">
+      <c r="N222" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A217" s="5" t="s">
+    <row r="223" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A223" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E217" t="s">
+      <c r="E223" s="5"/>
+      <c r="F223" s="5"/>
+      <c r="G223" s="5"/>
+      <c r="H223" s="5"/>
+      <c r="I223" s="5"/>
+      <c r="J223" s="5"/>
+      <c r="K223" t="s">
         <v>14</v>
       </c>
-      <c r="F217">
+      <c r="L223">
         <v>1</v>
       </c>
-      <c r="H217" s="5" t="s">
+      <c r="N223" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A218" s="5" t="s">
+    <row r="224" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A224" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E218" t="s">
+      <c r="E224" s="5"/>
+      <c r="F224" s="5"/>
+      <c r="G224" s="5"/>
+      <c r="H224" s="5"/>
+      <c r="I224" s="5"/>
+      <c r="J224" s="5"/>
+      <c r="K224" t="s">
         <v>14</v>
       </c>
-      <c r="F218">
+      <c r="L224">
         <v>1</v>
       </c>
-      <c r="H218" s="5" t="s">
+      <c r="N224" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A219" s="5" t="s">
+    <row r="225" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A225" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E219" t="s">
+      <c r="E225" s="5"/>
+      <c r="F225" s="5"/>
+      <c r="G225" s="5"/>
+      <c r="H225" s="5"/>
+      <c r="I225" s="5"/>
+      <c r="J225" s="5"/>
+      <c r="K225" t="s">
         <v>14</v>
       </c>
-      <c r="F219">
+      <c r="L225">
         <v>1</v>
       </c>
-      <c r="H219" s="5" t="s">
+      <c r="N225" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A220" s="5" t="s">
+    <row r="226" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A226" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="E220" t="s">
+      <c r="E226" s="5"/>
+      <c r="F226" s="5"/>
+      <c r="G226" s="5"/>
+      <c r="H226" s="5"/>
+      <c r="I226" s="5"/>
+      <c r="J226" s="5"/>
+      <c r="K226" t="s">
         <v>14</v>
       </c>
-      <c r="F220">
+      <c r="L226">
         <v>1</v>
       </c>
-      <c r="H220" s="5" t="s">
+      <c r="N226" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A221" s="5" t="s">
+    <row r="227" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A227" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="E221" t="s">
+      <c r="E227" s="5"/>
+      <c r="F227" s="5"/>
+      <c r="G227" s="5"/>
+      <c r="H227" s="5"/>
+      <c r="I227" s="5"/>
+      <c r="J227" s="5"/>
+      <c r="K227" t="s">
         <v>14</v>
       </c>
-      <c r="F221">
+      <c r="L227">
         <v>1</v>
       </c>
-      <c r="H221" s="5" t="s">
+      <c r="N227" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A222" s="5" t="s">
+    <row r="228" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A228" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E222" t="s">
+      <c r="E228" s="5"/>
+      <c r="F228" s="5"/>
+      <c r="G228" s="5"/>
+      <c r="H228" s="5"/>
+      <c r="I228" s="5"/>
+      <c r="J228" s="5"/>
+      <c r="K228" t="s">
         <v>14</v>
       </c>
-      <c r="F222">
+      <c r="L228">
         <v>1</v>
       </c>
-      <c r="H222" s="5" t="s">
+      <c r="N228" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A223" s="5" t="s">
+    <row r="229" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A229" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E223" t="s">
+      <c r="E229" s="5"/>
+      <c r="F229" s="5"/>
+      <c r="G229" s="5"/>
+      <c r="H229" s="5"/>
+      <c r="I229" s="5"/>
+      <c r="J229" s="5"/>
+      <c r="K229" t="s">
         <v>14</v>
       </c>
-      <c r="F223">
+      <c r="L229">
         <v>1</v>
       </c>
-      <c r="H223" s="5" t="s">
+      <c r="N229" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A224" s="5" t="s">
+    <row r="230" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A230" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="E224" t="s">
+      <c r="E230" s="5"/>
+      <c r="F230" s="5"/>
+      <c r="G230" s="5"/>
+      <c r="H230" s="5"/>
+      <c r="I230" s="5"/>
+      <c r="J230" s="5"/>
+      <c r="K230" t="s">
         <v>14</v>
       </c>
-      <c r="F224">
+      <c r="L230">
         <v>1</v>
       </c>
-      <c r="H224" s="5" t="s">
+      <c r="N230" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A225" s="5" t="s">
+    <row r="231" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A231" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="E225" t="s">
+      <c r="E231" s="5"/>
+      <c r="F231" s="5"/>
+      <c r="G231" s="5"/>
+      <c r="H231" s="5"/>
+      <c r="I231" s="5"/>
+      <c r="J231" s="5"/>
+      <c r="K231" t="s">
         <v>14</v>
       </c>
-      <c r="F225">
+      <c r="L231">
         <v>1</v>
       </c>
-      <c r="H225" s="5" t="s">
+      <c r="N231" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A226" s="5" t="s">
+    <row r="232" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A232" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E226" t="s">
+      <c r="E232" s="5"/>
+      <c r="F232" s="5"/>
+      <c r="G232" s="5"/>
+      <c r="H232" s="5"/>
+      <c r="I232" s="5"/>
+      <c r="J232" s="5"/>
+      <c r="K232" t="s">
         <v>14</v>
       </c>
-      <c r="F226">
+      <c r="L232">
         <v>1</v>
       </c>
-      <c r="H226" s="5" t="s">
+      <c r="N232" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A227" s="5" t="s">
+    <row r="233" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A233" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E227" t="s">
+      <c r="E233" s="5"/>
+      <c r="F233" s="5"/>
+      <c r="G233" s="5"/>
+      <c r="H233" s="5"/>
+      <c r="I233" s="5"/>
+      <c r="J233" s="5"/>
+      <c r="K233" t="s">
         <v>14</v>
       </c>
-      <c r="F227">
+      <c r="L233">
         <v>1</v>
       </c>
-      <c r="H227" s="5" t="s">
+      <c r="N233" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A228" s="5" t="s">
+    <row r="234" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A234" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E228" t="s">
+      <c r="E234" s="5"/>
+      <c r="F234" s="5"/>
+      <c r="G234" s="5"/>
+      <c r="H234" s="5"/>
+      <c r="I234" s="5"/>
+      <c r="J234" s="5"/>
+      <c r="K234" t="s">
         <v>14</v>
       </c>
-      <c r="F228">
+      <c r="L234">
         <v>1</v>
       </c>
-      <c r="H228" s="5" t="s">
+      <c r="N234" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A229" s="5" t="s">
+    <row r="235" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A235" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E229" t="s">
+      <c r="E235" s="5"/>
+      <c r="F235" s="5"/>
+      <c r="G235" s="5"/>
+      <c r="H235" s="5"/>
+      <c r="I235" s="5"/>
+      <c r="J235" s="5"/>
+      <c r="K235" t="s">
         <v>14</v>
       </c>
-      <c r="F229">
+      <c r="L235">
         <v>1</v>
       </c>
-      <c r="H229" s="5" t="s">
+      <c r="N235" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A230" s="5" t="s">
+    <row r="236" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A236" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E230" t="s">
+      <c r="E236" s="5"/>
+      <c r="F236" s="5"/>
+      <c r="G236" s="5"/>
+      <c r="H236" s="5"/>
+      <c r="I236" s="5"/>
+      <c r="J236" s="5"/>
+      <c r="K236" t="s">
         <v>14</v>
       </c>
-      <c r="F230">
+      <c r="L236">
         <v>1</v>
       </c>
-      <c r="H230" s="5" t="s">
+      <c r="N236" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A231" s="5" t="s">
+    <row r="237" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A237" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E231" t="s">
+      <c r="E237" s="5"/>
+      <c r="F237" s="5"/>
+      <c r="G237" s="5"/>
+      <c r="H237" s="5"/>
+      <c r="I237" s="5"/>
+      <c r="J237" s="5"/>
+      <c r="K237" t="s">
         <v>14</v>
       </c>
-      <c r="F231">
+      <c r="L237">
         <v>1</v>
       </c>
-      <c r="H231" s="5" t="s">
+      <c r="N237" s="5" t="s">
         <v>78</v>
+      </c>
+    </row>
+    <row r="239" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A239" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B239" s="2"/>
+      <c r="C239" s="2"/>
+      <c r="D239" s="2"/>
+      <c r="E239" s="2"/>
+      <c r="F239" s="2"/>
+      <c r="G239" s="2"/>
+      <c r="H239" s="2"/>
+      <c r="I239" s="2"/>
+      <c r="J239" s="2"/>
+      <c r="K239" s="2"/>
+      <c r="L239" s="2"/>
+      <c r="M239" s="2"/>
+      <c r="N239" s="2"/>
+      <c r="O239" s="2"/>
+    </row>
+    <row r="240" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="J240" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="K240" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="L240" s="14">
+        <v>0</v>
+      </c>
+      <c r="M240" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="N240" s="6" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="241" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A241" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="J241" s="6"/>
+      <c r="K241" s="6"/>
+      <c r="L241" s="14"/>
+      <c r="M241" s="6"/>
+      <c r="N241" s="6"/>
+    </row>
+    <row r="242" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="E242" t="s">
+        <v>126</v>
+      </c>
+      <c r="J242" t="s">
+        <v>132</v>
+      </c>
+      <c r="K242" t="s">
+        <v>164</v>
+      </c>
+      <c r="L242" s="12">
+        <f>8/1000*(14/(1*14+3*2))*100</f>
+        <v>0.55999999999999994</v>
+      </c>
+      <c r="M242" t="s">
+        <v>133</v>
+      </c>
+      <c r="N242" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="O242" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="243" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="E243" t="s">
+        <v>127</v>
+      </c>
+      <c r="J243" t="s">
+        <v>132</v>
+      </c>
+      <c r="K243" t="s">
+        <v>164</v>
+      </c>
+      <c r="L243" s="12">
+        <f>15/1000*(14/(1*14+3*2))*100</f>
+        <v>1.0499999999999998</v>
+      </c>
+      <c r="M243" t="s">
+        <v>133</v>
+      </c>
+      <c r="O243" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="244" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="E244" t="s">
+        <v>125</v>
+      </c>
+      <c r="J244" t="s">
+        <v>132</v>
+      </c>
+      <c r="K244" t="s">
+        <v>164</v>
+      </c>
+      <c r="L244" s="12">
+        <f>50/1000*(14/(1*14+3*2))*100</f>
+        <v>3.4999999999999996</v>
+      </c>
+      <c r="M244" t="s">
+        <v>133</v>
+      </c>
+      <c r="O244" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="245" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A245" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="246" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="F246" t="s">
+        <v>142</v>
+      </c>
+      <c r="G246" t="s">
+        <v>143</v>
+      </c>
+      <c r="H246" t="s">
+        <v>144</v>
+      </c>
+      <c r="I246" t="s">
+        <v>155</v>
+      </c>
+      <c r="J246" t="s">
+        <v>132</v>
+      </c>
+      <c r="K246" t="s">
+        <v>164</v>
+      </c>
+      <c r="L246">
+        <v>33</v>
+      </c>
+      <c r="M246" t="s">
+        <v>133</v>
+      </c>
+      <c r="O246" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="247" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="F247" t="s">
+        <v>142</v>
+      </c>
+      <c r="G247" t="s">
+        <v>143</v>
+      </c>
+      <c r="H247" t="s">
+        <v>144</v>
+      </c>
+      <c r="I247" t="s">
+        <v>156</v>
+      </c>
+      <c r="J247" t="s">
+        <v>132</v>
+      </c>
+      <c r="K247" t="s">
+        <v>164</v>
+      </c>
+      <c r="L247">
+        <v>38</v>
+      </c>
+      <c r="M247" t="s">
+        <v>133</v>
+      </c>
+      <c r="O247" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="248" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="F248" t="s">
+        <v>142</v>
+      </c>
+      <c r="G248" t="s">
+        <v>143</v>
+      </c>
+      <c r="H248" t="s">
+        <v>144</v>
+      </c>
+      <c r="I248" t="s">
+        <v>157</v>
+      </c>
+      <c r="J248" t="s">
+        <v>132</v>
+      </c>
+      <c r="K248" t="s">
+        <v>164</v>
+      </c>
+      <c r="L248">
+        <v>41</v>
+      </c>
+      <c r="M248" t="s">
+        <v>133</v>
+      </c>
+      <c r="O248" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="249" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="F249" t="s">
+        <v>142</v>
+      </c>
+      <c r="G249" t="s">
+        <v>145</v>
+      </c>
+      <c r="H249" t="s">
+        <v>144</v>
+      </c>
+      <c r="I249" t="s">
+        <v>155</v>
+      </c>
+      <c r="J249" t="s">
+        <v>132</v>
+      </c>
+      <c r="K249" t="s">
+        <v>164</v>
+      </c>
+      <c r="L249">
+        <v>32</v>
+      </c>
+      <c r="M249" t="s">
+        <v>133</v>
+      </c>
+      <c r="O249" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="250" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="F250" t="s">
+        <v>142</v>
+      </c>
+      <c r="G250" t="s">
+        <v>145</v>
+      </c>
+      <c r="H250" t="s">
+        <v>144</v>
+      </c>
+      <c r="I250" t="s">
+        <v>156</v>
+      </c>
+      <c r="J250" t="s">
+        <v>132</v>
+      </c>
+      <c r="K250" t="s">
+        <v>164</v>
+      </c>
+      <c r="L250">
+        <v>39</v>
+      </c>
+      <c r="M250" t="s">
+        <v>133</v>
+      </c>
+      <c r="O250" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="251" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="F251" t="s">
+        <v>142</v>
+      </c>
+      <c r="G251" t="s">
+        <v>145</v>
+      </c>
+      <c r="H251" t="s">
+        <v>144</v>
+      </c>
+      <c r="I251" t="s">
+        <v>157</v>
+      </c>
+      <c r="J251" t="s">
+        <v>132</v>
+      </c>
+      <c r="K251" t="s">
+        <v>164</v>
+      </c>
+      <c r="L251">
+        <v>46</v>
+      </c>
+      <c r="M251" t="s">
+        <v>133</v>
+      </c>
+      <c r="O251" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="252" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="F252" t="s">
+        <v>142</v>
+      </c>
+      <c r="H252" t="s">
+        <v>146</v>
+      </c>
+      <c r="I252" t="s">
+        <v>155</v>
+      </c>
+      <c r="J252" t="s">
+        <v>132</v>
+      </c>
+      <c r="K252" t="s">
+        <v>164</v>
+      </c>
+      <c r="L252">
+        <v>32</v>
+      </c>
+      <c r="M252" t="s">
+        <v>133</v>
+      </c>
+      <c r="O252" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="253" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="F253" t="s">
+        <v>142</v>
+      </c>
+      <c r="H253" t="s">
+        <v>146</v>
+      </c>
+      <c r="I253" t="s">
+        <v>156</v>
+      </c>
+      <c r="J253" t="s">
+        <v>132</v>
+      </c>
+      <c r="K253" t="s">
+        <v>164</v>
+      </c>
+      <c r="L253">
+        <v>38</v>
+      </c>
+      <c r="M253" t="s">
+        <v>133</v>
+      </c>
+      <c r="O253" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="254" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="F254" t="s">
+        <v>142</v>
+      </c>
+      <c r="H254" t="s">
+        <v>146</v>
+      </c>
+      <c r="I254" t="s">
+        <v>157</v>
+      </c>
+      <c r="J254" t="s">
+        <v>132</v>
+      </c>
+      <c r="K254" t="s">
+        <v>164</v>
+      </c>
+      <c r="L254">
+        <v>47</v>
+      </c>
+      <c r="M254" t="s">
+        <v>133</v>
+      </c>
+      <c r="O254" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="255" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="F255" t="s">
+        <v>142</v>
+      </c>
+      <c r="H255" t="s">
+        <v>147</v>
+      </c>
+      <c r="I255" t="s">
+        <v>155</v>
+      </c>
+      <c r="J255" t="s">
+        <v>132</v>
+      </c>
+      <c r="K255" t="s">
+        <v>164</v>
+      </c>
+      <c r="L255">
+        <v>33</v>
+      </c>
+      <c r="M255" t="s">
+        <v>133</v>
+      </c>
+      <c r="O255" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="256" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="F256" t="s">
+        <v>142</v>
+      </c>
+      <c r="H256" t="s">
+        <v>147</v>
+      </c>
+      <c r="I256" t="s">
+        <v>156</v>
+      </c>
+      <c r="J256" t="s">
+        <v>132</v>
+      </c>
+      <c r="K256" t="s">
+        <v>164</v>
+      </c>
+      <c r="L256">
+        <v>39</v>
+      </c>
+      <c r="M256" t="s">
+        <v>133</v>
+      </c>
+      <c r="O256" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="257" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="F257" t="s">
+        <v>142</v>
+      </c>
+      <c r="H257" t="s">
+        <v>147</v>
+      </c>
+      <c r="I257" t="s">
+        <v>157</v>
+      </c>
+      <c r="J257" t="s">
+        <v>132</v>
+      </c>
+      <c r="K257" t="s">
+        <v>164</v>
+      </c>
+      <c r="L257">
+        <v>47</v>
+      </c>
+      <c r="M257" t="s">
+        <v>133</v>
+      </c>
+      <c r="O257" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="258" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="F258" t="s">
+        <v>142</v>
+      </c>
+      <c r="I258" t="s">
+        <v>155</v>
+      </c>
+      <c r="J258" t="s">
+        <v>132</v>
+      </c>
+      <c r="K258" t="s">
+        <v>164</v>
+      </c>
+      <c r="L258">
+        <v>32</v>
+      </c>
+      <c r="M258" t="s">
+        <v>133</v>
+      </c>
+      <c r="N258" t="s">
+        <v>158</v>
+      </c>
+      <c r="O258" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="259" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="F259" t="s">
+        <v>142</v>
+      </c>
+      <c r="I259" t="s">
+        <v>156</v>
+      </c>
+      <c r="J259" t="s">
+        <v>132</v>
+      </c>
+      <c r="K259" t="s">
+        <v>164</v>
+      </c>
+      <c r="L259">
+        <v>39</v>
+      </c>
+      <c r="M259" t="s">
+        <v>133</v>
+      </c>
+      <c r="N259" t="s">
+        <v>158</v>
+      </c>
+      <c r="O259" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="260" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="F260" t="s">
+        <v>142</v>
+      </c>
+      <c r="I260" t="s">
+        <v>157</v>
+      </c>
+      <c r="J260" t="s">
+        <v>132</v>
+      </c>
+      <c r="K260" t="s">
+        <v>164</v>
+      </c>
+      <c r="L260">
+        <v>46</v>
+      </c>
+      <c r="M260" t="s">
+        <v>133</v>
+      </c>
+      <c r="N260" t="s">
+        <v>158</v>
+      </c>
+      <c r="O260" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="261" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="F261" t="s">
+        <v>161</v>
+      </c>
+      <c r="I261" t="s">
+        <v>156</v>
+      </c>
+      <c r="J261" t="s">
+        <v>132</v>
+      </c>
+      <c r="K261" t="s">
+        <v>164</v>
+      </c>
+      <c r="L261">
+        <v>43</v>
+      </c>
+      <c r="M261" t="s">
+        <v>133</v>
+      </c>
+      <c r="O261" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="262" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="F262" t="s">
+        <v>161</v>
+      </c>
+      <c r="I262" t="s">
+        <v>157</v>
+      </c>
+      <c r="J262" t="s">
+        <v>132</v>
+      </c>
+      <c r="K262" t="s">
+        <v>164</v>
+      </c>
+      <c r="L262">
+        <v>47</v>
+      </c>
+      <c r="M262" t="s">
+        <v>133</v>
+      </c>
+      <c r="O262" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="263" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="F263" t="s">
+        <v>148</v>
+      </c>
+      <c r="H263" t="s">
+        <v>149</v>
+      </c>
+      <c r="I263" t="s">
+        <v>155</v>
+      </c>
+      <c r="J263" t="s">
+        <v>132</v>
+      </c>
+      <c r="K263" t="s">
+        <v>164</v>
+      </c>
+      <c r="L263">
+        <v>30</v>
+      </c>
+      <c r="M263" t="s">
+        <v>133</v>
+      </c>
+      <c r="O263" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="264" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="F264" t="s">
+        <v>148</v>
+      </c>
+      <c r="H264" t="s">
+        <v>149</v>
+      </c>
+      <c r="I264" t="s">
+        <v>156</v>
+      </c>
+      <c r="J264" t="s">
+        <v>132</v>
+      </c>
+      <c r="K264" t="s">
+        <v>164</v>
+      </c>
+      <c r="L264">
+        <v>35</v>
+      </c>
+      <c r="M264" t="s">
+        <v>133</v>
+      </c>
+      <c r="O264" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="265" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="F265" t="s">
+        <v>148</v>
+      </c>
+      <c r="H265" t="s">
+        <v>149</v>
+      </c>
+      <c r="I265" t="s">
+        <v>157</v>
+      </c>
+      <c r="J265" t="s">
+        <v>132</v>
+      </c>
+      <c r="K265" t="s">
+        <v>164</v>
+      </c>
+      <c r="L265">
+        <v>48</v>
+      </c>
+      <c r="M265" t="s">
+        <v>133</v>
+      </c>
+      <c r="O265" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="266" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="F266" t="s">
+        <v>148</v>
+      </c>
+      <c r="H266" t="s">
+        <v>150</v>
+      </c>
+      <c r="I266" t="s">
+        <v>155</v>
+      </c>
+      <c r="J266" t="s">
+        <v>132</v>
+      </c>
+      <c r="K266" t="s">
+        <v>164</v>
+      </c>
+      <c r="L266">
+        <v>29</v>
+      </c>
+      <c r="M266" t="s">
+        <v>133</v>
+      </c>
+      <c r="O266" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="267" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="F267" t="s">
+        <v>148</v>
+      </c>
+      <c r="H267" t="s">
+        <v>150</v>
+      </c>
+      <c r="I267" t="s">
+        <v>156</v>
+      </c>
+      <c r="J267" t="s">
+        <v>132</v>
+      </c>
+      <c r="K267" t="s">
+        <v>164</v>
+      </c>
+      <c r="L267">
+        <v>34</v>
+      </c>
+      <c r="M267" t="s">
+        <v>133</v>
+      </c>
+      <c r="O267" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="268" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="F268" t="s">
+        <v>148</v>
+      </c>
+      <c r="H268" t="s">
+        <v>150</v>
+      </c>
+      <c r="I268" t="s">
+        <v>157</v>
+      </c>
+      <c r="J268" t="s">
+        <v>132</v>
+      </c>
+      <c r="K268" t="s">
+        <v>164</v>
+      </c>
+      <c r="L268">
+        <v>46</v>
+      </c>
+      <c r="M268" t="s">
+        <v>133</v>
+      </c>
+      <c r="O268" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="269" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="F269" t="s">
+        <v>148</v>
+      </c>
+      <c r="H269" t="s">
+        <v>151</v>
+      </c>
+      <c r="I269" t="s">
+        <v>155</v>
+      </c>
+      <c r="J269" t="s">
+        <v>132</v>
+      </c>
+      <c r="K269" t="s">
+        <v>164</v>
+      </c>
+      <c r="L269">
+        <v>29</v>
+      </c>
+      <c r="M269" t="s">
+        <v>133</v>
+      </c>
+      <c r="O269" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="270" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="F270" t="s">
+        <v>148</v>
+      </c>
+      <c r="H270" t="s">
+        <v>151</v>
+      </c>
+      <c r="I270" t="s">
+        <v>156</v>
+      </c>
+      <c r="J270" t="s">
+        <v>132</v>
+      </c>
+      <c r="K270" t="s">
+        <v>164</v>
+      </c>
+      <c r="L270">
+        <v>35</v>
+      </c>
+      <c r="M270" t="s">
+        <v>133</v>
+      </c>
+      <c r="O270" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="271" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="F271" t="s">
+        <v>148</v>
+      </c>
+      <c r="H271" t="s">
+        <v>151</v>
+      </c>
+      <c r="I271" t="s">
+        <v>157</v>
+      </c>
+      <c r="J271" t="s">
+        <v>132</v>
+      </c>
+      <c r="K271" t="s">
+        <v>164</v>
+      </c>
+      <c r="L271">
+        <v>48</v>
+      </c>
+      <c r="M271" t="s">
+        <v>133</v>
+      </c>
+      <c r="O271" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="272" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="F272" t="s">
+        <v>148</v>
+      </c>
+      <c r="H272" t="s">
+        <v>152</v>
+      </c>
+      <c r="I272" t="s">
+        <v>155</v>
+      </c>
+      <c r="J272" t="s">
+        <v>132</v>
+      </c>
+      <c r="K272" t="s">
+        <v>164</v>
+      </c>
+      <c r="L272" s="13">
+        <f>L263</f>
+        <v>30</v>
+      </c>
+      <c r="M272" t="s">
+        <v>133</v>
+      </c>
+      <c r="N272" t="s">
+        <v>160</v>
+      </c>
+      <c r="O272" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="273" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="F273" t="s">
+        <v>148</v>
+      </c>
+      <c r="H273" t="s">
+        <v>152</v>
+      </c>
+      <c r="I273" t="s">
+        <v>156</v>
+      </c>
+      <c r="J273" t="s">
+        <v>132</v>
+      </c>
+      <c r="K273" t="s">
+        <v>164</v>
+      </c>
+      <c r="L273" s="13">
+        <f t="shared" ref="L273:L274" si="4">L264</f>
+        <v>35</v>
+      </c>
+      <c r="M273" t="s">
+        <v>133</v>
+      </c>
+      <c r="N273" t="s">
+        <v>160</v>
+      </c>
+      <c r="O273" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="274" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="F274" t="s">
+        <v>148</v>
+      </c>
+      <c r="H274" t="s">
+        <v>152</v>
+      </c>
+      <c r="I274" t="s">
+        <v>157</v>
+      </c>
+      <c r="J274" t="s">
+        <v>132</v>
+      </c>
+      <c r="K274" t="s">
+        <v>164</v>
+      </c>
+      <c r="L274" s="13">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="M274" t="s">
+        <v>133</v>
+      </c>
+      <c r="N274" t="s">
+        <v>160</v>
+      </c>
+      <c r="O274" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="275" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="F275" t="s">
+        <v>148</v>
+      </c>
+      <c r="I275" t="s">
+        <v>155</v>
+      </c>
+      <c r="J275" t="s">
+        <v>132</v>
+      </c>
+      <c r="K275" t="s">
+        <v>164</v>
+      </c>
+      <c r="L275">
+        <v>29</v>
+      </c>
+      <c r="M275" t="s">
+        <v>133</v>
+      </c>
+      <c r="N275" t="s">
+        <v>159</v>
+      </c>
+      <c r="O275" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="276" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="F276" t="s">
+        <v>148</v>
+      </c>
+      <c r="I276" t="s">
+        <v>156</v>
+      </c>
+      <c r="J276" t="s">
+        <v>132</v>
+      </c>
+      <c r="K276" t="s">
+        <v>164</v>
+      </c>
+      <c r="L276">
+        <v>35</v>
+      </c>
+      <c r="M276" t="s">
+        <v>133</v>
+      </c>
+      <c r="N276" t="s">
+        <v>159</v>
+      </c>
+      <c r="O276" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="277" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="F277" t="s">
+        <v>148</v>
+      </c>
+      <c r="I277" t="s">
+        <v>157</v>
+      </c>
+      <c r="J277" t="s">
+        <v>132</v>
+      </c>
+      <c r="K277" t="s">
+        <v>164</v>
+      </c>
+      <c r="L277">
+        <v>44</v>
+      </c>
+      <c r="M277" t="s">
+        <v>133</v>
+      </c>
+      <c r="N277" t="s">
+        <v>159</v>
+      </c>
+      <c r="O277" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="278" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="F278" t="s">
+        <v>153</v>
+      </c>
+      <c r="G278" t="s">
+        <v>154</v>
+      </c>
+      <c r="I278" t="s">
+        <v>156</v>
+      </c>
+      <c r="J278" t="s">
+        <v>132</v>
+      </c>
+      <c r="K278" t="s">
+        <v>164</v>
+      </c>
+      <c r="L278">
+        <v>41</v>
+      </c>
+      <c r="M278" t="s">
+        <v>133</v>
+      </c>
+      <c r="O278" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="279" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="F279" t="s">
+        <v>153</v>
+      </c>
+      <c r="G279" t="s">
+        <v>154</v>
+      </c>
+      <c r="I279" t="s">
+        <v>157</v>
+      </c>
+      <c r="J279" t="s">
+        <v>132</v>
+      </c>
+      <c r="K279" t="s">
+        <v>164</v>
+      </c>
+      <c r="L279">
+        <v>41</v>
+      </c>
+      <c r="M279" t="s">
+        <v>133</v>
+      </c>
+      <c r="O279" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="281" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A281" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B281" s="2"/>
+      <c r="C281" s="2"/>
+      <c r="D281" s="2"/>
+      <c r="E281" s="2"/>
+      <c r="F281" s="2"/>
+      <c r="G281" s="2"/>
+      <c r="H281" s="2"/>
+      <c r="I281" s="2"/>
+      <c r="J281" s="2"/>
+      <c r="K281" s="2"/>
+      <c r="L281" s="2"/>
+      <c r="M281" s="2"/>
+      <c r="N281" s="2"/>
+      <c r="O281" s="2"/>
+    </row>
+    <row r="283" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="J283" t="s">
+        <v>173</v>
+      </c>
+      <c r="K283" t="s">
+        <v>174</v>
+      </c>
+      <c r="L283">
+        <v>1</v>
+      </c>
+      <c r="M283" t="s">
+        <v>128</v>
+      </c>
+      <c r="N283" t="s">
+        <v>184</v>
+      </c>
+      <c r="O283" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="284" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="J284" t="s">
+        <v>173</v>
+      </c>
+      <c r="K284" t="s">
+        <v>179</v>
+      </c>
+      <c r="L284">
+        <v>1</v>
+      </c>
+      <c r="M284" t="s">
+        <v>128</v>
+      </c>
+      <c r="N284" t="s">
+        <v>180</v>
+      </c>
+      <c r="O284" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="285" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="F285" t="s">
+        <v>142</v>
+      </c>
+      <c r="I285" t="s">
+        <v>176</v>
+      </c>
+      <c r="J285" t="s">
+        <v>173</v>
+      </c>
+      <c r="K285" t="s">
+        <v>179</v>
+      </c>
+      <c r="L285">
+        <v>2</v>
+      </c>
+      <c r="M285" t="s">
+        <v>128</v>
+      </c>
+      <c r="N285" t="s">
+        <v>181</v>
+      </c>
+      <c r="O285" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="286" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="I286" t="s">
+        <v>176</v>
+      </c>
+      <c r="J286" t="s">
+        <v>173</v>
+      </c>
+      <c r="K286" t="s">
+        <v>179</v>
+      </c>
+      <c r="L286">
+        <v>1</v>
+      </c>
+      <c r="M286" t="s">
+        <v>128</v>
+      </c>
+      <c r="N286" t="s">
+        <v>182</v>
+      </c>
+      <c r="O286" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="287" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="J287" t="s">
+        <v>173</v>
+      </c>
+      <c r="K287" t="s">
+        <v>175</v>
+      </c>
+      <c r="L287">
+        <v>1</v>
+      </c>
+      <c r="M287" t="s">
+        <v>128</v>
+      </c>
+      <c r="N287" t="s">
+        <v>183</v>
+      </c>
+      <c r="O287" t="s">
+        <v>178</v>
       </c>
     </row>
   </sheetData>

--- a/data/prod_parameters/PlantNutrientMgmt.xlsx
+++ b/data/prod_parameters/PlantNutrientMgmt.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1036" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="190">
   <si>
     <t>f_crop</t>
   </si>
@@ -469,9 +469,6 @@
     <t>f_MMS</t>
   </si>
   <si>
-    <t>Ammonia emissions spreading fertiliser and manure</t>
-  </si>
-  <si>
     <t>cattle</t>
   </si>
   <si>
@@ -562,18 +559,9 @@
     <t>Swedish IIR 2023. Table 5-13</t>
   </si>
   <si>
-    <t>Soil N2O emissions</t>
-  </si>
-  <si>
     <t>N2O-N</t>
   </si>
   <si>
-    <t>mineral_EF</t>
-  </si>
-  <si>
-    <t>crop_resid_EF</t>
-  </si>
-  <si>
     <t>grazing</t>
   </si>
   <si>
@@ -583,12 +571,6 @@
     <t>Swedish NIR 2021. Table 5.20</t>
   </si>
   <si>
-    <t>organic_EF</t>
-  </si>
-  <si>
-    <t>applied manure/other organic</t>
-  </si>
-  <si>
     <t>manure on pasture (cattle)</t>
   </si>
   <si>
@@ -599,6 +581,39 @@
   </si>
   <si>
     <t>mineral N fertiliser</t>
+  </si>
+  <si>
+    <t>NH3 from manure on pasture!!</t>
+  </si>
+  <si>
+    <t>applied manure</t>
+  </si>
+  <si>
+    <t>Application losses</t>
+  </si>
+  <si>
+    <t>Soil losses</t>
+  </si>
+  <si>
+    <t>soil_losses_mineral</t>
+  </si>
+  <si>
+    <t>soil_losses_organic</t>
+  </si>
+  <si>
+    <t>soil_losses_manure</t>
+  </si>
+  <si>
+    <t>soil_losses_crop_residues</t>
+  </si>
+  <si>
+    <t>organic fertilisers (other than manure)</t>
+  </si>
+  <si>
+    <t>Table 3.9. EMEP/EEA air pollutant emission inventory Guidebook 2019</t>
+  </si>
+  <si>
+    <t>emission factors are available for different spreading techniques and timings. Use these!!!</t>
   </si>
 </sst>
 </file>
@@ -998,7 +1013,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R287"/>
+  <dimension ref="A1:R292"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -1029,7 +1044,7 @@
         <v>8</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>137</v>
@@ -1120,7 +1135,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -1142,7 +1157,7 @@
         <v>114</v>
       </c>
       <c r="K8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -1151,18 +1166,18 @@
         <v>128</v>
       </c>
       <c r="N8" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E9" t="s">
         <v>126</v>
       </c>
       <c r="K9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L9">
         <v>59</v>
@@ -1179,13 +1194,13 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E10" t="s">
         <v>127</v>
       </c>
       <c r="K10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L10">
         <v>7</v>
@@ -1199,13 +1214,13 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E11" t="s">
         <v>125</v>
       </c>
       <c r="K11" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L11">
         <v>34</v>
@@ -4722,7 +4737,7 @@
     </row>
     <row r="239" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
-        <v>141</v>
+        <v>181</v>
       </c>
       <c r="B239" s="2"/>
       <c r="C239" s="2"/>
@@ -4744,7 +4759,7 @@
         <v>132</v>
       </c>
       <c r="K240" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L240" s="14">
         <v>0</v>
@@ -4753,12 +4768,12 @@
         <v>133</v>
       </c>
       <c r="N240" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="241" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J241" s="6"/>
       <c r="K241" s="6"/>
@@ -4774,7 +4789,7 @@
         <v>132</v>
       </c>
       <c r="K242" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L242" s="12">
         <f>8/1000*(14/(1*14+3*2))*100</f>
@@ -4798,7 +4813,7 @@
         <v>132</v>
       </c>
       <c r="K243" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L243" s="12">
         <f>15/1000*(14/(1*14+3*2))*100</f>
@@ -4819,7 +4834,7 @@
         <v>132</v>
       </c>
       <c r="K244" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L244" s="12">
         <f>50/1000*(14/(1*14+3*2))*100</f>
@@ -4834,27 +4849,30 @@
     </row>
     <row r="245" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
+      </c>
+      <c r="B245" s="7" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="246" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F246" t="s">
+        <v>141</v>
+      </c>
+      <c r="G246" t="s">
         <v>142</v>
       </c>
-      <c r="G246" t="s">
+      <c r="H246" t="s">
         <v>143</v>
       </c>
-      <c r="H246" t="s">
-        <v>144</v>
-      </c>
       <c r="I246" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J246" t="s">
         <v>132</v>
       </c>
       <c r="K246" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L246">
         <v>33</v>
@@ -4863,27 +4881,27 @@
         <v>133</v>
       </c>
       <c r="O246" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="247" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F247" t="s">
+        <v>141</v>
+      </c>
+      <c r="G247" t="s">
         <v>142</v>
       </c>
-      <c r="G247" t="s">
+      <c r="H247" t="s">
         <v>143</v>
       </c>
-      <c r="H247" t="s">
-        <v>144</v>
-      </c>
       <c r="I247" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J247" t="s">
         <v>132</v>
       </c>
       <c r="K247" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L247">
         <v>38</v>
@@ -4892,27 +4910,27 @@
         <v>133</v>
       </c>
       <c r="O247" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="248" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F248" t="s">
+        <v>141</v>
+      </c>
+      <c r="G248" t="s">
         <v>142</v>
       </c>
-      <c r="G248" t="s">
+      <c r="H248" t="s">
         <v>143</v>
       </c>
-      <c r="H248" t="s">
-        <v>144</v>
-      </c>
       <c r="I248" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J248" t="s">
         <v>132</v>
       </c>
       <c r="K248" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L248">
         <v>41</v>
@@ -4921,27 +4939,27 @@
         <v>133</v>
       </c>
       <c r="O248" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="249" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F249" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G249" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H249" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I249" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J249" t="s">
         <v>132</v>
       </c>
       <c r="K249" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L249">
         <v>32</v>
@@ -4950,27 +4968,27 @@
         <v>133</v>
       </c>
       <c r="O249" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="250" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F250" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G250" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H250" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I250" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J250" t="s">
         <v>132</v>
       </c>
       <c r="K250" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L250">
         <v>39</v>
@@ -4979,27 +4997,27 @@
         <v>133</v>
       </c>
       <c r="O250" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="251" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F251" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G251" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H251" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I251" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J251" t="s">
         <v>132</v>
       </c>
       <c r="K251" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L251">
         <v>46</v>
@@ -5008,24 +5026,24 @@
         <v>133</v>
       </c>
       <c r="O251" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="252" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F252" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H252" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I252" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J252" t="s">
         <v>132</v>
       </c>
       <c r="K252" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L252">
         <v>32</v>
@@ -5034,24 +5052,24 @@
         <v>133</v>
       </c>
       <c r="O252" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="253" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F253" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H253" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I253" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J253" t="s">
         <v>132</v>
       </c>
       <c r="K253" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L253">
         <v>38</v>
@@ -5060,24 +5078,24 @@
         <v>133</v>
       </c>
       <c r="O253" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="254" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F254" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H254" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I254" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J254" t="s">
         <v>132</v>
       </c>
       <c r="K254" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L254">
         <v>47</v>
@@ -5086,24 +5104,24 @@
         <v>133</v>
       </c>
       <c r="O254" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="255" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F255" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H255" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I255" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J255" t="s">
         <v>132</v>
       </c>
       <c r="K255" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L255">
         <v>33</v>
@@ -5112,24 +5130,24 @@
         <v>133</v>
       </c>
       <c r="O255" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="256" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F256" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H256" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I256" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J256" t="s">
         <v>132</v>
       </c>
       <c r="K256" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L256">
         <v>39</v>
@@ -5138,24 +5156,24 @@
         <v>133</v>
       </c>
       <c r="O256" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="257" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F257" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H257" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I257" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J257" t="s">
         <v>132</v>
       </c>
       <c r="K257" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L257">
         <v>47</v>
@@ -5164,21 +5182,21 @@
         <v>133</v>
       </c>
       <c r="O257" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="258" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F258" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I258" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J258" t="s">
         <v>132</v>
       </c>
       <c r="K258" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L258">
         <v>32</v>
@@ -5187,24 +5205,24 @@
         <v>133</v>
       </c>
       <c r="N258" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O258" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="259" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F259" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I259" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J259" t="s">
         <v>132</v>
       </c>
       <c r="K259" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L259">
         <v>39</v>
@@ -5213,24 +5231,24 @@
         <v>133</v>
       </c>
       <c r="N259" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O259" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="260" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F260" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I260" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J260" t="s">
         <v>132</v>
       </c>
       <c r="K260" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L260">
         <v>46</v>
@@ -5239,99 +5257,93 @@
         <v>133</v>
       </c>
       <c r="N260" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O260" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="261" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F261" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="I261" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="J261" t="s">
         <v>132</v>
       </c>
       <c r="K261" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L261">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="M261" t="s">
         <v>133</v>
       </c>
       <c r="O261" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
     </row>
     <row r="262" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F262" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I262" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="J262" t="s">
         <v>132</v>
       </c>
       <c r="K262" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L262">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="M262" t="s">
         <v>133</v>
       </c>
       <c r="O262" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="263" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F263" t="s">
-        <v>148</v>
-      </c>
-      <c r="H263" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="I263" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J263" t="s">
         <v>132</v>
       </c>
       <c r="K263" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L263">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="M263" t="s">
         <v>133</v>
       </c>
       <c r="O263" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="264" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F264" t="s">
-        <v>148</v>
-      </c>
-      <c r="H264" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="I264" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="J264" t="s">
         <v>132</v>
       </c>
       <c r="K264" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L264">
         <v>35</v>
@@ -5340,41 +5352,41 @@
         <v>133</v>
       </c>
       <c r="O264" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
     </row>
     <row r="265" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F265" t="s">
+        <v>147</v>
+      </c>
+      <c r="H265" t="s">
         <v>148</v>
       </c>
-      <c r="H265" t="s">
-        <v>149</v>
-      </c>
       <c r="I265" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="J265" t="s">
         <v>132</v>
       </c>
       <c r="K265" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L265">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="M265" t="s">
         <v>133</v>
       </c>
       <c r="O265" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="266" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F266" t="s">
+        <v>147</v>
+      </c>
+      <c r="H266" t="s">
         <v>148</v>
-      </c>
-      <c r="H266" t="s">
-        <v>150</v>
       </c>
       <c r="I266" t="s">
         <v>155</v>
@@ -5383,24 +5395,24 @@
         <v>132</v>
       </c>
       <c r="K266" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L266">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="M266" t="s">
         <v>133</v>
       </c>
       <c r="O266" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="267" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F267" t="s">
+        <v>147</v>
+      </c>
+      <c r="H267" t="s">
         <v>148</v>
-      </c>
-      <c r="H267" t="s">
-        <v>150</v>
       </c>
       <c r="I267" t="s">
         <v>156</v>
@@ -5409,50 +5421,50 @@
         <v>132</v>
       </c>
       <c r="K267" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L267">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="M267" t="s">
         <v>133</v>
       </c>
       <c r="O267" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="268" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F268" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H268" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I268" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="J268" t="s">
         <v>132</v>
       </c>
       <c r="K268" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L268">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="M268" t="s">
         <v>133</v>
       </c>
       <c r="O268" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="269" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F269" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H269" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="I269" t="s">
         <v>155</v>
@@ -5461,24 +5473,24 @@
         <v>132</v>
       </c>
       <c r="K269" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L269">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="M269" t="s">
         <v>133</v>
       </c>
       <c r="O269" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="270" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F270" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H270" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="I270" t="s">
         <v>156</v>
@@ -5487,50 +5499,50 @@
         <v>132</v>
       </c>
       <c r="K270" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L270">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="M270" t="s">
         <v>133</v>
       </c>
       <c r="O270" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="271" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F271" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H271" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I271" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="J271" t="s">
         <v>132</v>
       </c>
       <c r="K271" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L271">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="M271" t="s">
         <v>133</v>
       </c>
       <c r="O271" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="272" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F272" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H272" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I272" t="s">
         <v>155</v>
@@ -5539,28 +5551,24 @@
         <v>132</v>
       </c>
       <c r="K272" t="s">
-        <v>164</v>
-      </c>
-      <c r="L272" s="13">
-        <f>L263</f>
-        <v>30</v>
+        <v>163</v>
+      </c>
+      <c r="L272">
+        <v>35</v>
       </c>
       <c r="M272" t="s">
         <v>133</v>
       </c>
-      <c r="N272" t="s">
-        <v>160</v>
-      </c>
       <c r="O272" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="273" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F273" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H273" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I273" t="s">
         <v>156</v>
@@ -5569,94 +5577,98 @@
         <v>132</v>
       </c>
       <c r="K273" t="s">
-        <v>164</v>
-      </c>
-      <c r="L273" s="13">
-        <f t="shared" ref="L273:L274" si="4">L264</f>
-        <v>35</v>
+        <v>163</v>
+      </c>
+      <c r="L273">
+        <v>48</v>
       </c>
       <c r="M273" t="s">
         <v>133</v>
       </c>
-      <c r="N273" t="s">
-        <v>160</v>
-      </c>
       <c r="O273" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="274" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F274" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H274" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I274" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="J274" t="s">
         <v>132</v>
       </c>
       <c r="K274" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L274" s="13">
+        <f>L265</f>
+        <v>30</v>
+      </c>
+      <c r="M274" t="s">
+        <v>133</v>
+      </c>
+      <c r="N274" t="s">
+        <v>159</v>
+      </c>
+      <c r="O274" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="275" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="F275" t="s">
+        <v>147</v>
+      </c>
+      <c r="H275" t="s">
+        <v>151</v>
+      </c>
+      <c r="I275" t="s">
+        <v>155</v>
+      </c>
+      <c r="J275" t="s">
+        <v>132</v>
+      </c>
+      <c r="K275" t="s">
+        <v>163</v>
+      </c>
+      <c r="L275" s="13">
+        <f t="shared" ref="L275:L276" si="4">L266</f>
+        <v>35</v>
+      </c>
+      <c r="M275" t="s">
+        <v>133</v>
+      </c>
+      <c r="N275" t="s">
+        <v>159</v>
+      </c>
+      <c r="O275" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="276" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="F276" t="s">
+        <v>147</v>
+      </c>
+      <c r="H276" t="s">
+        <v>151</v>
+      </c>
+      <c r="I276" t="s">
+        <v>156</v>
+      </c>
+      <c r="J276" t="s">
+        <v>132</v>
+      </c>
+      <c r="K276" t="s">
+        <v>163</v>
+      </c>
+      <c r="L276" s="13">
         <f t="shared" si="4"/>
         <v>48</v>
       </c>
-      <c r="M274" t="s">
-        <v>133</v>
-      </c>
-      <c r="N274" t="s">
-        <v>160</v>
-      </c>
-      <c r="O274" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="275" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F275" t="s">
-        <v>148</v>
-      </c>
-      <c r="I275" t="s">
-        <v>155</v>
-      </c>
-      <c r="J275" t="s">
-        <v>132</v>
-      </c>
-      <c r="K275" t="s">
-        <v>164</v>
-      </c>
-      <c r="L275">
-        <v>29</v>
-      </c>
-      <c r="M275" t="s">
-        <v>133</v>
-      </c>
-      <c r="N275" t="s">
-        <v>159</v>
-      </c>
-      <c r="O275" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="276" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F276" t="s">
-        <v>148</v>
-      </c>
-      <c r="I276" t="s">
-        <v>156</v>
-      </c>
-      <c r="J276" t="s">
-        <v>132</v>
-      </c>
-      <c r="K276" t="s">
-        <v>164</v>
-      </c>
-      <c r="L276">
-        <v>35</v>
-      </c>
       <c r="M276" t="s">
         <v>133</v>
       </c>
@@ -5664,201 +5676,169 @@
         <v>159</v>
       </c>
       <c r="O276" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="277" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F277" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I277" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="J277" t="s">
         <v>132</v>
       </c>
       <c r="K277" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L277">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="M277" t="s">
         <v>133</v>
       </c>
       <c r="N277" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O277" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="278" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F278" t="s">
-        <v>153</v>
-      </c>
-      <c r="G278" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="I278" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J278" t="s">
         <v>132</v>
       </c>
       <c r="K278" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L278">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M278" t="s">
         <v>133</v>
       </c>
+      <c r="N278" t="s">
+        <v>158</v>
+      </c>
       <c r="O278" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="279" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F279" t="s">
-        <v>153</v>
-      </c>
-      <c r="G279" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="I279" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J279" t="s">
         <v>132</v>
       </c>
       <c r="K279" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L279">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M279" t="s">
         <v>133</v>
       </c>
+      <c r="N279" t="s">
+        <v>158</v>
+      </c>
       <c r="O279" t="s">
-        <v>171</v>
+        <v>170</v>
+      </c>
+    </row>
+    <row r="280" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="F280" t="s">
+        <v>152</v>
+      </c>
+      <c r="G280" t="s">
+        <v>153</v>
+      </c>
+      <c r="I280" t="s">
+        <v>155</v>
+      </c>
+      <c r="J280" t="s">
+        <v>132</v>
+      </c>
+      <c r="K280" t="s">
+        <v>163</v>
+      </c>
+      <c r="L280">
+        <v>41</v>
+      </c>
+      <c r="M280" t="s">
+        <v>133</v>
+      </c>
+      <c r="O280" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="281" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A281" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="B281" s="2"/>
-      <c r="C281" s="2"/>
-      <c r="D281" s="2"/>
-      <c r="E281" s="2"/>
-      <c r="F281" s="2"/>
-      <c r="G281" s="2"/>
-      <c r="H281" s="2"/>
-      <c r="I281" s="2"/>
-      <c r="J281" s="2"/>
-      <c r="K281" s="2"/>
-      <c r="L281" s="2"/>
-      <c r="M281" s="2"/>
-      <c r="N281" s="2"/>
-      <c r="O281" s="2"/>
+      <c r="F281" t="s">
+        <v>152</v>
+      </c>
+      <c r="G281" t="s">
+        <v>153</v>
+      </c>
+      <c r="I281" t="s">
+        <v>156</v>
+      </c>
+      <c r="J281" t="s">
+        <v>132</v>
+      </c>
+      <c r="K281" t="s">
+        <v>163</v>
+      </c>
+      <c r="L281">
+        <v>41</v>
+      </c>
+      <c r="M281" t="s">
+        <v>133</v>
+      </c>
+      <c r="O281" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="283" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="J283" t="s">
-        <v>173</v>
-      </c>
-      <c r="K283" t="s">
-        <v>174</v>
-      </c>
-      <c r="L283">
-        <v>1</v>
-      </c>
-      <c r="M283" t="s">
-        <v>128</v>
-      </c>
-      <c r="N283" t="s">
-        <v>184</v>
-      </c>
-      <c r="O283" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="284" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="J284" t="s">
-        <v>173</v>
-      </c>
-      <c r="K284" t="s">
+      <c r="A283" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="L284">
-        <v>1</v>
-      </c>
-      <c r="M284" t="s">
-        <v>128</v>
-      </c>
-      <c r="N284" t="s">
-        <v>180</v>
-      </c>
-      <c r="O284" t="s">
-        <v>178</v>
-      </c>
     </row>
     <row r="285" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F285" t="s">
-        <v>142</v>
-      </c>
-      <c r="I285" t="s">
-        <v>176</v>
-      </c>
-      <c r="J285" t="s">
-        <v>173</v>
-      </c>
-      <c r="K285" t="s">
-        <v>179</v>
-      </c>
-      <c r="L285">
-        <v>2</v>
-      </c>
-      <c r="M285" t="s">
-        <v>128</v>
-      </c>
-      <c r="N285" t="s">
-        <v>181</v>
-      </c>
-      <c r="O285" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="286" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="I286" t="s">
-        <v>176</v>
-      </c>
-      <c r="J286" t="s">
-        <v>173</v>
-      </c>
-      <c r="K286" t="s">
-        <v>179</v>
-      </c>
-      <c r="L286">
-        <v>1</v>
-      </c>
-      <c r="M286" t="s">
-        <v>128</v>
-      </c>
-      <c r="N286" t="s">
+      <c r="A285" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="O286" t="s">
-        <v>177</v>
-      </c>
+      <c r="B285" s="2"/>
+      <c r="C285" s="2"/>
+      <c r="D285" s="2"/>
+      <c r="E285" s="2"/>
+      <c r="F285" s="2"/>
+      <c r="G285" s="2"/>
+      <c r="H285" s="2"/>
+      <c r="I285" s="2"/>
+      <c r="J285" s="2"/>
+      <c r="K285" s="2"/>
+      <c r="L285" s="2"/>
+      <c r="M285" s="2"/>
+      <c r="N285" s="2"/>
+      <c r="O285" s="2"/>
     </row>
     <row r="287" spans="1:15" x14ac:dyDescent="0.25">
       <c r="J287" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K287" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="L287">
         <v>1</v>
@@ -5867,10 +5847,116 @@
         <v>128</v>
       </c>
       <c r="N287" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="O287" t="s">
-        <v>178</v>
+        <v>174</v>
+      </c>
+    </row>
+    <row r="288" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="J288" t="s">
+        <v>171</v>
+      </c>
+      <c r="K288" t="s">
+        <v>185</v>
+      </c>
+      <c r="L288">
+        <v>1</v>
+      </c>
+      <c r="M288" t="s">
+        <v>128</v>
+      </c>
+      <c r="N288" t="s">
+        <v>180</v>
+      </c>
+      <c r="O288" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="289" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="F289" t="s">
+        <v>141</v>
+      </c>
+      <c r="I289" t="s">
+        <v>172</v>
+      </c>
+      <c r="J289" t="s">
+        <v>171</v>
+      </c>
+      <c r="K289" t="s">
+        <v>185</v>
+      </c>
+      <c r="L289">
+        <v>2</v>
+      </c>
+      <c r="M289" t="s">
+        <v>128</v>
+      </c>
+      <c r="N289" t="s">
+        <v>175</v>
+      </c>
+      <c r="O289" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="290" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="I290" t="s">
+        <v>172</v>
+      </c>
+      <c r="J290" t="s">
+        <v>171</v>
+      </c>
+      <c r="K290" t="s">
+        <v>185</v>
+      </c>
+      <c r="L290">
+        <v>1</v>
+      </c>
+      <c r="M290" t="s">
+        <v>128</v>
+      </c>
+      <c r="N290" t="s">
+        <v>176</v>
+      </c>
+      <c r="O290" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="291" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="K291" t="s">
+        <v>184</v>
+      </c>
+      <c r="L291">
+        <v>1</v>
+      </c>
+      <c r="M291" t="s">
+        <v>128</v>
+      </c>
+      <c r="N291" t="s">
+        <v>187</v>
+      </c>
+      <c r="O291" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="292" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="J292" t="s">
+        <v>171</v>
+      </c>
+      <c r="K292" t="s">
+        <v>186</v>
+      </c>
+      <c r="L292">
+        <v>1</v>
+      </c>
+      <c r="M292" t="s">
+        <v>128</v>
+      </c>
+      <c r="N292" t="s">
+        <v>177</v>
+      </c>
+      <c r="O292" t="s">
+        <v>174</v>
       </c>
     </row>
   </sheetData>

--- a/data/prod_parameters/PlantNutrientMgmt.xlsx
+++ b/data/prod_parameters/PlantNutrientMgmt.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="192">
   <si>
     <t>f_crop</t>
   </si>
@@ -614,6 +614,12 @@
   </si>
   <si>
     <t>emission factors are available for different spreading techniques and timings. Use these!!!</t>
+  </si>
+  <si>
+    <t>soil_losses_organic_soils</t>
+  </si>
+  <si>
+    <t>kg N2O-N/ha</t>
   </si>
 </sst>
 </file>
@@ -1013,7 +1019,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R292"/>
+  <dimension ref="A1:R294"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -5923,6 +5929,9 @@
       </c>
     </row>
     <row r="291" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="J291" t="s">
+        <v>171</v>
+      </c>
       <c r="K291" t="s">
         <v>184</v>
       </c>
@@ -5957,6 +5966,20 @@
       </c>
       <c r="O292" t="s">
         <v>174</v>
+      </c>
+    </row>
+    <row r="294" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="J294" t="s">
+        <v>171</v>
+      </c>
+      <c r="K294" t="s">
+        <v>190</v>
+      </c>
+      <c r="L294">
+        <v>13</v>
+      </c>
+      <c r="M294" t="s">
+        <v>191</v>
       </c>
     </row>
   </sheetData>

--- a/data/prod_parameters/PlantNutrientMgmt.xlsx
+++ b/data/prod_parameters/PlantNutrientMgmt.xlsx
@@ -322,9 +322,6 @@
     <t>po8</t>
   </si>
   <si>
-    <t>f_po8</t>
-  </si>
-  <si>
     <t>Höstvete foder/bröd, södra götaland</t>
   </si>
   <si>
@@ -620,6 +617,9 @@
   </si>
   <si>
     <t>kg N2O-N/ha</t>
+  </si>
+  <si>
+    <t>f_po8:region</t>
   </si>
 </sst>
 </file>
@@ -1041,7 +1041,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>100</v>
+        <v>191</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>90</v>
@@ -1050,22 +1050,22 @@
         <v>8</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="J1" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>1</v>
@@ -1085,7 +1085,7 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -1104,44 +1104,44 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L4">
         <v>91</v>
       </c>
       <c r="M4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N4" t="s">
+        <v>121</v>
+      </c>
+      <c r="O4" t="s">
         <v>122</v>
-      </c>
-      <c r="O4" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L5">
         <v>22</v>
       </c>
       <c r="M5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -1160,87 +1160,87 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N8" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="L9">
         <v>59</v>
       </c>
       <c r="M9" t="s">
+        <v>127</v>
+      </c>
+      <c r="N9" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="O9" t="s">
         <v>128</v>
-      </c>
-      <c r="N9" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="O9" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="L10">
         <v>7</v>
       </c>
       <c r="M10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="L11">
         <v>34</v>
       </c>
       <c r="M11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -1304,7 +1304,7 @@
         <v>-0.80359999999999998</v>
       </c>
       <c r="N17" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
@@ -1357,7 +1357,7 @@
         <v>-0.71430000000000005</v>
       </c>
       <c r="N21" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
@@ -1544,7 +1544,7 @@
         <v>-1.25</v>
       </c>
       <c r="N34" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
@@ -1668,7 +1668,7 @@
         <v>-0.71430000000000005</v>
       </c>
       <c r="N42" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
@@ -1843,7 +1843,7 @@
         <v>-1.25</v>
       </c>
       <c r="N54" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
@@ -1891,7 +1891,7 @@
         <v>-2E-12</v>
       </c>
       <c r="N57" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
@@ -2049,7 +2049,7 @@
         <v>0</v>
       </c>
       <c r="N66" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
@@ -2295,7 +2295,7 @@
         <v>-1.25</v>
       </c>
       <c r="N81" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
@@ -2771,7 +2771,7 @@
         <v>-2.5000000000000001E-2</v>
       </c>
       <c r="N113" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.25">
@@ -3145,7 +3145,7 @@
         <v>1.3846000000000001</v>
       </c>
       <c r="N137" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="138" spans="1:15" x14ac:dyDescent="0.25">
@@ -3389,7 +3389,7 @@
         <v>3.3332999999999999</v>
       </c>
       <c r="N149" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="150" spans="1:15" x14ac:dyDescent="0.25">
@@ -3527,7 +3527,7 @@
         <v>100</v>
       </c>
       <c r="N157" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="158" spans="1:15" x14ac:dyDescent="0.25">
@@ -3671,7 +3671,7 @@
     </row>
     <row r="170" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
@@ -4743,7 +4743,7 @@
     </row>
     <row r="239" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B239" s="2"/>
       <c r="C239" s="2"/>
@@ -4762,24 +4762,24 @@
     </row>
     <row r="240" spans="1:15" x14ac:dyDescent="0.25">
       <c r="J240" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K240" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L240" s="14">
         <v>0</v>
       </c>
       <c r="M240" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="N240" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="241" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J241" s="6"/>
       <c r="K241" s="6"/>
@@ -4789,1040 +4789,1040 @@
     </row>
     <row r="242" spans="1:15" x14ac:dyDescent="0.25">
       <c r="E242" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J242" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K242" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L242" s="12">
         <f>8/1000*(14/(1*14+3*2))*100</f>
         <v>0.55999999999999994</v>
       </c>
       <c r="M242" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="N242" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O242" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="243" spans="1:15" x14ac:dyDescent="0.25">
       <c r="E243" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J243" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K243" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L243" s="12">
         <f>15/1000*(14/(1*14+3*2))*100</f>
         <v>1.0499999999999998</v>
       </c>
       <c r="M243" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O243" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="244" spans="1:15" x14ac:dyDescent="0.25">
       <c r="E244" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J244" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K244" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L244" s="12">
         <f>50/1000*(14/(1*14+3*2))*100</f>
         <v>3.4999999999999996</v>
       </c>
       <c r="M244" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O244" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="245" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B245" s="7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="246" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F246" t="s">
+        <v>140</v>
+      </c>
+      <c r="G246" t="s">
         <v>141</v>
       </c>
-      <c r="G246" t="s">
+      <c r="H246" t="s">
         <v>142</v>
       </c>
-      <c r="H246" t="s">
-        <v>143</v>
-      </c>
       <c r="I246" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J246" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K246" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L246">
         <v>33</v>
       </c>
       <c r="M246" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O246" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="247" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F247" t="s">
+        <v>140</v>
+      </c>
+      <c r="G247" t="s">
         <v>141</v>
       </c>
-      <c r="G247" t="s">
+      <c r="H247" t="s">
         <v>142</v>
       </c>
-      <c r="H247" t="s">
-        <v>143</v>
-      </c>
       <c r="I247" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J247" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K247" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L247">
         <v>38</v>
       </c>
       <c r="M247" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O247" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="248" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F248" t="s">
+        <v>140</v>
+      </c>
+      <c r="G248" t="s">
         <v>141</v>
       </c>
-      <c r="G248" t="s">
+      <c r="H248" t="s">
         <v>142</v>
       </c>
-      <c r="H248" t="s">
-        <v>143</v>
-      </c>
       <c r="I248" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J248" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K248" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L248">
         <v>41</v>
       </c>
       <c r="M248" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O248" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="249" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F249" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G249" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H249" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I249" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J249" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K249" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L249">
         <v>32</v>
       </c>
       <c r="M249" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O249" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="250" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F250" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G250" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H250" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I250" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J250" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K250" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L250">
         <v>39</v>
       </c>
       <c r="M250" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O250" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="251" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F251" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G251" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H251" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I251" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J251" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K251" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L251">
         <v>46</v>
       </c>
       <c r="M251" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O251" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="252" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F252" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H252" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I252" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J252" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K252" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L252">
         <v>32</v>
       </c>
       <c r="M252" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O252" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="253" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F253" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H253" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I253" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J253" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K253" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L253">
         <v>38</v>
       </c>
       <c r="M253" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O253" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="254" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F254" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H254" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I254" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J254" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K254" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L254">
         <v>47</v>
       </c>
       <c r="M254" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O254" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="255" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F255" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H255" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I255" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J255" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K255" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L255">
         <v>33</v>
       </c>
       <c r="M255" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O255" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="256" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F256" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H256" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I256" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J256" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K256" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L256">
         <v>39</v>
       </c>
       <c r="M256" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O256" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="257" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F257" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H257" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I257" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J257" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K257" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L257">
         <v>47</v>
       </c>
       <c r="M257" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O257" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="258" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F258" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I258" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J258" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K258" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L258">
         <v>32</v>
       </c>
       <c r="M258" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="N258" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O258" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="259" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F259" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I259" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J259" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K259" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L259">
         <v>39</v>
       </c>
       <c r="M259" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="N259" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O259" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="260" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F260" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I260" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J260" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K260" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L260">
         <v>46</v>
       </c>
       <c r="M260" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="N260" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O260" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="261" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F261" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I261" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J261" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K261" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L261">
         <v>14</v>
       </c>
       <c r="M261" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O261" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="262" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F262" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I262" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J262" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K262" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L262">
         <v>43</v>
       </c>
       <c r="M262" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O262" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="263" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F263" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I263" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J263" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K263" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L263">
         <v>47</v>
       </c>
       <c r="M263" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O263" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="264" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F264" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I264" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J264" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K264" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L264">
         <v>35</v>
       </c>
       <c r="M264" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O264" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="265" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F265" t="s">
+        <v>146</v>
+      </c>
+      <c r="H265" t="s">
         <v>147</v>
       </c>
-      <c r="H265" t="s">
-        <v>148</v>
-      </c>
       <c r="I265" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J265" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K265" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L265">
         <v>30</v>
       </c>
       <c r="M265" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O265" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="266" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F266" t="s">
+        <v>146</v>
+      </c>
+      <c r="H266" t="s">
         <v>147</v>
       </c>
-      <c r="H266" t="s">
-        <v>148</v>
-      </c>
       <c r="I266" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J266" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K266" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L266">
         <v>35</v>
       </c>
       <c r="M266" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O266" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="267" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F267" t="s">
+        <v>146</v>
+      </c>
+      <c r="H267" t="s">
         <v>147</v>
       </c>
-      <c r="H267" t="s">
-        <v>148</v>
-      </c>
       <c r="I267" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J267" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K267" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L267">
         <v>48</v>
       </c>
       <c r="M267" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O267" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="268" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F268" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H268" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I268" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J268" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K268" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L268">
         <v>29</v>
       </c>
       <c r="M268" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O268" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="269" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F269" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H269" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I269" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J269" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K269" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L269">
         <v>34</v>
       </c>
       <c r="M269" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O269" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="270" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F270" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H270" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I270" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J270" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K270" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L270">
         <v>46</v>
       </c>
       <c r="M270" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O270" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="271" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F271" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H271" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I271" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J271" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K271" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L271">
         <v>29</v>
       </c>
       <c r="M271" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O271" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="272" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F272" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H272" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I272" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J272" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K272" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L272">
         <v>35</v>
       </c>
       <c r="M272" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O272" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="273" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F273" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H273" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I273" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J273" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K273" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L273">
         <v>48</v>
       </c>
       <c r="M273" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O273" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="274" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F274" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H274" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I274" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J274" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K274" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L274" s="13">
         <f>L265</f>
         <v>30</v>
       </c>
       <c r="M274" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="N274" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O274" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="275" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F275" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H275" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I275" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J275" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K275" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L275" s="13">
         <f t="shared" ref="L275:L276" si="4">L266</f>
         <v>35</v>
       </c>
       <c r="M275" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="N275" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O275" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="276" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F276" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H276" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I276" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J276" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K276" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L276" s="13">
         <f t="shared" si="4"/>
         <v>48</v>
       </c>
       <c r="M276" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="N276" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O276" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="277" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F277" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I277" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J277" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K277" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L277">
         <v>29</v>
       </c>
       <c r="M277" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="N277" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O277" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="278" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F278" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I278" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J278" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K278" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L278">
         <v>35</v>
       </c>
       <c r="M278" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="N278" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O278" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="279" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F279" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I279" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J279" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K279" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L279">
         <v>44</v>
       </c>
       <c r="M279" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="N279" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O279" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="280" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F280" t="s">
+        <v>151</v>
+      </c>
+      <c r="G280" t="s">
         <v>152</v>
       </c>
-      <c r="G280" t="s">
-        <v>153</v>
-      </c>
       <c r="I280" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J280" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K280" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L280">
         <v>41</v>
       </c>
       <c r="M280" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O280" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="281" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F281" t="s">
+        <v>151</v>
+      </c>
+      <c r="G281" t="s">
         <v>152</v>
       </c>
-      <c r="G281" t="s">
-        <v>153</v>
-      </c>
       <c r="I281" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J281" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K281" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L281">
         <v>41</v>
       </c>
       <c r="M281" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O281" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="283" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A283" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="285" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B285" s="2"/>
       <c r="C285" s="2"/>
@@ -5841,145 +5841,145 @@
     </row>
     <row r="287" spans="1:15" x14ac:dyDescent="0.25">
       <c r="J287" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K287" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="L287">
         <v>1</v>
       </c>
       <c r="M287" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N287" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O287" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="288" spans="1:15" x14ac:dyDescent="0.25">
       <c r="J288" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K288" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L288">
         <v>1</v>
       </c>
       <c r="M288" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N288" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O288" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="289" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F289" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I289" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J289" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K289" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L289">
         <v>2</v>
       </c>
       <c r="M289" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N289" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O289" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="290" spans="6:15" x14ac:dyDescent="0.25">
       <c r="I290" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J290" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K290" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L290">
         <v>1</v>
       </c>
       <c r="M290" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N290" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="O290" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="291" spans="6:15" x14ac:dyDescent="0.25">
       <c r="J291" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K291" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L291">
         <v>1</v>
       </c>
       <c r="M291" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N291" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O291" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="292" spans="6:15" x14ac:dyDescent="0.25">
       <c r="J292" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K292" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="L292">
         <v>1</v>
       </c>
       <c r="M292" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N292" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="O292" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="294" spans="6:15" x14ac:dyDescent="0.25">
       <c r="J294" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K294" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L294">
         <v>13</v>
       </c>
       <c r="M294" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
